--- a/database/event/6868/event_6868_evp_summary.xlsx
+++ b/database/event/6868/event_6868_evp_summary.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,72 +418,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>evp_score</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>weighted_evp_score</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>z_score</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>normalized_score</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Norm_Group_Score_Scaled</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Norm_Playoff_Score</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Norm_Group_Score</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Raw_Group_Score</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Raw_Playoff_Score</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>group_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>playoff_weighted_rounds_played</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>total_weighted_score</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>total_weighted_rounds_played</t>
         </is>
@@ -504,219 +492,219 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sdy</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.0593</v>
+        <v>6.1471</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6059300000000001</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1.74527963666662</v>
+        <v>2.0619</v>
       </c>
       <c r="E2" t="n">
-        <v>62.7002</v>
+        <v>6.1471</v>
       </c>
       <c r="F2" t="n">
-        <v>30.10869745742382</v>
+        <v>4.3184</v>
       </c>
       <c r="G2" t="n">
-        <v>32.59146126565393</v>
+        <v>1.8287</v>
       </c>
       <c r="H2" t="n">
-        <v>30.11965434926753</v>
+        <v>4.8136</v>
       </c>
       <c r="I2" t="n">
-        <v>13.94262931301405</v>
+        <v>3.9016</v>
       </c>
       <c r="J2" t="n">
-        <v>32.59146126565393</v>
+        <v>1.8287</v>
       </c>
       <c r="K2" t="n">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="L2" t="n">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="M2" t="n">
-        <v>46.5341</v>
+        <v>5.7303</v>
       </c>
       <c r="N2" t="n">
-        <v>160</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>sdy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.9797</v>
+        <v>5.6211</v>
       </c>
       <c r="C3" t="n">
-        <v>0.59797</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1.709109271880101</v>
+        <v>1.8494</v>
       </c>
       <c r="E3" t="n">
-        <v>61.1263</v>
+        <v>5.6211</v>
       </c>
       <c r="F3" t="n">
-        <v>22.58476488718355</v>
+        <v>2.4171</v>
       </c>
       <c r="G3" t="n">
-        <v>38.54155635407221</v>
+        <v>3.204</v>
       </c>
       <c r="H3" t="n">
-        <v>22.58476488718355</v>
+        <v>2.4171</v>
       </c>
       <c r="I3" t="n">
-        <v>27.0749110220242</v>
+        <v>1.9591</v>
       </c>
       <c r="J3" t="n">
-        <v>38.54155635407221</v>
+        <v>3.204</v>
       </c>
       <c r="K3" t="n">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="L3" t="n">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="M3" t="n">
-        <v>65.6165</v>
+        <v>5.1631</v>
       </c>
       <c r="N3" t="n">
-        <v>252</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>br0</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.9988</v>
+        <v>4.8504</v>
       </c>
       <c r="C4" t="n">
-        <v>0.49988</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1.300523632302087</v>
+        <v>1.5381</v>
       </c>
       <c r="E4" t="n">
-        <v>43.348</v>
+        <v>4.8504</v>
       </c>
       <c r="F4" t="n">
-        <v>4.709649178928794</v>
+        <v>4.2604</v>
       </c>
       <c r="G4" t="n">
-        <v>38.6383776520434</v>
+        <v>0.59</v>
       </c>
       <c r="H4" t="n">
-        <v>4.709649178928794</v>
+        <v>4.58</v>
       </c>
       <c r="I4" t="n">
-        <v>2.180134338020451</v>
+        <v>3.7122</v>
       </c>
       <c r="J4" t="n">
-        <v>38.6383776520434</v>
+        <v>0.59</v>
       </c>
       <c r="K4" t="n">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="L4" t="n">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="M4" t="n">
-        <v>40.8185</v>
+        <v>4.3022</v>
       </c>
       <c r="N4" t="n">
-        <v>160</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>Calyx</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.0323</v>
+        <v>3.2913</v>
       </c>
       <c r="C5" t="n">
-        <v>0.40323</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9582358347474831</v>
+        <v>0.9082</v>
       </c>
       <c r="E5" t="n">
-        <v>28.4545</v>
+        <v>3.2913</v>
       </c>
       <c r="F5" t="n">
-        <v>15.94269151912839</v>
+        <v>3.373</v>
       </c>
       <c r="G5" t="n">
-        <v>12.51177898358381</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>15.94269151912839</v>
+        <v>3.373</v>
       </c>
       <c r="I5" t="n">
-        <v>21.19384510554753</v>
+        <v>2.7339</v>
       </c>
       <c r="J5" t="n">
-        <v>12.51177898358381</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="L5" t="n">
-        <v>63</v>
+        <v>151</v>
       </c>
       <c r="M5" t="n">
-        <v>33.7056</v>
+        <v>2.6522</v>
       </c>
       <c r="N5" t="n">
-        <v>175</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.7715</v>
+        <v>2.8898</v>
       </c>
       <c r="C6" t="n">
-        <v>0.37715</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8749419856291349</v>
+        <v>0.7461</v>
       </c>
       <c r="E6" t="n">
-        <v>24.8302</v>
+        <v>2.8898</v>
       </c>
       <c r="F6" t="n">
-        <v>1.100825215999256</v>
+        <v>1.9086</v>
       </c>
       <c r="G6" t="n">
-        <v>23.72938043560089</v>
+        <v>0.9812</v>
       </c>
       <c r="H6" t="n">
-        <v>1.100825215999256</v>
+        <v>1.9086</v>
       </c>
       <c r="I6" t="n">
-        <v>1.463411563108804</v>
+        <v>1.547</v>
       </c>
       <c r="J6" t="n">
-        <v>23.72938043560089</v>
+        <v>0.9812</v>
       </c>
       <c r="K6" t="n">
         <v>112</v>
@@ -725,7 +713,7 @@
         <v>63</v>
       </c>
       <c r="M6" t="n">
-        <v>25.1928</v>
+        <v>2.5282</v>
       </c>
       <c r="N6" t="n">
         <v>175</v>
@@ -734,722 +722,722 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Djoko</t>
+          <t>br0</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.9937</v>
+        <v>2.8344</v>
       </c>
       <c r="C7" t="n">
-        <v>0.29937</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6469848218798453</v>
+        <v>0.7237</v>
       </c>
       <c r="E7" t="n">
-        <v>14.9114</v>
+        <v>2.8344</v>
       </c>
       <c r="F7" t="n">
-        <v>14.9113803736151</v>
+        <v>0.7668</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2.0676</v>
       </c>
       <c r="H7" t="n">
-        <v>14.9113803736151</v>
+        <v>0.7668</v>
       </c>
       <c r="I7" t="n">
-        <v>15.04412263213393</v>
+        <v>0.6215000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2.0676</v>
       </c>
       <c r="K7" t="n">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="M7" t="n">
-        <v>15.0441</v>
+        <v>2.6891</v>
       </c>
       <c r="N7" t="n">
-        <v>85</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.6011</v>
+        <v>2.7961</v>
       </c>
       <c r="C8" t="n">
-        <v>0.26011</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5426857901779369</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>10.3731</v>
+        <v>2.7961</v>
       </c>
       <c r="F8" t="n">
-        <v>2.763522902622954</v>
+        <v>2.2933</v>
       </c>
       <c r="G8" t="n">
-        <v>7.609619430567872</v>
+        <v>0.5028</v>
       </c>
       <c r="H8" t="n">
-        <v>2.763522902622954</v>
+        <v>2.2933</v>
       </c>
       <c r="I8" t="n">
-        <v>2.26330065615411</v>
+        <v>1.8588</v>
       </c>
       <c r="J8" t="n">
-        <v>7.609619430567872</v>
+        <v>0.5028</v>
       </c>
       <c r="K8" t="n">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="L8" t="n">
-        <v>93</v>
+        <v>151</v>
       </c>
       <c r="M8" t="n">
-        <v>9.8729</v>
+        <v>2.3616</v>
       </c>
       <c r="N8" t="n">
-        <v>162</v>
+        <v>252</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>brnz4n</t>
+          <t>kRaSnaL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.5757</v>
+        <v>2.3473</v>
       </c>
       <c r="C9" t="n">
-        <v>0.25757</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5361544672167396</v>
+        <v>0.5269</v>
       </c>
       <c r="E9" t="n">
-        <v>10.089</v>
+        <v>2.3473</v>
       </c>
       <c r="F9" t="n">
-        <v>9.882054405920149</v>
+        <v>1.8273</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2068983443652783</v>
+        <v>0.52</v>
       </c>
       <c r="H9" t="n">
-        <v>9.882054405920149</v>
+        <v>1.8273</v>
       </c>
       <c r="I9" t="n">
-        <v>8.093314587637867</v>
+        <v>1.4811</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2068983443652783</v>
+        <v>0.52</v>
       </c>
       <c r="K9" t="n">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="L9" t="n">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="M9" t="n">
-        <v>8.3002</v>
+        <v>2.0011</v>
       </c>
       <c r="N9" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ex3rcice</t>
+          <t>insani</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.6709</v>
+        <v>2.2831</v>
       </c>
       <c r="C10" t="n">
-        <v>0.16709</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3211242899284567</v>
+        <v>0.501</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7326</v>
+        <v>2.2831</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7326038514968753</v>
+        <v>2.5591</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0.276</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7326038514968753</v>
+        <v>2.5591</v>
       </c>
       <c r="I10" t="n">
-        <v>0.739125547504266</v>
+        <v>2.0742</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0.276</v>
       </c>
       <c r="K10" t="n">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7391</v>
+        <v>1.7982</v>
       </c>
       <c r="N10" t="n">
-        <v>85</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>volt</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.6649</v>
+        <v>2.161</v>
       </c>
       <c r="C11" t="n">
-        <v>0.16649</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3198039900817428</v>
+        <v>0.4516</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6752</v>
+        <v>2.161</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6751552358064788</v>
+        <v>0.7035</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1.4575</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6751552358064788</v>
+        <v>0.7035</v>
       </c>
       <c r="I11" t="n">
-        <v>1.025755135705986</v>
+        <v>0.5702</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1.4575</v>
       </c>
       <c r="K11" t="n">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M11" t="n">
-        <v>1.0258</v>
+        <v>2.0277</v>
       </c>
       <c r="N11" t="n">
-        <v>128</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>DemQQ</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.6605</v>
+        <v>1.9003</v>
       </c>
       <c r="C12" t="n">
-        <v>0.16605</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3188333503502461</v>
+        <v>0.3463</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6329</v>
+        <v>1.9003</v>
       </c>
       <c r="F12" t="n">
-        <v>15.97634892505541</v>
+        <v>1.9975</v>
       </c>
       <c r="G12" t="n">
-        <v>-15.34342796583948</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>15.97634892505541</v>
+        <v>1.9975</v>
       </c>
       <c r="I12" t="n">
-        <v>19.15265568463616</v>
+        <v>1.619</v>
       </c>
       <c r="J12" t="n">
-        <v>-15.34342796583948</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="L12" t="n">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8092</v>
+        <v>1.5218</v>
       </c>
       <c r="N12" t="n">
-        <v>252</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>insani</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.552</v>
+        <v>1.8867</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1552</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.295211758623169</v>
+        <v>0.3408</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3949</v>
+        <v>1.8867</v>
       </c>
       <c r="F13" t="n">
-        <v>35.15689589742447</v>
+        <v>2.656</v>
       </c>
       <c r="G13" t="n">
-        <v>-35.5517927846635</v>
+        <v>-0.7693</v>
       </c>
       <c r="H13" t="n">
-        <v>36.23570728670916</v>
+        <v>2.656</v>
       </c>
       <c r="I13" t="n">
-        <v>29.6767216947529</v>
+        <v>2.1528</v>
       </c>
       <c r="J13" t="n">
-        <v>-35.5517927846635</v>
+        <v>-0.7693</v>
       </c>
       <c r="K13" t="n">
-        <v>69</v>
+        <v>112</v>
       </c>
       <c r="L13" t="n">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.8751</v>
+        <v>1.3835</v>
       </c>
       <c r="N13" t="n">
-        <v>162</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kRaSnaL</t>
+          <t>Djoko</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.3505</v>
+        <v>1.7884</v>
       </c>
       <c r="C14" t="n">
-        <v>0.13505</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2524362624081374</v>
+        <v>0.3011</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.2561</v>
+        <v>1.7884</v>
       </c>
       <c r="F14" t="n">
-        <v>23.21194480744597</v>
+        <v>1.7884</v>
       </c>
       <c r="G14" t="n">
-        <v>-25.46808029827914</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>23.21194480744597</v>
+        <v>1.7884</v>
       </c>
       <c r="I14" t="n">
-        <v>10.7449952224379</v>
+        <v>1.7884</v>
       </c>
       <c r="J14" t="n">
-        <v>-25.46808029827914</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="L14" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-14.7231</v>
+        <v>1.7884</v>
       </c>
       <c r="N14" t="n">
-        <v>160</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>brnz4n</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.0631</v>
+        <v>1.6528</v>
       </c>
       <c r="C15" t="n">
-        <v>0.10631</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1938463987623586</v>
+        <v>0.2463</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.8055</v>
+        <v>1.6528</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.805485601201267</v>
+        <v>0.5311</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1.1217</v>
       </c>
       <c r="H15" t="n">
-        <v>-4.805485601201267</v>
+        <v>0.5311</v>
       </c>
       <c r="I15" t="n">
-        <v>-4.848264404772791</v>
+        <v>0.4305</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1.1217</v>
       </c>
       <c r="K15" t="n">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="M15" t="n">
-        <v>-4.8483</v>
+        <v>1.5522</v>
       </c>
       <c r="N15" t="n">
-        <v>85</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cynic</t>
+          <t>volt</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9133</v>
+        <v>1.6244</v>
       </c>
       <c r="C16" t="n">
-        <v>0.09133000000000001</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.164409361010709</v>
+        <v>0.2349</v>
       </c>
       <c r="E16" t="n">
-        <v>-6.0863</v>
+        <v>1.6244</v>
       </c>
       <c r="F16" t="n">
-        <v>-6.086343940363557</v>
+        <v>1.6244</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>-6.086343940363557</v>
+        <v>1.6244</v>
       </c>
       <c r="I16" t="n">
-        <v>-5.996042101485759</v>
+        <v>1.6244</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>83</v>
+        <v>128</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-5.996</v>
+        <v>1.6244</v>
       </c>
       <c r="N16" t="n">
-        <v>83</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DemQQ</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6058</v>
+        <v>1.4712</v>
       </c>
       <c r="C17" t="n">
-        <v>0.06058</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1062435638702001</v>
+        <v>0.173</v>
       </c>
       <c r="E17" t="n">
-        <v>-8.6172</v>
+        <v>1.4712</v>
       </c>
       <c r="F17" t="n">
-        <v>23.3550524838384</v>
+        <v>2.2078</v>
       </c>
       <c r="G17" t="n">
-        <v>-31.97229463991214</v>
+        <v>-0.7366</v>
       </c>
       <c r="H17" t="n">
-        <v>23.3550524838384</v>
+        <v>2.2078</v>
       </c>
       <c r="I17" t="n">
-        <v>10.81124091239997</v>
+        <v>1.7895</v>
       </c>
       <c r="J17" t="n">
-        <v>-31.97229463991214</v>
+        <v>-0.7366</v>
       </c>
       <c r="K17" t="n">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c r="L17" t="n">
-        <v>121</v>
+        <v>63</v>
       </c>
       <c r="M17" t="n">
-        <v>-21.1611</v>
+        <v>1.0529</v>
       </c>
       <c r="N17" t="n">
-        <v>160</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>hAdji</t>
+          <t>exit</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5345</v>
+        <v>1.2192</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05345</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.09317354091650337</v>
+        <v>0.0712</v>
       </c>
       <c r="E18" t="n">
-        <v>-9.1859</v>
+        <v>1.2192</v>
       </c>
       <c r="F18" t="n">
-        <v>-9.185942309755026</v>
+        <v>0.39</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.8292</v>
       </c>
       <c r="H18" t="n">
-        <v>-9.185942309755026</v>
+        <v>0.39</v>
       </c>
       <c r="I18" t="n">
-        <v>-9.26771627690418</v>
+        <v>0.3161</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.8292</v>
       </c>
       <c r="K18" t="n">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="M18" t="n">
-        <v>-9.2677</v>
+        <v>1.1453</v>
       </c>
       <c r="N18" t="n">
-        <v>85</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1984</v>
+        <v>0.9643</v>
       </c>
       <c r="C19" t="n">
-        <v>0.01984</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.03361250522079211</v>
+        <v>-0.0318</v>
       </c>
       <c r="E19" t="n">
-        <v>-11.7775</v>
+        <v>0.9643</v>
       </c>
       <c r="F19" t="n">
-        <v>-11.77754985884409</v>
+        <v>0.4846</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.4797</v>
       </c>
       <c r="H19" t="n">
-        <v>-11.77754985884409</v>
+        <v>0.4846</v>
       </c>
       <c r="I19" t="n">
-        <v>-17.89348821284324</v>
+        <v>0.3928</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.4797</v>
       </c>
       <c r="K19" t="n">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M19" t="n">
-        <v>-17.8935</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>128</v>
+        <v>175</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>Ex3rcice</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.05</v>
+        <v>0.824</v>
       </c>
       <c r="C20" t="n">
-        <v>0.005000000000000001</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.008374822691351291</v>
+        <v>-0.0885</v>
       </c>
       <c r="E20" t="n">
-        <v>-12.8757</v>
+        <v>0.824</v>
       </c>
       <c r="F20" t="n">
-        <v>-15.10262494356211</v>
+        <v>0.824</v>
       </c>
       <c r="G20" t="n">
-        <v>2.226938227277149</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-15.10262494356211</v>
+        <v>0.824</v>
       </c>
       <c r="I20" t="n">
-        <v>-20.07708004366713</v>
+        <v>0.824</v>
       </c>
       <c r="J20" t="n">
-        <v>2.226938227277149</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="L20" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-17.8501</v>
+        <v>0.824</v>
       </c>
       <c r="N20" t="n">
-        <v>175</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>acoR</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0174</v>
+        <v>0.8168</v>
       </c>
       <c r="C21" t="n">
-        <v>0.00174</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.002905526556222226</v>
+        <v>-0.0914</v>
       </c>
       <c r="E21" t="n">
-        <v>-13.1137</v>
+        <v>0.8168</v>
       </c>
       <c r="F21" t="n">
-        <v>17.05390904894953</v>
+        <v>0.8168</v>
       </c>
       <c r="G21" t="n">
-        <v>-30.16757465506472</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>17.05390904894953</v>
+        <v>0.8168</v>
       </c>
       <c r="I21" t="n">
-        <v>22.67107197011688</v>
+        <v>0.8168</v>
       </c>
       <c r="J21" t="n">
-        <v>-30.16757465506472</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="L21" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-7.4965</v>
+        <v>0.8168</v>
       </c>
       <c r="N21" t="n">
-        <v>175</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Bwills</t>
+          <t>cynic</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1158</v>
+        <v>0.7135</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.01158</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.01947913645941063</v>
+        <v>-0.1331</v>
       </c>
       <c r="E22" t="n">
-        <v>-14.0877</v>
+        <v>0.7135</v>
       </c>
       <c r="F22" t="n">
-        <v>-14.08766246459</v>
+        <v>0.7135</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-14.08766246459</v>
+        <v>0.7135</v>
       </c>
       <c r="I22" t="n">
-        <v>-13.87864670102042</v>
+        <v>0.7135</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1461,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-13.8786</v>
+        <v>0.7135</v>
       </c>
       <c r="N22" t="n">
         <v>83</v>
@@ -1470,78 +1458,78 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.1167</v>
+        <v>0.4871</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.01167</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.01964371021072872</v>
+        <v>-0.2246</v>
       </c>
       <c r="E23" t="n">
-        <v>-14.0948</v>
+        <v>0.4871</v>
       </c>
       <c r="F23" t="n">
-        <v>-9.007756688156958</v>
+        <v>0.4871</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.087066675690687</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-9.007756688156958</v>
+        <v>0.4871</v>
       </c>
       <c r="I23" t="n">
-        <v>-7.377272539855549</v>
+        <v>0.4871</v>
       </c>
       <c r="J23" t="n">
-        <v>-5.087066675690687</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="L23" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-12.4643</v>
+        <v>0.4871</v>
       </c>
       <c r="N23" t="n">
-        <v>162</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>acoR</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.1354</v>
+        <v>0.3731</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.01354</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.02281961155133483</v>
+        <v>-0.2706</v>
       </c>
       <c r="E24" t="n">
-        <v>-14.233</v>
+        <v>0.3731</v>
       </c>
       <c r="F24" t="n">
-        <v>-14.23301253052914</v>
+        <v>0.3731</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-14.23301253052914</v>
+        <v>0.3731</v>
       </c>
       <c r="I24" t="n">
-        <v>-21.62404277635287</v>
+        <v>0.3731</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1553,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-21.624</v>
+        <v>0.3731</v>
       </c>
       <c r="N24" t="n">
         <v>128</v>
@@ -1562,32 +1550,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MarKE</t>
+          <t>Bwills</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.4851</v>
+        <v>0.135</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.04851</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.08421258206745828</v>
+        <v>-0.3668</v>
       </c>
       <c r="E25" t="n">
-        <v>-16.9043</v>
+        <v>0.135</v>
       </c>
       <c r="F25" t="n">
-        <v>-16.90433085117487</v>
+        <v>0.135</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-16.90433085117487</v>
+        <v>0.135</v>
       </c>
       <c r="I25" t="n">
-        <v>-16.6535247554601</v>
+        <v>0.135</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1599,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-16.6535</v>
+        <v>0.135</v>
       </c>
       <c r="N25" t="n">
         <v>83</v>
@@ -1608,78 +1596,78 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>hAdji</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.4925</v>
+        <v>0.0399</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.04925</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.08554492576183587</v>
+        <v>-0.4052</v>
       </c>
       <c r="E26" t="n">
-        <v>-16.9623</v>
+        <v>0.0399</v>
       </c>
       <c r="F26" t="n">
-        <v>-16.96230351629054</v>
+        <v>0.0399</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-16.96230351629054</v>
+        <v>0.0399</v>
       </c>
       <c r="I26" t="n">
-        <v>-11.47597982704523</v>
+        <v>0.0399</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-11.476</v>
+        <v>0.0399</v>
       </c>
       <c r="N26" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>kaze</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1.3157</v>
+        <v>-0.0507</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.13157</v>
+        <v>-0</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2451813274645236</v>
+        <v>-0.4418</v>
       </c>
       <c r="E27" t="n">
-        <v>-23.9084</v>
+        <v>-0.0507</v>
       </c>
       <c r="F27" t="n">
-        <v>-23.90836983178763</v>
+        <v>-0.0507</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-23.90836983178763</v>
+        <v>-0.0507</v>
       </c>
       <c r="I27" t="n">
-        <v>-16.17539561319757</v>
+        <v>-0.0507</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1691,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-16.1754</v>
+        <v>-0.0507</v>
       </c>
       <c r="N27" t="n">
         <v>57</v>
@@ -1700,32 +1688,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cJ dA K1nG</t>
+          <t>MarKE</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.4215</v>
+        <v>-0.1342</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.14215</v>
+        <v>-0</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.2673293530236624</v>
+        <v>-0.4756</v>
       </c>
       <c r="E28" t="n">
-        <v>-24.8721</v>
+        <v>-0.1342</v>
       </c>
       <c r="F28" t="n">
-        <v>-24.8720701698698</v>
+        <v>-0.1342</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-24.8720701698698</v>
+        <v>-0.1342</v>
       </c>
       <c r="I28" t="n">
-        <v>-24.50304835726046</v>
+        <v>-0.1342</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1737,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-24.503</v>
+        <v>-0.1342</v>
       </c>
       <c r="N28" t="n">
         <v>83</v>
@@ -1746,78 +1734,78 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.6069</v>
+        <v>-0.463</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.16069</v>
+        <v>-0</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3071178971557345</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>-26.6033</v>
+        <v>-0.463</v>
       </c>
       <c r="F29" t="n">
-        <v>-26.60334112806381</v>
+        <v>-0.3858</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-0.0772</v>
       </c>
       <c r="H29" t="n">
-        <v>-26.60334112806381</v>
+        <v>-0.3858</v>
       </c>
       <c r="I29" t="n">
-        <v>-26.84016612326912</v>
+        <v>-0.3127</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-0.0772</v>
       </c>
       <c r="K29" t="n">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="M29" t="n">
-        <v>-26.8402</v>
+        <v>-0.3899</v>
       </c>
       <c r="N29" t="n">
-        <v>85</v>
+        <v>252</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Moseyuh</t>
+          <t>kaze</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.7476</v>
+        <v>-0.5311</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.17476</v>
+        <v>-0</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.3381305892954704</v>
+        <v>-0.6359</v>
       </c>
       <c r="E30" t="n">
-        <v>-27.9528</v>
+        <v>-0.5311</v>
       </c>
       <c r="F30" t="n">
-        <v>-27.95275901726115</v>
+        <v>-0.5311</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-27.95275901726115</v>
+        <v>-0.5311</v>
       </c>
       <c r="I30" t="n">
-        <v>-18.91165891969004</v>
+        <v>-0.5311</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1829,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-18.9117</v>
+        <v>-0.5311</v>
       </c>
       <c r="N30" t="n">
         <v>57</v>
@@ -1838,231 +1826,231 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>Moseyuh</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.8761</v>
+        <v>-0.6169</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.18761</v>
+        <v>-0</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.3670812209840691</v>
+        <v>-0.6706</v>
       </c>
       <c r="E31" t="n">
-        <v>-29.2125</v>
+        <v>-0.6169</v>
       </c>
       <c r="F31" t="n">
-        <v>9.709938692134932</v>
+        <v>-0.6169</v>
       </c>
       <c r="G31" t="n">
-        <v>-38.92239164786923</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>9.709938692134932</v>
+        <v>-0.6169</v>
       </c>
       <c r="I31" t="n">
-        <v>11.64040128077897</v>
+        <v>-0.6169</v>
       </c>
       <c r="J31" t="n">
-        <v>-38.92239164786923</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="L31" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-27.282</v>
+        <v>-0.6169</v>
       </c>
       <c r="N31" t="n">
-        <v>252</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Keoz</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-2.2365</v>
+        <v>-0.6185</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.22365</v>
+        <v>-0</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.4517123342053747</v>
+        <v>-0.6712</v>
       </c>
       <c r="E32" t="n">
-        <v>-32.8949</v>
+        <v>-0.6185</v>
       </c>
       <c r="F32" t="n">
-        <v>-32.8949045677693</v>
+        <v>-0.6752</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.0567</v>
       </c>
       <c r="H32" t="n">
-        <v>-32.8949045677693</v>
+        <v>-0.6752</v>
       </c>
       <c r="I32" t="n">
-        <v>-49.97682830474149</v>
+        <v>-0.5473</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>0.0567</v>
       </c>
       <c r="K32" t="n">
-        <v>128</v>
+        <v>69</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="M32" t="n">
-        <v>-49.9768</v>
+        <v>-0.4906</v>
       </c>
       <c r="N32" t="n">
-        <v>128</v>
+        <v>162</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>isak</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-2.3107</v>
+        <v>-0.6731</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.23107</v>
+        <v>-0</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.4697820933470577</v>
+        <v>-0.6933</v>
       </c>
       <c r="E33" t="n">
-        <v>-33.6812</v>
+        <v>-0.6731</v>
       </c>
       <c r="F33" t="n">
-        <v>-33.68115221532622</v>
+        <v>0.3269</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H33" t="n">
-        <v>-33.68115221532622</v>
+        <v>0.3269</v>
       </c>
       <c r="I33" t="n">
-        <v>-51.17136479005053</v>
+        <v>0.265</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K33" t="n">
-        <v>128</v>
+        <v>69</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="M33" t="n">
-        <v>-51.1714</v>
+        <v>-0.735</v>
       </c>
       <c r="N33" t="n">
-        <v>128</v>
+        <v>162</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>cJ dA K1nG</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-2.5092</v>
+        <v>-0.8746</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.25092</v>
+        <v>-0</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.519235968610389</v>
+        <v>-0.7747000000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>-35.833</v>
+        <v>-0.8746</v>
       </c>
       <c r="F34" t="n">
-        <v>-8.336099137231983</v>
+        <v>-0.8746</v>
       </c>
       <c r="G34" t="n">
-        <v>-27.49687993884486</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-8.336099137231983</v>
+        <v>-0.8746</v>
       </c>
       <c r="I34" t="n">
-        <v>-11.08181725068228</v>
+        <v>-0.8746</v>
       </c>
       <c r="J34" t="n">
-        <v>-27.49687993884486</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="L34" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-38.5787</v>
+        <v>-0.8746</v>
       </c>
       <c r="N34" t="n">
-        <v>175</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>nosraC</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-2.565</v>
+        <v>-0.8925</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2565</v>
+        <v>-0</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.5334096937269206</v>
+        <v>-0.7819</v>
       </c>
       <c r="E35" t="n">
-        <v>-36.4497</v>
+        <v>-0.8925</v>
       </c>
       <c r="F35" t="n">
-        <v>-36.44970329152499</v>
+        <v>-0.8925</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-36.44970329152499</v>
+        <v>-0.8925</v>
       </c>
       <c r="I35" t="n">
-        <v>-35.90890650678426</v>
+        <v>-0.8925</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-35.9089</v>
+        <v>-0.8925</v>
       </c>
       <c r="N35" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36">
@@ -2072,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-2.7321</v>
+        <v>-1.2588</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.27321</v>
+        <v>-0</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.5767331937604573</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>-38.3348</v>
+        <v>-1.2588</v>
       </c>
       <c r="F36" t="n">
-        <v>-38.33478652468909</v>
+        <v>-1.2588</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-38.33478652468909</v>
+        <v>-1.2588</v>
       </c>
       <c r="I36" t="n">
-        <v>-25.93570126892912</v>
+        <v>-1.2588</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2105,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-25.9357</v>
+        <v>-1.2588</v>
       </c>
       <c r="N36" t="n">
         <v>57</v>
@@ -2114,47 +2102,47 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>Woro2k</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-3.2939</v>
+        <v>-1.3695</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.32939</v>
+        <v>-0</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.7314795369424936</v>
+        <v>-0.9746</v>
       </c>
       <c r="E37" t="n">
-        <v>-45.0681</v>
+        <v>-1.3695</v>
       </c>
       <c r="F37" t="n">
-        <v>11.37789229814643</v>
+        <v>-0.3469</v>
       </c>
       <c r="G37" t="n">
-        <v>-56.44596991658609</v>
+        <v>-1.0226</v>
       </c>
       <c r="H37" t="n">
-        <v>11.37789229814643</v>
+        <v>-0.3469</v>
       </c>
       <c r="I37" t="n">
-        <v>9.318392505306868</v>
+        <v>-0.2812</v>
       </c>
       <c r="J37" t="n">
-        <v>-56.44596991658609</v>
+        <v>-1.0226</v>
       </c>
       <c r="K37" t="n">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="L37" t="n">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="M37" t="n">
-        <v>-47.1276</v>
+        <v>-1.3038</v>
       </c>
       <c r="N37" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="38">
@@ -2164,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-3.8803</v>
+        <v>-1.6029</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.38803</v>
+        <v>-0</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9092661794114102</v>
+        <v>-1.0689</v>
       </c>
       <c r="E38" t="n">
-        <v>-52.8039</v>
+        <v>-1.6029</v>
       </c>
       <c r="F38" t="n">
-        <v>-52.80389348140692</v>
+        <v>-1.6029</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-52.80389348140692</v>
+        <v>-1.6029</v>
       </c>
       <c r="I38" t="n">
-        <v>-35.72488935834059</v>
+        <v>-1.6029</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2197,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-35.7249</v>
+        <v>-1.6029</v>
       </c>
       <c r="N38" t="n">
         <v>57</v>
@@ -2206,139 +2194,139 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Calyx</t>
+          <t>nosraC</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-3.906</v>
+        <v>-1.9705</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3906000000000001</v>
+        <v>-0</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9174492585953986</v>
+        <v>-1.2174</v>
       </c>
       <c r="E39" t="n">
-        <v>-53.16</v>
+        <v>-1.9705</v>
       </c>
       <c r="F39" t="n">
-        <v>5.380362388480275</v>
+        <v>-1.9705</v>
       </c>
       <c r="G39" t="n">
-        <v>-58.54031633022511</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>5.380362388480275</v>
+        <v>-1.9705</v>
       </c>
       <c r="I39" t="n">
-        <v>6.450048679365079</v>
+        <v>-1.9705</v>
       </c>
       <c r="J39" t="n">
-        <v>-58.54031633022511</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="L39" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-52.0903</v>
+        <v>-1.9705</v>
       </c>
       <c r="N39" t="n">
-        <v>252</v>
+        <v>83</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>Keoz</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-3.9989</v>
+        <v>-2.0267</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.39989</v>
+        <v>-0</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.94738259718189</v>
+        <v>-1.2401</v>
       </c>
       <c r="E40" t="n">
-        <v>-54.4624</v>
+        <v>-2.0267</v>
       </c>
       <c r="F40" t="n">
-        <v>-5.019415643954569</v>
+        <v>-2.0267</v>
       </c>
       <c r="G40" t="n">
-        <v>-49.44299157691913</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-5.019415643954569</v>
+        <v>-2.0267</v>
       </c>
       <c r="I40" t="n">
-        <v>-6.01734100936987</v>
+        <v>-2.0267</v>
       </c>
       <c r="J40" t="n">
-        <v>-49.44299157691913</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="L40" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-55.4603</v>
+        <v>-2.0267</v>
       </c>
       <c r="N40" t="n">
-        <v>252</v>
+        <v>128</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Woro2k</t>
+          <t>isak</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-4.0552</v>
+        <v>-2.0705</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.40552</v>
+        <v>-0</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.965722082737373</v>
+        <v>-1.2578</v>
       </c>
       <c r="E41" t="n">
-        <v>-55.2604</v>
+        <v>-2.0705</v>
       </c>
       <c r="F41" t="n">
-        <v>-15.41612037179766</v>
+        <v>-2.0705</v>
       </c>
       <c r="G41" t="n">
-        <v>-39.84427077693815</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-15.41612037179766</v>
+        <v>-2.0705</v>
       </c>
       <c r="I41" t="n">
-        <v>-7.136245632048767</v>
+        <v>-2.0705</v>
       </c>
       <c r="J41" t="n">
-        <v>-39.84427077693815</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="L41" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-46.9805</v>
+        <v>-2.0705</v>
       </c>
       <c r="N41" t="n">
-        <v>160</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -2356,52 +2344,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>opponent</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>opponent_rank</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>match_stage</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>round_differential</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>total_rounds</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>perf_score_raw</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>perf_score_weighted</t>
         </is>
@@ -2441,10 +2429,10 @@
         <v>1.34</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6486345839902661</v>
+        <v>0.9208</v>
       </c>
       <c r="J2" t="n">
-        <v>14.91859543177612</v>
+        <v>21.1784</v>
       </c>
     </row>
     <row r="3">
@@ -2481,10 +2469,10 @@
         <v>1.34</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6486345839902661</v>
+        <v>0.9208</v>
       </c>
       <c r="J3" t="n">
-        <v>14.91859543177612</v>
+        <v>21.1784</v>
       </c>
     </row>
     <row r="4">
@@ -2521,10 +2509,10 @@
         <v>1.03</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.14771727026036</v>
+        <v>0.0454</v>
       </c>
       <c r="J4" t="n">
-        <v>-3.397497215988279</v>
+        <v>1.0442</v>
       </c>
     </row>
     <row r="5">
@@ -2561,10 +2549,10 @@
         <v>0.98</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3584079010510368</v>
+        <v>-0.1971</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.243381724173846</v>
+        <v>-4.5333</v>
       </c>
     </row>
     <row r="6">
@@ -2601,10 +2589,10 @@
         <v>0.97</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3942116704581327</v>
+        <v>-0.2351</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.066868420537052</v>
+        <v>-5.4073</v>
       </c>
     </row>
     <row r="7">
@@ -2641,10 +2629,10 @@
         <v>1.29</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4774421407065379</v>
+        <v>0.4952</v>
       </c>
       <c r="J7" t="n">
-        <v>10.98116923625037</v>
+        <v>11.3896</v>
       </c>
     </row>
     <row r="8">
@@ -2681,10 +2669,10 @@
         <v>1.18</v>
       </c>
       <c r="I8" t="n">
-        <v>0.230860723003555</v>
+        <v>0.3417</v>
       </c>
       <c r="J8" t="n">
-        <v>5.309796629081765</v>
+        <v>7.8591</v>
       </c>
     </row>
     <row r="9">
@@ -2721,10 +2709,10 @@
         <v>1.03</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3659119155105142</v>
+        <v>0.0653</v>
       </c>
       <c r="J9" t="n">
-        <v>-8.415974056741828</v>
+        <v>1.5019</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2749,10 @@
         <v>0.84</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9323100311169945</v>
+        <v>-0.3332</v>
       </c>
       <c r="J10" t="n">
-        <v>-21.44313071569087</v>
+        <v>-7.6636</v>
       </c>
     </row>
     <row r="11">
@@ -2801,10 +2789,10 @@
         <v>0.84</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9323100311169945</v>
+        <v>-0.3332</v>
       </c>
       <c r="J11" t="n">
-        <v>-21.44313071569087</v>
+        <v>-7.6636</v>
       </c>
     </row>
     <row r="12">
@@ -2841,10 +2829,10 @@
         <v>1.81</v>
       </c>
       <c r="I12" t="n">
-        <v>1.164623988824866</v>
+        <v>1.8335</v>
       </c>
       <c r="J12" t="n">
-        <v>40.76183960887032</v>
+        <v>64.1725</v>
       </c>
     </row>
     <row r="13">
@@ -2881,10 +2869,10 @@
         <v>1.08</v>
       </c>
       <c r="I13" t="n">
-        <v>0.03140594008409851</v>
+        <v>0.2125</v>
       </c>
       <c r="J13" t="n">
-        <v>1.099207902943448</v>
+        <v>7.4375</v>
       </c>
     </row>
     <row r="14">
@@ -2921,10 +2909,10 @@
         <v>0.95</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5025847706483964</v>
+        <v>-0.3047</v>
       </c>
       <c r="J14" t="n">
-        <v>-17.59046697269387</v>
+        <v>-10.6645</v>
       </c>
     </row>
     <row r="15">
@@ -2961,10 +2949,10 @@
         <v>0.95</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5025847706483964</v>
+        <v>-0.3047</v>
       </c>
       <c r="J15" t="n">
-        <v>-17.59046697269387</v>
+        <v>-10.6645</v>
       </c>
     </row>
     <row r="16">
@@ -3001,10 +2989,10 @@
         <v>0.88</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7078102443092635</v>
+        <v>-0.5099</v>
       </c>
       <c r="J16" t="n">
-        <v>-24.77335855082422</v>
+        <v>-17.8465</v>
       </c>
     </row>
     <row r="17">
@@ -3041,10 +3029,10 @@
         <v>1.5</v>
       </c>
       <c r="I17" t="n">
-        <v>0.804701471109679</v>
+        <v>0.7442</v>
       </c>
       <c r="J17" t="n">
-        <v>28.16455148883877</v>
+        <v>26.047</v>
       </c>
     </row>
     <row r="18">
@@ -3081,10 +3069,10 @@
         <v>1.45</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7299362742901871</v>
+        <v>0.6861</v>
       </c>
       <c r="J18" t="n">
-        <v>25.54776960015655</v>
+        <v>24.0135</v>
       </c>
     </row>
     <row r="19">
@@ -3121,10 +3109,10 @@
         <v>0.87</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8991650000766909</v>
+        <v>-0.2929</v>
       </c>
       <c r="J19" t="n">
-        <v>-31.47077500268418</v>
+        <v>-10.2515</v>
       </c>
     </row>
     <row r="20">
@@ -3161,10 +3149,10 @@
         <v>0.8</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.052180060124867</v>
+        <v>-0.3964</v>
       </c>
       <c r="J20" t="n">
-        <v>-36.82630210437033</v>
+        <v>-13.874</v>
       </c>
     </row>
     <row r="21">
@@ -3201,10 +3189,10 @@
         <v>0.68</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.279553167010376</v>
+        <v>-0.5558</v>
       </c>
       <c r="J21" t="n">
-        <v>-44.78436084536317</v>
+        <v>-19.453</v>
       </c>
     </row>
     <row r="22">
@@ -3241,10 +3229,10 @@
         <v>1.36</v>
       </c>
       <c r="I22" t="n">
-        <v>0.489804179173389</v>
+        <v>0.981</v>
       </c>
       <c r="J22" t="n">
-        <v>14.20432119602828</v>
+        <v>28.449</v>
       </c>
     </row>
     <row r="23">
@@ -3281,10 +3269,10 @@
         <v>1.12</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2015878017776984</v>
+        <v>0.3805</v>
       </c>
       <c r="J23" t="n">
-        <v>5.846046251553255</v>
+        <v>11.0345</v>
       </c>
     </row>
     <row r="24">
@@ -3321,10 +3309,10 @@
         <v>1.09</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1288747586305151</v>
+        <v>0.2699</v>
       </c>
       <c r="J24" t="n">
-        <v>3.737368000284938</v>
+        <v>7.8271</v>
       </c>
     </row>
     <row r="25">
@@ -3361,10 +3349,10 @@
         <v>1.06</v>
       </c>
       <c r="I25" t="n">
-        <v>0.07405393852355983</v>
+        <v>0.1684</v>
       </c>
       <c r="J25" t="n">
-        <v>2.147564217183235</v>
+        <v>4.8836</v>
       </c>
     </row>
     <row r="26">
@@ -3401,10 +3389,10 @@
         <v>0.88</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4265898303429163</v>
+        <v>-0.4987</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.37110507994457</v>
+        <v>-14.4623</v>
       </c>
     </row>
     <row r="27">
@@ -3441,10 +3429,10 @@
         <v>1.14</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1411231151770226</v>
+        <v>0.2985</v>
       </c>
       <c r="J27" t="n">
-        <v>4.092570340133655</v>
+        <v>8.656499999999999</v>
       </c>
     </row>
     <row r="28">
@@ -3481,10 +3469,10 @@
         <v>1.09</v>
       </c>
       <c r="I28" t="n">
-        <v>0.03462824725136032</v>
+        <v>0.216</v>
       </c>
       <c r="J28" t="n">
-        <v>1.004219170289449</v>
+        <v>6.264</v>
       </c>
     </row>
     <row r="29">
@@ -3521,10 +3509,10 @@
         <v>1.02</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1555839769057143</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>-4.511935330265715</v>
+        <v>2.1866</v>
       </c>
     </row>
     <row r="30">
@@ -3561,10 +3549,10 @@
         <v>0.87</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6057140877860591</v>
+        <v>-0.2734</v>
       </c>
       <c r="J30" t="n">
-        <v>-17.56570854579571</v>
+        <v>-7.9286</v>
       </c>
     </row>
     <row r="31">
@@ -3601,10 +3589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7250914949957508</v>
+        <v>-0.3657</v>
       </c>
       <c r="J31" t="n">
-        <v>-21.02765335487677</v>
+        <v>-10.6053</v>
       </c>
     </row>
     <row r="32">
@@ -3641,10 +3629,10 @@
         <v>1.29</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2665849066471767</v>
+        <v>0.4945</v>
       </c>
       <c r="J32" t="n">
-        <v>6.131452852885063</v>
+        <v>11.3735</v>
       </c>
     </row>
     <row r="33">
@@ -3681,10 +3669,10 @@
         <v>1.08</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.09944443077566496</v>
+        <v>0.1765</v>
       </c>
       <c r="J33" t="n">
-        <v>-2.287221907840294</v>
+        <v>4.0595</v>
       </c>
     </row>
     <row r="34">
@@ -3721,10 +3709,10 @@
         <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2617283991537283</v>
+        <v>0.092</v>
       </c>
       <c r="J34" t="n">
-        <v>-6.019753180535751</v>
+        <v>2.116</v>
       </c>
     </row>
     <row r="35">
@@ -3761,10 +3749,10 @@
         <v>1.03</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3213133771346389</v>
+        <v>0.0639</v>
       </c>
       <c r="J35" t="n">
-        <v>-7.390207674096695</v>
+        <v>1.4697</v>
       </c>
     </row>
     <row r="36">
@@ -3801,10 +3789,10 @@
         <v>0.75</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.001570905285826</v>
+        <v>-0.461</v>
       </c>
       <c r="J36" t="n">
-        <v>-23.036130821574</v>
+        <v>-10.603</v>
       </c>
     </row>
     <row r="37">
@@ -3841,10 +3829,10 @@
         <v>1.83</v>
       </c>
       <c r="I37" t="n">
-        <v>0.897500391323656</v>
+        <v>1.0783</v>
       </c>
       <c r="J37" t="n">
-        <v>20.64250900044409</v>
+        <v>24.8009</v>
       </c>
     </row>
     <row r="38">
@@ -3881,10 +3869,10 @@
         <v>1.39</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5472197192406516</v>
+        <v>0.5954</v>
       </c>
       <c r="J38" t="n">
-        <v>12.58605354253499</v>
+        <v>13.6942</v>
       </c>
     </row>
     <row r="39">
@@ -3921,10 +3909,10 @@
         <v>1.11</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1257074993137493</v>
+        <v>0.1836</v>
       </c>
       <c r="J39" t="n">
-        <v>2.891272484216233</v>
+        <v>4.2228</v>
       </c>
     </row>
     <row r="40">
@@ -3961,10 +3949,10 @@
         <v>0.72</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.7186152560127906</v>
+        <v>-0.5137</v>
       </c>
       <c r="J40" t="n">
-        <v>-16.52815088829418</v>
+        <v>-11.8151</v>
       </c>
     </row>
     <row r="41">
@@ -4001,10 +3989,10 @@
         <v>0.55</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.9470869460750432</v>
+        <v>-0.719</v>
       </c>
       <c r="J41" t="n">
-        <v>-21.78299975972599</v>
+        <v>-16.537</v>
       </c>
     </row>
     <row r="42">
@@ -4041,10 +4029,10 @@
         <v>1.42</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5450122492344829</v>
+        <v>1.1295</v>
       </c>
       <c r="J42" t="n">
-        <v>22.3455022186138</v>
+        <v>46.3095</v>
       </c>
     </row>
     <row r="43">
@@ -4081,10 +4069,10 @@
         <v>1.3</v>
       </c>
       <c r="I43" t="n">
-        <v>0.435700073996545</v>
+        <v>0.8685</v>
       </c>
       <c r="J43" t="n">
-        <v>17.86370303385835</v>
+        <v>35.6085</v>
       </c>
     </row>
     <row r="44">
@@ -4121,10 +4109,10 @@
         <v>1.06</v>
       </c>
       <c r="I44" t="n">
-        <v>0.08675070585874943</v>
+        <v>0.203</v>
       </c>
       <c r="J44" t="n">
-        <v>3.556778940208726</v>
+        <v>8.323</v>
       </c>
     </row>
     <row r="45">
@@ -4161,10 +4149,10 @@
         <v>0.78</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.6404925798144074</v>
+        <v>-0.7395</v>
       </c>
       <c r="J45" t="n">
-        <v>-26.26019577239071</v>
+        <v>-30.3195</v>
       </c>
     </row>
     <row r="46">
@@ -4201,10 +4189,10 @@
         <v>0.76</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6779343159707456</v>
+        <v>-0.7869</v>
       </c>
       <c r="J46" t="n">
-        <v>-27.79530695480057</v>
+        <v>-32.2629</v>
       </c>
     </row>
     <row r="47">
@@ -4241,10 +4229,10 @@
         <v>1.34</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3827247296035575</v>
+        <v>0.5597</v>
       </c>
       <c r="J47" t="n">
-        <v>15.69171391374586</v>
+        <v>22.9477</v>
       </c>
     </row>
     <row r="48">
@@ -4281,10 +4269,10 @@
         <v>1.07</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.01132923857808293</v>
+        <v>0.1584</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.4644987817014</v>
+        <v>6.4944</v>
       </c>
     </row>
     <row r="49">
@@ -4321,10 +4309,10 @@
         <v>0.95</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.4607357481320764</v>
+        <v>-0.1485</v>
       </c>
       <c r="J49" t="n">
-        <v>-18.89016567341513</v>
+        <v>-6.0885</v>
       </c>
     </row>
     <row r="50">
@@ -4361,10 +4349,10 @@
         <v>0.93</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.5092038225142447</v>
+        <v>-0.1862</v>
       </c>
       <c r="J50" t="n">
-        <v>-20.87735672308403</v>
+        <v>-7.6342</v>
       </c>
     </row>
     <row r="51">
@@ -4401,10 +4389,10 @@
         <v>0.89</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5982483169807918</v>
+        <v>-0.2551</v>
       </c>
       <c r="J51" t="n">
-        <v>-24.52818099621247</v>
+        <v>-10.4591</v>
       </c>
     </row>
     <row r="52">
@@ -4441,10 +4429,10 @@
         <v>1.49</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7795116780398912</v>
+        <v>1.2355</v>
       </c>
       <c r="J52" t="n">
-        <v>16.36974523883772</v>
+        <v>25.9455</v>
       </c>
     </row>
     <row r="53">
@@ -4481,10 +4469,10 @@
         <v>1.39</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6755604863142105</v>
+        <v>1.0286</v>
       </c>
       <c r="J53" t="n">
-        <v>14.18677021259842</v>
+        <v>21.6006</v>
       </c>
     </row>
     <row r="54">
@@ -4521,10 +4509,10 @@
         <v>1.18</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3862001084599241</v>
+        <v>0.5309</v>
       </c>
       <c r="J54" t="n">
-        <v>8.110202277658406</v>
+        <v>11.1489</v>
       </c>
     </row>
     <row r="55">
@@ -4561,10 +4549,10 @@
         <v>0.87</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.313554241808247</v>
+        <v>-0.5366</v>
       </c>
       <c r="J55" t="n">
-        <v>-6.584639077973188</v>
+        <v>-11.2686</v>
       </c>
     </row>
     <row r="56">
@@ -4601,10 +4589,10 @@
         <v>0.74</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5225533814958948</v>
+        <v>-0.8522999999999999</v>
       </c>
       <c r="J56" t="n">
-        <v>-10.97362101141379</v>
+        <v>-17.8983</v>
       </c>
     </row>
     <row r="57">
@@ -4641,10 +4629,10 @@
         <v>1.42</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5017575454036763</v>
+        <v>0.6774</v>
       </c>
       <c r="J57" t="n">
-        <v>10.5369084534772</v>
+        <v>14.2254</v>
       </c>
     </row>
     <row r="58">
@@ -4681,10 +4669,10 @@
         <v>1.41</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4902507519614202</v>
+        <v>0.6654</v>
       </c>
       <c r="J58" t="n">
-        <v>10.29526579118982</v>
+        <v>13.9734</v>
       </c>
     </row>
     <row r="59">
@@ -4721,10 +4709,10 @@
         <v>0.79</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.7261766507868654</v>
+        <v>-0.3928</v>
       </c>
       <c r="J59" t="n">
-        <v>-15.24970966652417</v>
+        <v>-8.248799999999999</v>
       </c>
     </row>
     <row r="60">
@@ -4761,10 +4749,10 @@
         <v>0.78</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.7412371284867608</v>
+        <v>-0.4071</v>
       </c>
       <c r="J60" t="n">
-        <v>-15.56597969822198</v>
+        <v>-8.549099999999999</v>
       </c>
     </row>
     <row r="61">
@@ -4801,10 +4789,10 @@
         <v>0.49</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.095688542104238</v>
+        <v>-0.7727000000000001</v>
       </c>
       <c r="J61" t="n">
-        <v>-23.00945938418901</v>
+        <v>-16.2267</v>
       </c>
     </row>
     <row r="62">
@@ -4841,10 +4829,10 @@
         <v>1.38</v>
       </c>
       <c r="I62" t="n">
-        <v>0.285190145286773</v>
+        <v>0.6652</v>
       </c>
       <c r="J62" t="n">
-        <v>5.418612760448687</v>
+        <v>12.6388</v>
       </c>
     </row>
     <row r="63">
@@ -4881,10 +4869,10 @@
         <v>0.95</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.4375334759771786</v>
+        <v>-0.063</v>
       </c>
       <c r="J63" t="n">
-        <v>-8.313136043566393</v>
+        <v>-1.197</v>
       </c>
     </row>
     <row r="64">
@@ -4921,10 +4909,10 @@
         <v>0.91</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.5236344685087816</v>
+        <v>-0.1413</v>
       </c>
       <c r="J64" t="n">
-        <v>-9.94905490166685</v>
+        <v>-2.6847</v>
       </c>
     </row>
     <row r="65">
@@ -4961,10 +4949,10 @@
         <v>0.65</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.046894712197121</v>
+        <v>-0.5608</v>
       </c>
       <c r="J65" t="n">
-        <v>-19.89099953174529</v>
+        <v>-10.6552</v>
       </c>
     </row>
     <row r="66">
@@ -5001,10 +4989,10 @@
         <v>0.5</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.232484458125335</v>
+        <v>-0.7478</v>
       </c>
       <c r="J66" t="n">
-        <v>-23.41720470438136</v>
+        <v>-14.2082</v>
       </c>
     </row>
     <row r="67">
@@ -5041,10 +5029,10 @@
         <v>1.67</v>
       </c>
       <c r="I67" t="n">
-        <v>1.018364652158407</v>
+        <v>0.8568</v>
       </c>
       <c r="J67" t="n">
-        <v>19.34892839100972</v>
+        <v>16.2792</v>
       </c>
     </row>
     <row r="68">
@@ -5081,10 +5069,10 @@
         <v>1.65</v>
       </c>
       <c r="I68" t="n">
-        <v>0.998220275310008</v>
+        <v>0.8355</v>
       </c>
       <c r="J68" t="n">
-        <v>18.96618523089015</v>
+        <v>15.8745</v>
       </c>
     </row>
     <row r="69">
@@ -5121,10 +5109,10 @@
         <v>1.16</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2285015196094847</v>
+        <v>0.1983</v>
       </c>
       <c r="J69" t="n">
-        <v>4.34152887258021</v>
+        <v>3.7677</v>
       </c>
     </row>
     <row r="70">
@@ -5161,10 +5149,10 @@
         <v>1.12</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1703608466268778</v>
+        <v>0.1384</v>
       </c>
       <c r="J70" t="n">
-        <v>3.236856085910677</v>
+        <v>2.6296</v>
       </c>
     </row>
     <row r="71">
@@ -5201,10 +5189,10 @@
         <v>1.02</v>
       </c>
       <c r="I71" t="n">
-        <v>0.0278815513977623</v>
+        <v>-0.0366</v>
       </c>
       <c r="J71" t="n">
-        <v>0.5297494765574837</v>
+        <v>-0.6954</v>
       </c>
     </row>
     <row r="72">
@@ -5241,10 +5229,10 @@
         <v>1.76</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9449790334115038</v>
+        <v>1.7163</v>
       </c>
       <c r="J72" t="n">
-        <v>21.73451776846459</v>
+        <v>39.4749</v>
       </c>
     </row>
     <row r="73">
@@ -5281,10 +5269,10 @@
         <v>1.19</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3223142549622704</v>
+        <v>0.5341</v>
       </c>
       <c r="J73" t="n">
-        <v>7.413227864132219</v>
+        <v>12.2843</v>
       </c>
     </row>
     <row r="74">
@@ -5321,10 +5309,10 @@
         <v>1.02</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.02210275691143493</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="J74" t="n">
-        <v>-0.5083634089630035</v>
+        <v>-0.2024</v>
       </c>
     </row>
     <row r="75">
@@ -5361,10 +5349,10 @@
         <v>1.01</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.04399955287762853</v>
+        <v>-0.0512</v>
       </c>
       <c r="J75" t="n">
-        <v>-1.011989716185456</v>
+        <v>-1.1776</v>
       </c>
     </row>
     <row r="76">
@@ -5401,10 +5389,10 @@
         <v>0.85</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4206553496578981</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.675073042131656</v>
+        <v>-13.7609</v>
       </c>
     </row>
     <row r="77">
@@ -5441,10 +5429,10 @@
         <v>1.21</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2726179295902611</v>
+        <v>0.4169</v>
       </c>
       <c r="J77" t="n">
-        <v>6.270212380576005</v>
+        <v>9.588699999999999</v>
       </c>
     </row>
     <row r="78">
@@ -5481,10 +5469,10 @@
         <v>1.06</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.04436273450072586</v>
+        <v>0.1774</v>
       </c>
       <c r="J78" t="n">
-        <v>-1.020342893516695</v>
+        <v>4.0802</v>
       </c>
     </row>
     <row r="79">
@@ -5521,10 +5509,10 @@
         <v>0.96</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2676720177776538</v>
+        <v>-0.0767</v>
       </c>
       <c r="J79" t="n">
-        <v>-6.156456408886037</v>
+        <v>-1.7641</v>
       </c>
     </row>
     <row r="80">
@@ -5561,10 +5549,10 @@
         <v>0.85</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.5417673790078422</v>
+        <v>-0.2929</v>
       </c>
       <c r="J80" t="n">
-        <v>-12.46064971718037</v>
+        <v>-6.7367</v>
       </c>
     </row>
     <row r="81">
@@ -5601,10 +5589,10 @@
         <v>0.65</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.8373649504835112</v>
+        <v>-0.5748</v>
       </c>
       <c r="J81" t="n">
-        <v>-19.25939386112076</v>
+        <v>-13.2204</v>
       </c>
     </row>
     <row r="82">
@@ -5641,10 +5629,10 @@
         <v>0.82</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.4337428554933438</v>
+        <v>-0.236</v>
       </c>
       <c r="J82" t="n">
-        <v>-6.939885687893502</v>
+        <v>-3.776</v>
       </c>
     </row>
     <row r="83">
@@ -5681,10 +5669,10 @@
         <v>0.79</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.4734048346816899</v>
+        <v>-0.2866</v>
       </c>
       <c r="J83" t="n">
-        <v>-7.574477354907039</v>
+        <v>-4.5856</v>
       </c>
     </row>
     <row r="84">
@@ -5721,10 +5709,10 @@
         <v>0.75</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.5520198051321422</v>
+        <v>-0.3667</v>
       </c>
       <c r="J84" t="n">
-        <v>-8.832316882114275</v>
+        <v>-5.8672</v>
       </c>
     </row>
     <row r="85">
@@ -5761,10 +5749,10 @@
         <v>0.73</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.586252718180449</v>
+        <v>-0.4031</v>
       </c>
       <c r="J85" t="n">
-        <v>-9.380043490887184</v>
+        <v>-6.4496</v>
       </c>
     </row>
     <row r="86">
@@ -5801,10 +5789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.6392760191951994</v>
+        <v>-0.467</v>
       </c>
       <c r="J86" t="n">
-        <v>-10.22841630712319</v>
+        <v>-7.472</v>
       </c>
     </row>
     <row r="87">
@@ -5841,10 +5829,10 @@
         <v>1.56</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3891996577913715</v>
+        <v>1.2319</v>
       </c>
       <c r="J87" t="n">
-        <v>6.227194524661944</v>
+        <v>19.7104</v>
       </c>
     </row>
     <row r="88">
@@ -5881,10 +5869,10 @@
         <v>1.54</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3779554856815197</v>
+        <v>1.1915</v>
       </c>
       <c r="J88" t="n">
-        <v>6.047287770904315</v>
+        <v>19.064</v>
       </c>
     </row>
     <row r="89">
@@ -5921,10 +5909,10 @@
         <v>1.53</v>
       </c>
       <c r="I89" t="n">
-        <v>0.3721193405900391</v>
+        <v>1.171</v>
       </c>
       <c r="J89" t="n">
-        <v>5.953909449440626</v>
+        <v>18.736</v>
       </c>
     </row>
     <row r="90">
@@ -5961,10 +5949,10 @@
         <v>1.35</v>
       </c>
       <c r="I90" t="n">
-        <v>0.2274827152211487</v>
+        <v>0.7499</v>
       </c>
       <c r="J90" t="n">
-        <v>3.639723443538379</v>
+        <v>11.9984</v>
       </c>
     </row>
     <row r="91">
@@ -6001,10 +5989,10 @@
         <v>1.17</v>
       </c>
       <c r="I91" t="n">
-        <v>0.1267916771707024</v>
+        <v>0.3344</v>
       </c>
       <c r="J91" t="n">
-        <v>2.028666834731238</v>
+        <v>5.3504</v>
       </c>
     </row>
     <row r="92">
@@ -6041,10 +6029,10 @@
         <v>1.04</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.03356390688933167</v>
+        <v>0.184</v>
       </c>
       <c r="J92" t="n">
-        <v>-0.7384059515652968</v>
+        <v>4.048</v>
       </c>
     </row>
     <row r="93">
@@ -6081,10 +6069,10 @@
         <v>0.9</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1998282509390742</v>
+        <v>-0.1364</v>
       </c>
       <c r="J93" t="n">
-        <v>-4.396221520659632</v>
+        <v>-3.0008</v>
       </c>
     </row>
     <row r="94">
@@ -6121,10 +6109,10 @@
         <v>0.8</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.3750050819563415</v>
+        <v>-0.3275</v>
       </c>
       <c r="J94" t="n">
-        <v>-8.250111803039513</v>
+        <v>-7.205</v>
       </c>
     </row>
     <row r="95">
@@ -6161,10 +6149,10 @@
         <v>0.73</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.4651408430140602</v>
+        <v>-0.4372</v>
       </c>
       <c r="J95" t="n">
-        <v>-10.23309854630932</v>
+        <v>-9.618399999999999</v>
       </c>
     </row>
     <row r="96">
@@ -6201,10 +6189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5085918378603698</v>
+        <v>-0.4946</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.18902043292814</v>
+        <v>-10.8812</v>
       </c>
     </row>
     <row r="97">
@@ -6241,10 +6229,10 @@
         <v>1.57</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3734563656290932</v>
+        <v>1.3433</v>
       </c>
       <c r="J97" t="n">
-        <v>8.216040043840049</v>
+        <v>29.5526</v>
       </c>
     </row>
     <row r="98">
@@ -6281,10 +6269,10 @@
         <v>1.22</v>
       </c>
       <c r="I98" t="n">
-        <v>0.1540280486438124</v>
+        <v>0.5486</v>
       </c>
       <c r="J98" t="n">
-        <v>3.388617070163873</v>
+        <v>12.0692</v>
       </c>
     </row>
     <row r="99">
@@ -6321,10 +6309,10 @@
         <v>1.21</v>
       </c>
       <c r="I99" t="n">
-        <v>0.1446069764558882</v>
+        <v>0.5205</v>
       </c>
       <c r="J99" t="n">
-        <v>3.181353482029541</v>
+        <v>11.451</v>
       </c>
     </row>
     <row r="100">
@@ -6361,10 +6349,10 @@
         <v>1.13</v>
       </c>
       <c r="I100" t="n">
-        <v>0.0845846605206252</v>
+        <v>0.3043</v>
       </c>
       <c r="J100" t="n">
-        <v>1.860862531453754</v>
+        <v>6.6946</v>
       </c>
     </row>
     <row r="101">
@@ -6401,10 +6389,10 @@
         <v>1.04</v>
       </c>
       <c r="I101" t="n">
-        <v>0.02705696376233447</v>
+        <v>0.0368</v>
       </c>
       <c r="J101" t="n">
-        <v>0.5952532027713584</v>
+        <v>0.8096</v>
       </c>
     </row>
     <row r="102">
@@ -6441,10 +6429,10 @@
         <v>1.39</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4179990731410065</v>
+        <v>0.971</v>
       </c>
       <c r="J102" t="n">
-        <v>8.35998146282013</v>
+        <v>19.42</v>
       </c>
     </row>
     <row r="103">
@@ -6481,10 +6469,10 @@
         <v>1.31</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3488824682101073</v>
+        <v>0.7892</v>
       </c>
       <c r="J103" t="n">
-        <v>6.977649364202146</v>
+        <v>15.784</v>
       </c>
     </row>
     <row r="104">
@@ -6521,10 +6509,10 @@
         <v>1.31</v>
       </c>
       <c r="I104" t="n">
-        <v>0.3488824682101073</v>
+        <v>0.7892</v>
       </c>
       <c r="J104" t="n">
-        <v>6.977649364202146</v>
+        <v>15.784</v>
       </c>
     </row>
     <row r="105">
@@ -6561,10 +6549,10 @@
         <v>1.25</v>
       </c>
       <c r="I105" t="n">
-        <v>0.2789807960778506</v>
+        <v>0.6339</v>
       </c>
       <c r="J105" t="n">
-        <v>5.579615921557012</v>
+        <v>12.678</v>
       </c>
     </row>
     <row r="106">
@@ -6601,10 +6589,10 @@
         <v>0.96</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.01696402733522082</v>
+        <v>-0.3097</v>
       </c>
       <c r="J106" t="n">
-        <v>-0.3392805467044164</v>
+        <v>-6.194</v>
       </c>
     </row>
     <row r="107">
@@ -6641,10 +6629,10 @@
         <v>1.17</v>
       </c>
       <c r="I107" t="n">
-        <v>0.03506932562247388</v>
+        <v>0.3895</v>
       </c>
       <c r="J107" t="n">
-        <v>0.7013865124494777</v>
+        <v>7.79</v>
       </c>
     </row>
     <row r="108">
@@ -6681,10 +6669,10 @@
         <v>0.93</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.2185939222522489</v>
+        <v>-0.0959</v>
       </c>
       <c r="J108" t="n">
-        <v>-4.371878445044979</v>
+        <v>-1.918</v>
       </c>
     </row>
     <row r="109">
@@ -6721,10 +6709,10 @@
         <v>0.83</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.378667113743935</v>
+        <v>-0.2927</v>
       </c>
       <c r="J109" t="n">
-        <v>-7.5733422748787</v>
+        <v>-5.854</v>
       </c>
     </row>
     <row r="110">
@@ -6761,10 +6749,10 @@
         <v>0.76</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4602469285588981</v>
+        <v>-0.4039</v>
       </c>
       <c r="J110" t="n">
-        <v>-9.204938571177962</v>
+        <v>-8.077999999999999</v>
       </c>
     </row>
     <row r="111">
@@ -6801,10 +6789,10 @@
         <v>0.63</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5779308603959163</v>
+        <v>-0.5838</v>
       </c>
       <c r="J111" t="n">
-        <v>-11.55861720791833</v>
+        <v>-11.676</v>
       </c>
     </row>
     <row r="112">
@@ -6841,10 +6829,10 @@
         <v>1.24</v>
       </c>
       <c r="I112" t="n">
-        <v>0.2860552762958054</v>
+        <v>0.6937</v>
       </c>
       <c r="J112" t="n">
-        <v>6.579271354803525</v>
+        <v>15.9551</v>
       </c>
     </row>
     <row r="113">
@@ -6881,10 +6869,10 @@
         <v>1.19</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2375614984814665</v>
+        <v>0.5663</v>
       </c>
       <c r="J113" t="n">
-        <v>5.463914465073729</v>
+        <v>13.0249</v>
       </c>
     </row>
     <row r="114">
@@ -6921,10 +6909,10 @@
         <v>1.17</v>
       </c>
       <c r="I114" t="n">
-        <v>0.2157605794988029</v>
+        <v>0.512</v>
       </c>
       <c r="J114" t="n">
-        <v>4.962493328472466</v>
+        <v>11.776</v>
       </c>
     </row>
     <row r="115">
@@ -6961,10 +6949,10 @@
         <v>1.06</v>
       </c>
       <c r="I115" t="n">
-        <v>0.05836988213952227</v>
+        <v>0.1553</v>
       </c>
       <c r="J115" t="n">
-        <v>1.342507289209012</v>
+        <v>3.5719</v>
       </c>
     </row>
     <row r="116">
@@ -7001,10 +6989,10 @@
         <v>0.95</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.101038314331867</v>
+        <v>-0.2998</v>
       </c>
       <c r="J116" t="n">
-        <v>-2.323881229632941</v>
+        <v>-6.8954</v>
       </c>
     </row>
     <row r="117">
@@ -7041,10 +7029,10 @@
         <v>1.13</v>
       </c>
       <c r="I117" t="n">
-        <v>0.09426495289083238</v>
+        <v>0.2952</v>
       </c>
       <c r="J117" t="n">
-        <v>2.168093916489145</v>
+        <v>6.7896</v>
       </c>
     </row>
     <row r="118">
@@ -7081,10 +7069,10 @@
         <v>1.04</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.03381278724906505</v>
+        <v>0.1355</v>
       </c>
       <c r="J118" t="n">
-        <v>-0.7776941067284961</v>
+        <v>3.1165</v>
       </c>
     </row>
     <row r="119">
@@ -7121,10 +7109,10 @@
         <v>1</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.09020255567070781</v>
+        <v>0.03</v>
       </c>
       <c r="J119" t="n">
-        <v>-2.074658780426279</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="120">
@@ -7161,10 +7149,10 @@
         <v>0.8</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3787812047560353</v>
+        <v>-0.3715</v>
       </c>
       <c r="J120" t="n">
-        <v>-8.711967709388812</v>
+        <v>-8.544499999999999</v>
       </c>
     </row>
     <row r="121">
@@ -7201,10 +7189,10 @@
         <v>0.79</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3887431652757388</v>
+        <v>-0.3862</v>
       </c>
       <c r="J121" t="n">
-        <v>-8.941092801341991</v>
+        <v>-8.8826</v>
       </c>
     </row>
     <row r="122">
@@ -7241,10 +7229,10 @@
         <v>1.21</v>
       </c>
       <c r="I122" t="n">
-        <v>0.1685876805555042</v>
+        <v>0.4658</v>
       </c>
       <c r="J122" t="n">
-        <v>3.708928972221092</v>
+        <v>10.2476</v>
       </c>
     </row>
     <row r="123">
@@ -7281,10 +7269,10 @@
         <v>0.82</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.2938878974838931</v>
+        <v>-0.2761</v>
       </c>
       <c r="J123" t="n">
-        <v>-6.465533744645648</v>
+        <v>-6.0742</v>
       </c>
     </row>
     <row r="124">
@@ -7321,10 +7309,10 @@
         <v>0.78</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.3723995350857367</v>
+        <v>-0.3538</v>
       </c>
       <c r="J124" t="n">
-        <v>-8.192789771886208</v>
+        <v>-7.7836</v>
       </c>
     </row>
     <row r="125">
@@ -7361,10 +7349,10 @@
         <v>0.7</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.4725205374864818</v>
+        <v>-0.476</v>
       </c>
       <c r="J125" t="n">
-        <v>-10.3954518247026</v>
+        <v>-10.472</v>
       </c>
     </row>
     <row r="126">
@@ -7401,10 +7389,10 @@
         <v>0.58</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5905893741168057</v>
+        <v>-0.638</v>
       </c>
       <c r="J126" t="n">
-        <v>-12.99296623056972</v>
+        <v>-14.036</v>
       </c>
     </row>
     <row r="127">
@@ -7441,10 +7429,10 @@
         <v>1.35</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3099500520039968</v>
+        <v>0.9139</v>
       </c>
       <c r="J127" t="n">
-        <v>6.81890114408793</v>
+        <v>20.1058</v>
       </c>
     </row>
     <row r="128">
@@ -7481,10 +7469,10 @@
         <v>1.33</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2977700276674757</v>
+        <v>0.8691</v>
       </c>
       <c r="J128" t="n">
-        <v>6.550940608684465</v>
+        <v>19.1202</v>
       </c>
     </row>
     <row r="129">
@@ -7521,10 +7509,10 @@
         <v>1.26</v>
       </c>
       <c r="I129" t="n">
-        <v>0.2504251369806977</v>
+        <v>0.7039</v>
       </c>
       <c r="J129" t="n">
-        <v>5.509353013575349</v>
+        <v>15.4858</v>
       </c>
     </row>
     <row r="130">
@@ -7561,10 +7549,10 @@
         <v>1.01</v>
       </c>
       <c r="I130" t="n">
-        <v>0.03203370049639053</v>
+        <v>-0.0594</v>
       </c>
       <c r="J130" t="n">
-        <v>0.7047414109205917</v>
+        <v>-1.3068</v>
       </c>
     </row>
     <row r="131">
@@ -7601,10 +7589,10 @@
         <v>0.98</v>
       </c>
       <c r="I131" t="n">
-        <v>0.01131629207264673</v>
+        <v>-0.2186</v>
       </c>
       <c r="J131" t="n">
-        <v>0.248958425598228</v>
+        <v>-4.8092</v>
       </c>
     </row>
     <row r="132">
@@ -7641,10 +7629,10 @@
         <v>0.93</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.2105287571254505</v>
+        <v>-0.0218</v>
       </c>
       <c r="J132" t="n">
-        <v>-3.578988871132659</v>
+        <v>-0.3706</v>
       </c>
     </row>
     <row r="133">
@@ -7681,10 +7669,10 @@
         <v>0.83</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.313242833414596</v>
+        <v>-0.192</v>
       </c>
       <c r="J133" t="n">
-        <v>-5.325128168048132</v>
+        <v>-3.264</v>
       </c>
     </row>
     <row r="134">
@@ -7721,10 +7709,10 @@
         <v>0.73</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.4369315732391602</v>
+        <v>-0.355</v>
       </c>
       <c r="J134" t="n">
-        <v>-7.427836745065723</v>
+        <v>-6.035</v>
       </c>
     </row>
     <row r="135">
@@ -7761,10 +7749,10 @@
         <v>0.54</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.6980046204161092</v>
+        <v>-0.6598000000000001</v>
       </c>
       <c r="J135" t="n">
-        <v>-11.86607854707386</v>
+        <v>-11.2166</v>
       </c>
     </row>
     <row r="136">
@@ -7801,10 +7789,10 @@
         <v>0.48</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.752112120205913</v>
+        <v>-0.7383</v>
       </c>
       <c r="J136" t="n">
-        <v>-12.78590604350052</v>
+        <v>-12.5511</v>
       </c>
     </row>
     <row r="137">
@@ -7841,10 +7829,10 @@
         <v>1.72</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5370651742156535</v>
+        <v>1.5941</v>
       </c>
       <c r="J137" t="n">
-        <v>9.130107961666109</v>
+        <v>27.0997</v>
       </c>
     </row>
     <row r="138">
@@ -7881,10 +7869,10 @@
         <v>1.37</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3588244554333431</v>
+        <v>0.8968</v>
       </c>
       <c r="J138" t="n">
-        <v>6.100015742366832</v>
+        <v>15.2456</v>
       </c>
     </row>
     <row r="139">
@@ -7921,10 +7909,10 @@
         <v>1.26</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2512955096249891</v>
+        <v>0.6078</v>
       </c>
       <c r="J139" t="n">
-        <v>4.272023663624815</v>
+        <v>10.3326</v>
       </c>
     </row>
     <row r="140">
@@ -7961,10 +7949,10 @@
         <v>1.2</v>
       </c>
       <c r="I140" t="n">
-        <v>0.2063742796902532</v>
+        <v>0.4571</v>
       </c>
       <c r="J140" t="n">
-        <v>3.508362754734304</v>
+        <v>7.7707</v>
       </c>
     </row>
     <row r="141">
@@ -8001,10 +7989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I141" t="n">
-        <v>0.05129629640464707</v>
+        <v>-0.3882</v>
       </c>
       <c r="J141" t="n">
-        <v>0.8720370388790002</v>
+        <v>-6.5994</v>
       </c>
     </row>
     <row r="142">
@@ -8041,10 +8029,10 @@
         <v>1.69</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5877351109726262</v>
+        <v>0.8407</v>
       </c>
       <c r="J142" t="n">
-        <v>9.991496886534646</v>
+        <v>14.2919</v>
       </c>
     </row>
     <row r="143">
@@ -8081,10 +8069,10 @@
         <v>1.67</v>
       </c>
       <c r="I143" t="n">
-        <v>0.5747914000110629</v>
+        <v>0.8191000000000001</v>
       </c>
       <c r="J143" t="n">
-        <v>9.77145380018807</v>
+        <v>13.9247</v>
       </c>
     </row>
     <row r="144">
@@ -8121,10 +8109,10 @@
         <v>1.41</v>
       </c>
       <c r="I144" t="n">
-        <v>0.3225528635601942</v>
+        <v>0.4956</v>
       </c>
       <c r="J144" t="n">
-        <v>5.483398680523301</v>
+        <v>8.4252</v>
       </c>
     </row>
     <row r="145">
@@ -8161,10 +8149,10 @@
         <v>1.36</v>
       </c>
       <c r="I145" t="n">
-        <v>0.279423087099485</v>
+        <v>0.4325</v>
       </c>
       <c r="J145" t="n">
-        <v>4.750192480691246</v>
+        <v>7.3525</v>
       </c>
     </row>
     <row r="146">
@@ -8201,10 +8189,10 @@
         <v>1.24</v>
       </c>
       <c r="I146" t="n">
-        <v>0.1900822693476201</v>
+        <v>0.2794</v>
       </c>
       <c r="J146" t="n">
-        <v>3.231398578909542</v>
+        <v>4.7498</v>
       </c>
     </row>
     <row r="147">
@@ -8241,10 +8229,10 @@
         <v>1.26</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.0001783055127129352</v>
+        <v>0.5701000000000001</v>
       </c>
       <c r="J147" t="n">
-        <v>-0.003031193716119898</v>
+        <v>9.691700000000001</v>
       </c>
     </row>
     <row r="148">
@@ -8281,10 +8269,10 @@
         <v>0.67</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.7748422780477286</v>
+        <v>-0.4893</v>
       </c>
       <c r="J148" t="n">
-        <v>-13.17231872681139</v>
+        <v>-8.318099999999999</v>
       </c>
     </row>
     <row r="149">
@@ -8321,10 +8309,10 @@
         <v>0.65</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.8027563973077235</v>
+        <v>-0.519</v>
       </c>
       <c r="J149" t="n">
-        <v>-13.6468587542313</v>
+        <v>-8.823</v>
       </c>
     </row>
     <row r="150">
@@ -8361,10 +8349,10 @@
         <v>0.64</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.816066506683961</v>
+        <v>-0.5335</v>
       </c>
       <c r="J150" t="n">
-        <v>-13.87313061362734</v>
+        <v>-9.0695</v>
       </c>
     </row>
     <row r="151">
@@ -8401,10 +8389,10 @@
         <v>0.47</v>
       </c>
       <c r="I151" t="n">
-        <v>-1.003725833705255</v>
+        <v>-0.7592</v>
       </c>
       <c r="J151" t="n">
-        <v>-17.06333917298933</v>
+        <v>-12.9064</v>
       </c>
     </row>
     <row r="152">
@@ -8441,10 +8429,10 @@
         <v>1.35</v>
       </c>
       <c r="I152" t="n">
-        <v>0.223200938941446</v>
+        <v>0.5703</v>
       </c>
       <c r="J152" t="n">
-        <v>4.910420656711812</v>
+        <v>12.5466</v>
       </c>
     </row>
     <row r="153">
@@ -8481,10 +8469,10 @@
         <v>1.2</v>
       </c>
       <c r="I153" t="n">
-        <v>0.0863826696794584</v>
+        <v>0.369</v>
       </c>
       <c r="J153" t="n">
-        <v>1.900418732948085</v>
+        <v>8.118</v>
       </c>
     </row>
     <row r="154">
@@ -8521,10 +8509,10 @@
         <v>1.13</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.01818015413252169</v>
+        <v>0.2617</v>
       </c>
       <c r="J154" t="n">
-        <v>-0.3999633909154772</v>
+        <v>5.7574</v>
       </c>
     </row>
     <row r="155">
@@ -8561,10 +8549,10 @@
         <v>0.78</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.5092577925452672</v>
+        <v>-0.4208</v>
       </c>
       <c r="J155" t="n">
-        <v>-11.20367143599588</v>
+        <v>-9.2576</v>
       </c>
     </row>
     <row r="156">
@@ -8601,10 +8589,10 @@
         <v>0.75</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5356959877123337</v>
+        <v>-0.4618</v>
       </c>
       <c r="J156" t="n">
-        <v>-11.78531172967134</v>
+        <v>-10.1596</v>
       </c>
     </row>
     <row r="157">
@@ -8641,10 +8629,10 @@
         <v>1.44</v>
       </c>
       <c r="I157" t="n">
-        <v>0.3263939687658585</v>
+        <v>1.1223</v>
       </c>
       <c r="J157" t="n">
-        <v>7.180667312848888</v>
+        <v>24.6906</v>
       </c>
     </row>
     <row r="158">
@@ -8681,10 +8669,10 @@
         <v>1.21</v>
       </c>
       <c r="I158" t="n">
-        <v>0.1719420905617981</v>
+        <v>0.5962</v>
       </c>
       <c r="J158" t="n">
-        <v>3.782725992359558</v>
+        <v>13.1164</v>
       </c>
     </row>
     <row r="159">
@@ -8721,10 +8709,10 @@
         <v>1.15</v>
       </c>
       <c r="I159" t="n">
-        <v>0.0997496868029613</v>
+        <v>0.4132</v>
       </c>
       <c r="J159" t="n">
-        <v>2.194493109665149</v>
+        <v>9.090400000000001</v>
       </c>
     </row>
     <row r="160">
@@ -8761,10 +8749,10 @@
         <v>1.14</v>
       </c>
       <c r="I160" t="n">
-        <v>0.08685639848974917</v>
+        <v>0.3812</v>
       </c>
       <c r="J160" t="n">
-        <v>1.910840766774482</v>
+        <v>8.3864</v>
       </c>
     </row>
     <row r="161">
@@ -8801,10 +8789,10 @@
         <v>0.84</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3715229761019098</v>
+        <v>-0.6207</v>
       </c>
       <c r="J161" t="n">
-        <v>-8.173505474242017</v>
+        <v>-13.6554</v>
       </c>
     </row>
     <row r="162">
@@ -8841,10 +8829,10 @@
         <v>1.14</v>
       </c>
       <c r="I162" t="n">
-        <v>0.1234818366961757</v>
+        <v>0.3044</v>
       </c>
       <c r="J162" t="n">
-        <v>2.963564080708216</v>
+        <v>7.3056</v>
       </c>
     </row>
     <row r="163">
@@ -8881,10 +8869,10 @@
         <v>1.13</v>
       </c>
       <c r="I163" t="n">
-        <v>0.1116658028244587</v>
+        <v>0.2886</v>
       </c>
       <c r="J163" t="n">
-        <v>2.67997926778701</v>
+        <v>6.9264</v>
       </c>
     </row>
     <row r="164">
@@ -8921,10 +8909,10 @@
         <v>1.01</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.06503005986244681</v>
+        <v>0.057</v>
       </c>
       <c r="J164" t="n">
-        <v>-1.560721436698723</v>
+        <v>1.368</v>
       </c>
     </row>
     <row r="165">
@@ -8961,10 +8949,10 @@
         <v>0.87</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3036407549823094</v>
+        <v>-0.2684</v>
       </c>
       <c r="J165" t="n">
-        <v>-7.287378119575425</v>
+        <v>-6.4416</v>
       </c>
     </row>
     <row r="166">
@@ -9001,10 +8989,10 @@
         <v>0.7</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4781198522329179</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="J166" t="n">
-        <v>-11.47487645359003</v>
+        <v>-12.3504</v>
       </c>
     </row>
     <row r="167">
@@ -9041,10 +9029,10 @@
         <v>1.49</v>
       </c>
       <c r="I167" t="n">
-        <v>0.3535355571434225</v>
+        <v>1.2511</v>
       </c>
       <c r="J167" t="n">
-        <v>8.48485337144214</v>
+        <v>30.0264</v>
       </c>
     </row>
     <row r="168">
@@ -9081,10 +9069,10 @@
         <v>1.43</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3244416148095114</v>
+        <v>1.1287</v>
       </c>
       <c r="J168" t="n">
-        <v>7.786598755428273</v>
+        <v>27.0888</v>
       </c>
     </row>
     <row r="169">
@@ -9121,10 +9109,10 @@
         <v>1.3</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2524336106918527</v>
+        <v>0.8461</v>
       </c>
       <c r="J169" t="n">
-        <v>6.058406656604465</v>
+        <v>20.3064</v>
       </c>
     </row>
     <row r="170">
@@ -9161,10 +9149,10 @@
         <v>0.73</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.48688525041406</v>
+        <v>-0.8672</v>
       </c>
       <c r="J170" t="n">
-        <v>-11.68524600993744</v>
+        <v>-20.8128</v>
       </c>
     </row>
     <row r="171">
@@ -9201,10 +9189,10 @@
         <v>0.57</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6514483947040318</v>
+        <v>-1.208</v>
       </c>
       <c r="J171" t="n">
-        <v>-15.63476147289676</v>
+        <v>-28.992</v>
       </c>
     </row>
     <row r="172">
@@ -9241,10 +9229,10 @@
         <v>1.32</v>
       </c>
       <c r="I172" t="n">
-        <v>0.2199869974394408</v>
+        <v>0.5488</v>
       </c>
       <c r="J172" t="n">
-        <v>10.33938887965372</v>
+        <v>25.7936</v>
       </c>
     </row>
     <row r="173">
@@ -9281,10 +9269,10 @@
         <v>1.25</v>
       </c>
       <c r="I173" t="n">
-        <v>0.1726833318196688</v>
+        <v>0.4564</v>
       </c>
       <c r="J173" t="n">
-        <v>8.116116595524433</v>
+        <v>21.4508</v>
       </c>
     </row>
     <row r="174">
@@ -9321,10 +9309,10 @@
         <v>1.07</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.0107867788327971</v>
+        <v>0.1776</v>
       </c>
       <c r="J174" t="n">
-        <v>-0.5069786051414636</v>
+        <v>8.347200000000001</v>
       </c>
     </row>
     <row r="175">
@@ -9361,10 +9349,10 @@
         <v>0.72</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.5787437677513957</v>
+        <v>-0.4924</v>
       </c>
       <c r="J175" t="n">
-        <v>-27.2009570843156</v>
+        <v>-23.1428</v>
       </c>
     </row>
     <row r="176">
@@ -9401,10 +9389,10 @@
         <v>0.6</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.693954461423673</v>
+        <v>-0.6447000000000001</v>
       </c>
       <c r="J176" t="n">
-        <v>-32.61585968691263</v>
+        <v>-30.3009</v>
       </c>
     </row>
     <row r="177">
@@ -9441,10 +9429,10 @@
         <v>1.26</v>
       </c>
       <c r="I177" t="n">
-        <v>0.3190699405146303</v>
+        <v>0.7538</v>
       </c>
       <c r="J177" t="n">
-        <v>14.99628720418763</v>
+        <v>35.4286</v>
       </c>
     </row>
     <row r="178">
@@ -9481,10 +9469,10 @@
         <v>1.17</v>
       </c>
       <c r="I178" t="n">
-        <v>0.2282723156494988</v>
+        <v>0.526</v>
       </c>
       <c r="J178" t="n">
-        <v>10.72879883552644</v>
+        <v>24.722</v>
       </c>
     </row>
     <row r="179">
@@ -9521,10 +9509,10 @@
         <v>1.12</v>
       </c>
       <c r="I179" t="n">
-        <v>0.163296221084364</v>
+        <v>0.3805</v>
       </c>
       <c r="J179" t="n">
-        <v>7.674922390965109</v>
+        <v>17.8835</v>
       </c>
     </row>
     <row r="180">
@@ -9561,10 +9549,10 @@
         <v>1.02</v>
       </c>
       <c r="I180" t="n">
-        <v>0.002043766791155544</v>
+        <v>0.0225</v>
       </c>
       <c r="J180" t="n">
-        <v>0.09605703918431058</v>
+        <v>1.0575</v>
       </c>
     </row>
     <row r="181">
@@ -9601,10 +9589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.1330845443132093</v>
+        <v>-0.3237</v>
       </c>
       <c r="J181" t="n">
-        <v>-6.254973582720837</v>
+        <v>-15.2139</v>
       </c>
     </row>
     <row r="182">
@@ -9641,10 +9629,10 @@
         <v>1.73</v>
       </c>
       <c r="I182" t="n">
-        <v>0.4211556571258722</v>
+        <v>1.6286</v>
       </c>
       <c r="J182" t="n">
-        <v>8.844268799643316</v>
+        <v>34.2006</v>
       </c>
     </row>
     <row r="183">
@@ -9681,10 +9669,10 @@
         <v>1.41</v>
       </c>
       <c r="I183" t="n">
-        <v>0.272636151027026</v>
+        <v>1.0049</v>
       </c>
       <c r="J183" t="n">
-        <v>5.725359171567546</v>
+        <v>21.1029</v>
       </c>
     </row>
     <row r="184">
@@ -9721,10 +9709,10 @@
         <v>1.36</v>
       </c>
       <c r="I184" t="n">
-        <v>0.2415189106192114</v>
+        <v>0.8948</v>
       </c>
       <c r="J184" t="n">
-        <v>5.071897123003438</v>
+        <v>18.7908</v>
       </c>
     </row>
     <row r="185">
@@ -9761,10 +9749,10 @@
         <v>1.03</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.06720836506076719</v>
+        <v>-0.0077</v>
       </c>
       <c r="J185" t="n">
-        <v>-1.411375666276111</v>
+        <v>-0.1617</v>
       </c>
     </row>
     <row r="186">
@@ -9801,10 +9789,10 @@
         <v>0.78</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4800837328902922</v>
+        <v>-0.7904</v>
       </c>
       <c r="J186" t="n">
-        <v>-10.08175839069614</v>
+        <v>-16.5984</v>
       </c>
     </row>
     <row r="187">
@@ -9841,10 +9829,10 @@
         <v>1.22</v>
       </c>
       <c r="I187" t="n">
-        <v>0.0400694051385241</v>
+        <v>0.4149</v>
       </c>
       <c r="J187" t="n">
-        <v>0.8414575079090062</v>
+        <v>8.712899999999999</v>
       </c>
     </row>
     <row r="188">
@@ -9881,10 +9869,10 @@
         <v>1.11</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.08495310427370559</v>
+        <v>0.2478</v>
       </c>
       <c r="J188" t="n">
-        <v>-1.784015189747817</v>
+        <v>5.2038</v>
       </c>
     </row>
     <row r="189">
@@ -9921,10 +9909,10 @@
         <v>1.02</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1941162078166794</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="J189" t="n">
-        <v>-4.076440364150267</v>
+        <v>1.5204</v>
       </c>
     </row>
     <row r="190">
@@ -9961,10 +9949,10 @@
         <v>0.95</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.310977353571491</v>
+        <v>-0.132</v>
       </c>
       <c r="J190" t="n">
-        <v>-6.530524425001312</v>
+        <v>-2.772</v>
       </c>
     </row>
     <row r="191">
@@ -10001,10 +9989,10 @@
         <v>0.66</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5661218571571455</v>
+        <v>-0.5702</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.88855900030005</v>
+        <v>-11.9742</v>
       </c>
     </row>
     <row r="192">
@@ -10041,10 +10029,10 @@
         <v>1.89</v>
       </c>
       <c r="I192" t="n">
-        <v>0.6672924768438763</v>
+        <v>1.9244</v>
       </c>
       <c r="J192" t="n">
-        <v>14.68043449056528</v>
+        <v>42.3368</v>
       </c>
     </row>
     <row r="193">
@@ -10081,10 +10069,10 @@
         <v>1.12</v>
       </c>
       <c r="I193" t="n">
-        <v>0.09851107349862727</v>
+        <v>0.2936</v>
       </c>
       <c r="J193" t="n">
-        <v>2.1672436169698</v>
+        <v>6.4592</v>
       </c>
     </row>
     <row r="194">
@@ -10121,10 +10109,10 @@
         <v>1.04</v>
       </c>
       <c r="I194" t="n">
-        <v>0.01901782712148899</v>
+        <v>0.05</v>
       </c>
       <c r="J194" t="n">
-        <v>0.4183921966727578</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="195">
@@ -10161,10 +10149,10 @@
         <v>0.98</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.05101358896066874</v>
+        <v>-0.2236</v>
       </c>
       <c r="J195" t="n">
-        <v>-1.122298957134712</v>
+        <v>-4.9192</v>
       </c>
     </row>
     <row r="196">
@@ -10201,10 +10189,10 @@
         <v>0.97</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.06410937864634436</v>
+        <v>-0.261</v>
       </c>
       <c r="J196" t="n">
-        <v>-1.410406330219576</v>
+        <v>-5.742</v>
       </c>
     </row>
     <row r="197">
@@ -10241,10 +10229,10 @@
         <v>1.16</v>
       </c>
       <c r="I197" t="n">
-        <v>0.04868116323506548</v>
+        <v>0.3519</v>
       </c>
       <c r="J197" t="n">
-        <v>1.070985591171441</v>
+        <v>7.7418</v>
       </c>
     </row>
     <row r="198">
@@ -10281,10 +10269,10 @@
         <v>1.15</v>
       </c>
       <c r="I198" t="n">
-        <v>0.03970720520011564</v>
+        <v>0.3367</v>
       </c>
       <c r="J198" t="n">
-        <v>0.8735585144025442</v>
+        <v>7.4074</v>
       </c>
     </row>
     <row r="199">
@@ -10321,10 +10309,10 @@
         <v>0.83</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.4632069252245598</v>
+        <v>-0.3173</v>
       </c>
       <c r="J199" t="n">
-        <v>-10.19055235494031</v>
+        <v>-6.9806</v>
       </c>
     </row>
     <row r="200">
@@ -10361,10 +10349,10 @@
         <v>0.77</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.5390675698629525</v>
+        <v>-0.4076</v>
       </c>
       <c r="J200" t="n">
-        <v>-11.85948653698495</v>
+        <v>-8.9672</v>
       </c>
     </row>
     <row r="201">
@@ -10401,10 +10389,10 @@
         <v>0.71</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6061890563925091</v>
+        <v>-0.4914</v>
       </c>
       <c r="J201" t="n">
-        <v>-13.3361592406352</v>
+        <v>-10.8108</v>
       </c>
     </row>
     <row r="202">
@@ -10441,10 +10429,10 @@
         <v>1.63</v>
       </c>
       <c r="I202" t="n">
-        <v>0.4261434163577187</v>
+        <v>1.4662</v>
       </c>
       <c r="J202" t="n">
-        <v>9.375155159869811</v>
+        <v>32.2564</v>
       </c>
     </row>
     <row r="203">
@@ -10481,10 +10469,10 @@
         <v>1.35</v>
       </c>
       <c r="I203" t="n">
-        <v>0.2832383383693528</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="J203" t="n">
-        <v>6.231243444125762</v>
+        <v>19.7494</v>
       </c>
     </row>
     <row r="204">
@@ -10521,10 +10509,10 @@
         <v>1.16</v>
       </c>
       <c r="I204" t="n">
-        <v>0.1122776775490572</v>
+        <v>0.3958</v>
       </c>
       <c r="J204" t="n">
-        <v>2.470108906079258</v>
+        <v>8.707599999999999</v>
       </c>
     </row>
     <row r="205">
@@ -10561,10 +10549,10 @@
         <v>1.14</v>
       </c>
       <c r="I205" t="n">
-        <v>0.0960632520598443</v>
+        <v>0.3409</v>
       </c>
       <c r="J205" t="n">
-        <v>2.113391545316575</v>
+        <v>7.4998</v>
       </c>
     </row>
     <row r="206">
@@ -10601,10 +10589,10 @@
         <v>0.8</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3514590265354034</v>
+        <v>-0.7337</v>
       </c>
       <c r="J206" t="n">
-        <v>-7.732098583778875</v>
+        <v>-16.1414</v>
       </c>
     </row>
     <row r="207">
@@ -10641,10 +10629,10 @@
         <v>1.11</v>
       </c>
       <c r="I207" t="n">
-        <v>0.02146489749382676</v>
+        <v>0.2902</v>
       </c>
       <c r="J207" t="n">
-        <v>0.4722277448641887</v>
+        <v>6.3844</v>
       </c>
     </row>
     <row r="208">
@@ -10681,10 +10669,10 @@
         <v>0.99</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.1076052577343374</v>
+        <v>0.0265</v>
       </c>
       <c r="J208" t="n">
-        <v>-2.367315670155423</v>
+        <v>0.583</v>
       </c>
     </row>
     <row r="209">
@@ -10721,10 +10709,10 @@
         <v>0.92</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1935912500239118</v>
+        <v>-0.1231</v>
       </c>
       <c r="J209" t="n">
-        <v>-4.25900750052606</v>
+        <v>-2.7082</v>
       </c>
     </row>
     <row r="210">
@@ -10761,10 +10749,10 @@
         <v>0.8</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3786441100317728</v>
+        <v>-0.3486</v>
       </c>
       <c r="J210" t="n">
-        <v>-8.330170420699002</v>
+        <v>-7.6692</v>
       </c>
     </row>
     <row r="211">
@@ -10801,10 +10789,10 @@
         <v>0.58</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5754106080612118</v>
+        <v>-0.6506999999999999</v>
       </c>
       <c r="J211" t="n">
-        <v>-12.65903337734666</v>
+        <v>-14.3154</v>
       </c>
     </row>
     <row r="212">
@@ -10841,10 +10829,10 @@
         <v>1.41</v>
       </c>
       <c r="I212" t="n">
-        <v>0.3726006290818669</v>
+        <v>1.0901</v>
       </c>
       <c r="J212" t="n">
-        <v>8.942415097964806</v>
+        <v>26.1624</v>
       </c>
     </row>
     <row r="213">
@@ -10881,10 +10869,10 @@
         <v>1.24</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2461009387797724</v>
+        <v>0.7079</v>
       </c>
       <c r="J213" t="n">
-        <v>5.906422530714538</v>
+        <v>16.9896</v>
       </c>
     </row>
     <row r="214">
@@ -10921,10 +10909,10 @@
         <v>1.16</v>
       </c>
       <c r="I214" t="n">
-        <v>0.1684747324544062</v>
+        <v>0.5013</v>
       </c>
       <c r="J214" t="n">
-        <v>4.043393578905748</v>
+        <v>12.0312</v>
       </c>
     </row>
     <row r="215">
@@ -10961,10 +10949,10 @@
         <v>0.92</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2181921042573825</v>
+        <v>-0.3835</v>
       </c>
       <c r="J215" t="n">
-        <v>-5.23661050217718</v>
+        <v>-9.204000000000001</v>
       </c>
     </row>
     <row r="216">
@@ -11001,10 +10989,10 @@
         <v>0.76</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3914879032792246</v>
+        <v>-0.7969000000000001</v>
       </c>
       <c r="J216" t="n">
-        <v>-9.39570967870139</v>
+        <v>-19.1256</v>
       </c>
     </row>
     <row r="217">
@@ -11041,10 +11029,10 @@
         <v>1.46</v>
       </c>
       <c r="I217" t="n">
-        <v>0.2603268263838071</v>
+        <v>0.7081</v>
       </c>
       <c r="J217" t="n">
-        <v>6.247843833211371</v>
+        <v>16.9944</v>
       </c>
     </row>
     <row r="218">
@@ -11081,10 +11069,10 @@
         <v>1.09</v>
       </c>
       <c r="I218" t="n">
-        <v>0.01243092774950026</v>
+        <v>0.1992</v>
       </c>
       <c r="J218" t="n">
-        <v>0.2983422659880063</v>
+        <v>4.7808</v>
       </c>
     </row>
     <row r="219">
@@ -11121,10 +11109,10 @@
         <v>0.99</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.2560085200225097</v>
+        <v>-0.0551</v>
       </c>
       <c r="J219" t="n">
-        <v>-6.144204480540234</v>
+        <v>-1.3224</v>
       </c>
     </row>
     <row r="220">
@@ -11161,10 +11149,10 @@
         <v>0.9</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4257516456946692</v>
+        <v>-0.2363</v>
       </c>
       <c r="J220" t="n">
-        <v>-10.21803949667206</v>
+        <v>-5.6712</v>
       </c>
     </row>
     <row r="221">
@@ -11201,10 +11189,10 @@
         <v>0.7</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6974006909260522</v>
+        <v>-0.5252</v>
       </c>
       <c r="J221" t="n">
-        <v>-16.73761658222525</v>
+        <v>-12.6048</v>
       </c>
     </row>
     <row r="222">
@@ -11241,10 +11229,10 @@
         <v>1.72</v>
       </c>
       <c r="I222" t="n">
-        <v>0.4928184550005897</v>
+        <v>1.5728</v>
       </c>
       <c r="J222" t="n">
-        <v>8.870732190010614</v>
+        <v>28.3104</v>
       </c>
     </row>
     <row r="223">
@@ -11281,10 +11269,10 @@
         <v>1.36</v>
       </c>
       <c r="I223" t="n">
-        <v>0.2825489856018014</v>
+        <v>0.8403</v>
       </c>
       <c r="J223" t="n">
-        <v>5.085881740832424</v>
+        <v>15.1254</v>
       </c>
     </row>
     <row r="224">
@@ -11321,10 +11309,10 @@
         <v>1.28</v>
       </c>
       <c r="I224" t="n">
-        <v>0.1995283335720312</v>
+        <v>0.6292</v>
       </c>
       <c r="J224" t="n">
-        <v>3.591510004296561</v>
+        <v>11.3256</v>
       </c>
     </row>
     <row r="225">
@@ -11361,10 +11349,10 @@
         <v>1.23</v>
       </c>
       <c r="I225" t="n">
-        <v>0.1636395977026316</v>
+        <v>0.5092</v>
       </c>
       <c r="J225" t="n">
-        <v>2.945512758647369</v>
+        <v>9.1656</v>
       </c>
     </row>
     <row r="226">
@@ -11401,10 +11389,10 @@
         <v>1.14</v>
       </c>
       <c r="I226" t="n">
-        <v>0.1055959123774766</v>
+        <v>0.2858</v>
       </c>
       <c r="J226" t="n">
-        <v>1.900726422794579</v>
+        <v>5.1444</v>
       </c>
     </row>
     <row r="227">
@@ -11441,10 +11429,10 @@
         <v>1.06</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.133277930875878</v>
+        <v>0.2218</v>
       </c>
       <c r="J227" t="n">
-        <v>-2.399002755765804</v>
+        <v>3.9924</v>
       </c>
     </row>
     <row r="228">
@@ -11481,10 +11469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.2435963166946547</v>
+        <v>-0.063</v>
       </c>
       <c r="J228" t="n">
-        <v>-4.384733700503785</v>
+        <v>-1.134</v>
       </c>
     </row>
     <row r="229">
@@ -11521,10 +11509,10 @@
         <v>0.91</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2742899013252655</v>
+        <v>-0.1191</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.93721822385478</v>
+        <v>-2.1438</v>
       </c>
     </row>
     <row r="230">
@@ -11561,10 +11549,10 @@
         <v>0.65</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.5730597084431772</v>
+        <v>-0.55</v>
       </c>
       <c r="J230" t="n">
-        <v>-10.31507475197719</v>
+        <v>-9.9</v>
       </c>
     </row>
     <row r="231">
@@ -11601,10 +11589,10 @@
         <v>0.61</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6036580322609448</v>
+        <v>-0.6029</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.86584458069701</v>
+        <v>-10.8522</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/6868/event_6868_evp_summary.xlsx
+++ b/database/event/6868/event_6868_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>6.1471</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.7916</v>
       </c>
       <c r="D2" t="n">
         <v>2.0619</v>
@@ -545,7 +545,7 @@
         <v>5.6211</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.7238</v>
       </c>
       <c r="D3" t="n">
         <v>1.8494</v>
@@ -591,7 +591,7 @@
         <v>4.8504</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>0.6246</v>
       </c>
       <c r="D4" t="n">
         <v>1.5381</v>
@@ -637,7 +637,7 @@
         <v>3.2913</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.4238</v>
       </c>
       <c r="D5" t="n">
         <v>0.9082</v>
@@ -683,7 +683,7 @@
         <v>2.8898</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.3721</v>
       </c>
       <c r="D6" t="n">
         <v>0.7461</v>
@@ -729,7 +729,7 @@
         <v>2.8344</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>0.365</v>
       </c>
       <c r="D7" t="n">
         <v>0.7237</v>
@@ -775,7 +775,7 @@
         <v>2.7961</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.3601</v>
       </c>
       <c r="D8" t="n">
         <v>0.7082000000000001</v>
@@ -821,7 +821,7 @@
         <v>2.3473</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.3023</v>
       </c>
       <c r="D9" t="n">
         <v>0.5269</v>
@@ -867,7 +867,7 @@
         <v>2.2831</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.294</v>
       </c>
       <c r="D10" t="n">
         <v>0.501</v>
@@ -913,7 +913,7 @@
         <v>2.161</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>0.2783</v>
       </c>
       <c r="D11" t="n">
         <v>0.4516</v>
@@ -959,7 +959,7 @@
         <v>1.9003</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.2447</v>
       </c>
       <c r="D12" t="n">
         <v>0.3463</v>
@@ -1005,7 +1005,7 @@
         <v>1.8867</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>0.243</v>
       </c>
       <c r="D13" t="n">
         <v>0.3408</v>
@@ -1051,7 +1051,7 @@
         <v>1.7884</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.2303</v>
       </c>
       <c r="D14" t="n">
         <v>0.3011</v>
@@ -1097,7 +1097,7 @@
         <v>1.6528</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.2128</v>
       </c>
       <c r="D15" t="n">
         <v>0.2463</v>
@@ -1143,7 +1143,7 @@
         <v>1.6244</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.2092</v>
       </c>
       <c r="D16" t="n">
         <v>0.2349</v>
@@ -1189,7 +1189,7 @@
         <v>1.4712</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.1894</v>
       </c>
       <c r="D17" t="n">
         <v>0.173</v>
@@ -1235,7 +1235,7 @@
         <v>1.2192</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.157</v>
       </c>
       <c r="D18" t="n">
         <v>0.0712</v>
@@ -1281,7 +1281,7 @@
         <v>0.9643</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.1242</v>
       </c>
       <c r="D19" t="n">
         <v>-0.0318</v>
@@ -1327,7 +1327,7 @@
         <v>0.824</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.1061</v>
       </c>
       <c r="D20" t="n">
         <v>-0.0885</v>
@@ -1373,7 +1373,7 @@
         <v>0.8168</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.1052</v>
       </c>
       <c r="D21" t="n">
         <v>-0.0914</v>
@@ -1419,7 +1419,7 @@
         <v>0.7135</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.0919</v>
       </c>
       <c r="D22" t="n">
         <v>-0.1331</v>
@@ -1465,7 +1465,7 @@
         <v>0.4871</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="D23" t="n">
         <v>-0.2246</v>
@@ -1511,7 +1511,7 @@
         <v>0.3731</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="D24" t="n">
         <v>-0.2706</v>
@@ -1557,7 +1557,7 @@
         <v>0.135</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.0174</v>
       </c>
       <c r="D25" t="n">
         <v>-0.3668</v>
@@ -1603,7 +1603,7 @@
         <v>0.0399</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.0051</v>
       </c>
       <c r="D26" t="n">
         <v>-0.4052</v>
@@ -1649,7 +1649,7 @@
         <v>-0.0507</v>
       </c>
       <c r="C27" t="n">
-        <v>-0</v>
+        <v>-0.0065</v>
       </c>
       <c r="D27" t="n">
         <v>-0.4418</v>
@@ -1695,7 +1695,7 @@
         <v>-0.1342</v>
       </c>
       <c r="C28" t="n">
-        <v>-0</v>
+        <v>-0.0173</v>
       </c>
       <c r="D28" t="n">
         <v>-0.4756</v>
@@ -1741,7 +1741,7 @@
         <v>-0.463</v>
       </c>
       <c r="C29" t="n">
-        <v>-0</v>
+        <v>-0.0596</v>
       </c>
       <c r="D29" t="n">
         <v>-0.6084000000000001</v>
@@ -1787,7 +1787,7 @@
         <v>-0.5311</v>
       </c>
       <c r="C30" t="n">
-        <v>-0</v>
+        <v>-0.0684</v>
       </c>
       <c r="D30" t="n">
         <v>-0.6359</v>
@@ -1833,7 +1833,7 @@
         <v>-0.6169</v>
       </c>
       <c r="C31" t="n">
-        <v>-0</v>
+        <v>-0.0794</v>
       </c>
       <c r="D31" t="n">
         <v>-0.6706</v>
@@ -1879,7 +1879,7 @@
         <v>-0.6185</v>
       </c>
       <c r="C32" t="n">
-        <v>-0</v>
+        <v>-0.0796</v>
       </c>
       <c r="D32" t="n">
         <v>-0.6712</v>
@@ -1925,7 +1925,7 @@
         <v>-0.6731</v>
       </c>
       <c r="C33" t="n">
-        <v>-0</v>
+        <v>-0.0867</v>
       </c>
       <c r="D33" t="n">
         <v>-0.6933</v>
@@ -1971,7 +1971,7 @@
         <v>-0.8746</v>
       </c>
       <c r="C34" t="n">
-        <v>-0</v>
+        <v>-0.1126</v>
       </c>
       <c r="D34" t="n">
         <v>-0.7747000000000001</v>
@@ -2017,7 +2017,7 @@
         <v>-0.8925</v>
       </c>
       <c r="C35" t="n">
-        <v>-0</v>
+        <v>-0.1149</v>
       </c>
       <c r="D35" t="n">
         <v>-0.7819</v>
@@ -2063,7 +2063,7 @@
         <v>-1.2588</v>
       </c>
       <c r="C36" t="n">
-        <v>-0</v>
+        <v>-0.1621</v>
       </c>
       <c r="D36" t="n">
         <v>-0.9298999999999999</v>
@@ -2109,7 +2109,7 @@
         <v>-1.3695</v>
       </c>
       <c r="C37" t="n">
-        <v>-0</v>
+        <v>-0.1764</v>
       </c>
       <c r="D37" t="n">
         <v>-0.9746</v>
@@ -2155,7 +2155,7 @@
         <v>-1.6029</v>
       </c>
       <c r="C38" t="n">
-        <v>-0</v>
+        <v>-0.2064</v>
       </c>
       <c r="D38" t="n">
         <v>-1.0689</v>
@@ -2201,7 +2201,7 @@
         <v>-1.9705</v>
       </c>
       <c r="C39" t="n">
-        <v>-0</v>
+        <v>-0.2537</v>
       </c>
       <c r="D39" t="n">
         <v>-1.2174</v>
@@ -2247,7 +2247,7 @@
         <v>-2.0267</v>
       </c>
       <c r="C40" t="n">
-        <v>-0</v>
+        <v>-0.261</v>
       </c>
       <c r="D40" t="n">
         <v>-1.2401</v>
@@ -2293,7 +2293,7 @@
         <v>-2.0705</v>
       </c>
       <c r="C41" t="n">
-        <v>-0</v>
+        <v>-0.2666</v>
       </c>
       <c r="D41" t="n">
         <v>-1.2578</v>

--- a/database/event/6868/event_6868_evp_summary.xlsx
+++ b/database/event/6868/event_6868_evp_summary.xlsx
@@ -492,93 +492,93 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>sdy</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.1471</v>
+        <v>6.2484</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7916</v>
+        <v>0.8046</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0619</v>
+        <v>2.0455</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1471</v>
+        <v>6.2484</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3184</v>
+        <v>3.0444</v>
       </c>
       <c r="G2" t="n">
-        <v>1.8287</v>
+        <v>3.204</v>
       </c>
       <c r="H2" t="n">
-        <v>4.8136</v>
+        <v>3.0444</v>
       </c>
       <c r="I2" t="n">
-        <v>3.9016</v>
+        <v>2.4676</v>
       </c>
       <c r="J2" t="n">
-        <v>1.8287</v>
+        <v>3.204</v>
       </c>
       <c r="K2" t="n">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="L2" t="n">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="M2" t="n">
-        <v>5.7303</v>
+        <v>5.6716</v>
       </c>
       <c r="N2" t="n">
-        <v>252</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sdy</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.6211</v>
+        <v>6.152</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7238</v>
+        <v>0.7922</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8494</v>
+        <v>2.007</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6211</v>
+        <v>6.152</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4171</v>
+        <v>4.3233</v>
       </c>
       <c r="G3" t="n">
-        <v>3.204</v>
+        <v>1.8287</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4171</v>
+        <v>4.8333</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9591</v>
+        <v>3.9175</v>
       </c>
       <c r="J3" t="n">
-        <v>3.204</v>
+        <v>1.8287</v>
       </c>
       <c r="K3" t="n">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="L3" t="n">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="M3" t="n">
-        <v>5.1631</v>
+        <v>5.7462</v>
       </c>
       <c r="N3" t="n">
-        <v>160</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4">
@@ -594,7 +594,7 @@
         <v>0.6246</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5381</v>
+        <v>1.4885</v>
       </c>
       <c r="E4" t="n">
         <v>4.8504</v>
@@ -640,7 +640,7 @@
         <v>0.4238</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9082</v>
+        <v>0.8673</v>
       </c>
       <c r="E5" t="n">
         <v>3.2913</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.8898</v>
+        <v>3.0154</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3721</v>
+        <v>0.3883</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7461</v>
+        <v>0.7574</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8898</v>
+        <v>3.0154</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9086</v>
+        <v>2.0342</v>
       </c>
       <c r="G6" t="n">
         <v>0.9812</v>
       </c>
       <c r="H6" t="n">
-        <v>1.9086</v>
+        <v>2.0342</v>
       </c>
       <c r="I6" t="n">
-        <v>1.547</v>
+        <v>1.6488</v>
       </c>
       <c r="J6" t="n">
         <v>0.9812</v>
@@ -713,7 +713,7 @@
         <v>63</v>
       </c>
       <c r="M6" t="n">
-        <v>2.5282</v>
+        <v>2.63</v>
       </c>
       <c r="N6" t="n">
         <v>175</v>
@@ -722,127 +722,127 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>br0</t>
+          <t>insani</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.8344</v>
+        <v>2.8933</v>
       </c>
       <c r="C7" t="n">
-        <v>0.365</v>
+        <v>0.3726</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7237</v>
+        <v>0.7088</v>
       </c>
       <c r="E7" t="n">
-        <v>2.8344</v>
+        <v>2.8933</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7668</v>
+        <v>3.1693</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0676</v>
+        <v>-0.276</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7668</v>
+        <v>3.1693</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6215000000000001</v>
+        <v>2.5688</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0676</v>
+        <v>-0.276</v>
       </c>
       <c r="K7" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="L7" t="n">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="M7" t="n">
-        <v>2.6891</v>
+        <v>2.2928</v>
       </c>
       <c r="N7" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>kRaSnaL</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.7961</v>
+        <v>2.8792</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3601</v>
+        <v>0.3708</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7082000000000001</v>
+        <v>0.7032</v>
       </c>
       <c r="E8" t="n">
-        <v>2.7961</v>
+        <v>2.8792</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2933</v>
+        <v>2.3592</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5028</v>
+        <v>0.52</v>
       </c>
       <c r="H8" t="n">
-        <v>2.2933</v>
+        <v>2.3592</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8588</v>
+        <v>1.9122</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5028</v>
+        <v>0.52</v>
       </c>
       <c r="K8" t="n">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="L8" t="n">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="M8" t="n">
-        <v>2.3616</v>
+        <v>2.4322</v>
       </c>
       <c r="N8" t="n">
-        <v>252</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kRaSnaL</t>
+          <t>br0</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.3473</v>
+        <v>2.8344</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3023</v>
+        <v>0.365</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5269</v>
+        <v>0.6853</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3473</v>
+        <v>2.8344</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8273</v>
+        <v>0.7668</v>
       </c>
       <c r="G9" t="n">
-        <v>0.52</v>
+        <v>2.0676</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8273</v>
+        <v>0.7668</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4811</v>
+        <v>0.6215000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.52</v>
+        <v>2.0676</v>
       </c>
       <c r="K9" t="n">
         <v>39</v>
@@ -851,7 +851,7 @@
         <v>121</v>
       </c>
       <c r="M9" t="n">
-        <v>2.0011</v>
+        <v>2.6891</v>
       </c>
       <c r="N9" t="n">
         <v>160</v>
@@ -860,173 +860,173 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>insani</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.2831</v>
+        <v>2.7961</v>
       </c>
       <c r="C10" t="n">
-        <v>0.294</v>
+        <v>0.3601</v>
       </c>
       <c r="D10" t="n">
-        <v>0.501</v>
+        <v>0.6701</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2831</v>
+        <v>2.7961</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5591</v>
+        <v>2.2933</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.276</v>
+        <v>0.5028</v>
       </c>
       <c r="H10" t="n">
-        <v>2.5591</v>
+        <v>2.2933</v>
       </c>
       <c r="I10" t="n">
-        <v>2.0742</v>
+        <v>1.8588</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.276</v>
+        <v>0.5028</v>
       </c>
       <c r="K10" t="n">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="L10" t="n">
-        <v>93</v>
+        <v>151</v>
       </c>
       <c r="M10" t="n">
-        <v>1.7982</v>
+        <v>2.3616</v>
       </c>
       <c r="N10" t="n">
-        <v>162</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>DemQQ</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.161</v>
+        <v>2.1793</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2783</v>
+        <v>0.2806</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4516</v>
+        <v>0.4243</v>
       </c>
       <c r="E11" t="n">
-        <v>2.161</v>
+        <v>2.1793</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7035</v>
+        <v>2.2765</v>
       </c>
       <c r="G11" t="n">
-        <v>1.4575</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7035</v>
+        <v>2.2765</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5702</v>
+        <v>1.8452</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4575</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="L11" t="n">
-        <v>63</v>
+        <v>121</v>
       </c>
       <c r="M11" t="n">
-        <v>2.0277</v>
+        <v>1.748</v>
       </c>
       <c r="N11" t="n">
-        <v>175</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DemQQ</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.9003</v>
+        <v>2.161</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2447</v>
+        <v>0.2783</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3463</v>
+        <v>0.417</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9003</v>
+        <v>2.161</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9975</v>
+        <v>0.7035</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.09719999999999999</v>
+        <v>1.4575</v>
       </c>
       <c r="H12" t="n">
-        <v>1.9975</v>
+        <v>0.7035</v>
       </c>
       <c r="I12" t="n">
-        <v>1.619</v>
+        <v>0.5702</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.09719999999999999</v>
+        <v>1.4575</v>
       </c>
       <c r="K12" t="n">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c r="L12" t="n">
-        <v>121</v>
+        <v>63</v>
       </c>
       <c r="M12" t="n">
-        <v>1.5218</v>
+        <v>2.0277</v>
       </c>
       <c r="N12" t="n">
-        <v>160</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.8867</v>
+        <v>1.9149</v>
       </c>
       <c r="C13" t="n">
-        <v>0.243</v>
+        <v>0.2466</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3408</v>
+        <v>0.319</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8867</v>
+        <v>1.9149</v>
       </c>
       <c r="F13" t="n">
-        <v>2.656</v>
+        <v>2.6515</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.7693</v>
+        <v>-0.7366</v>
       </c>
       <c r="H13" t="n">
-        <v>2.656</v>
+        <v>2.6515</v>
       </c>
       <c r="I13" t="n">
-        <v>2.1528</v>
+        <v>2.1491</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.7693</v>
+        <v>-0.7366</v>
       </c>
       <c r="K13" t="n">
         <v>112</v>
@@ -1035,7 +1035,7 @@
         <v>63</v>
       </c>
       <c r="M13" t="n">
-        <v>1.3835</v>
+        <v>1.4125</v>
       </c>
       <c r="N13" t="n">
         <v>175</v>
@@ -1044,185 +1044,185 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Djoko</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.7884</v>
+        <v>1.8867</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2303</v>
+        <v>0.243</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3011</v>
+        <v>0.3078</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7884</v>
+        <v>1.8867</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7884</v>
+        <v>2.656</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.7693</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7884</v>
+        <v>2.656</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7884</v>
+        <v>2.1528</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.7693</v>
       </c>
       <c r="K14" t="n">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7884</v>
+        <v>1.3835</v>
       </c>
       <c r="N14" t="n">
-        <v>85</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>brnz4n</t>
+          <t>Djoko</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.6528</v>
+        <v>1.7884</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2128</v>
+        <v>0.2303</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2463</v>
+        <v>0.2686</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6528</v>
+        <v>1.7884</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5311</v>
+        <v>1.7884</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1217</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5311</v>
+        <v>1.7884</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4305</v>
+        <v>1.7884</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1217</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="L15" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.5522</v>
+        <v>1.7884</v>
       </c>
       <c r="N15" t="n">
-        <v>162</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>volt</t>
+          <t>brnz4n</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.6244</v>
+        <v>1.6528</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2092</v>
+        <v>0.2128</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2349</v>
+        <v>0.2146</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6244</v>
+        <v>1.6528</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6244</v>
+        <v>0.5311</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1.1217</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6244</v>
+        <v>0.5311</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6244</v>
+        <v>0.4305</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1.1217</v>
       </c>
       <c r="K16" t="n">
-        <v>128</v>
+        <v>69</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="M16" t="n">
-        <v>1.6244</v>
+        <v>1.5522</v>
       </c>
       <c r="N16" t="n">
-        <v>128</v>
+        <v>162</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>volt</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.4712</v>
+        <v>1.6244</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1894</v>
+        <v>0.2092</v>
       </c>
       <c r="D17" t="n">
-        <v>0.173</v>
+        <v>0.2033</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4712</v>
+        <v>1.6244</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2078</v>
+        <v>1.6244</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7366</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2078</v>
+        <v>1.6244</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7895</v>
+        <v>1.6244</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7366</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="L17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0529</v>
+        <v>1.6244</v>
       </c>
       <c r="N17" t="n">
-        <v>175</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18">
@@ -1238,7 +1238,7 @@
         <v>0.157</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0712</v>
+        <v>0.0418</v>
       </c>
       <c r="E18" t="n">
         <v>1.2192</v>
@@ -1284,7 +1284,7 @@
         <v>0.1242</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0318</v>
+        <v>-0.0597</v>
       </c>
       <c r="E19" t="n">
         <v>0.9643</v>
@@ -1330,7 +1330,7 @@
         <v>0.1061</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0885</v>
+        <v>-0.1156</v>
       </c>
       <c r="E20" t="n">
         <v>0.824</v>
@@ -1376,7 +1376,7 @@
         <v>0.1052</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0914</v>
+        <v>-0.1185</v>
       </c>
       <c r="E21" t="n">
         <v>0.8168</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7135</v>
+        <v>0.7366</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0919</v>
+        <v>0.0949</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1331</v>
+        <v>-0.1504</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7135</v>
+        <v>0.7366</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7135</v>
+        <v>0.7366</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7135</v>
+        <v>0.7366</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7135</v>
+        <v>0.7366</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7135</v>
+        <v>0.7366</v>
       </c>
       <c r="N22" t="n">
         <v>83</v>
@@ -1468,7 +1468,7 @@
         <v>0.06270000000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2246</v>
+        <v>-0.2498</v>
       </c>
       <c r="E23" t="n">
         <v>0.4871</v>
@@ -1514,7 +1514,7 @@
         <v>0.048</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2706</v>
+        <v>-0.2953</v>
       </c>
       <c r="E24" t="n">
         <v>0.3731</v>
@@ -1550,32 +1550,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Bwills</t>
+          <t>MarKE</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.135</v>
+        <v>0.1542</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0174</v>
+        <v>0.0199</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3668</v>
+        <v>-0.3825</v>
       </c>
       <c r="E25" t="n">
-        <v>0.135</v>
+        <v>0.1542</v>
       </c>
       <c r="F25" t="n">
-        <v>0.135</v>
+        <v>0.1542</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.135</v>
+        <v>0.1542</v>
       </c>
       <c r="I25" t="n">
-        <v>0.135</v>
+        <v>0.1542</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.135</v>
+        <v>0.1542</v>
       </c>
       <c r="N25" t="n">
         <v>83</v>
@@ -1596,139 +1596,139 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>hAdji</t>
+          <t>Bwills</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0399</v>
+        <v>0.135</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0051</v>
+        <v>0.0174</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4052</v>
+        <v>-0.3901</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0399</v>
+        <v>0.135</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0399</v>
+        <v>0.135</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0399</v>
+        <v>0.135</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0399</v>
+        <v>0.135</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0399</v>
+        <v>0.135</v>
       </c>
       <c r="N26" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>hAdji</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0507</v>
+        <v>0.0399</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0065</v>
+        <v>0.0051</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4418</v>
+        <v>-0.428</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0507</v>
+        <v>0.0399</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0507</v>
+        <v>0.0399</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.0507</v>
+        <v>0.0399</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0507</v>
+        <v>0.0399</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0507</v>
+        <v>0.0399</v>
       </c>
       <c r="N27" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MarKE</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1342</v>
+        <v>-0.0507</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0173</v>
+        <v>-0.0065</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4756</v>
+        <v>-0.4641</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1342</v>
+        <v>-0.0507</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1342</v>
+        <v>-0.0507</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.1342</v>
+        <v>-0.0507</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1342</v>
+        <v>-0.0507</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1342</v>
+        <v>-0.0507</v>
       </c>
       <c r="N28" t="n">
-        <v>83</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29">
@@ -1744,7 +1744,7 @@
         <v>-0.0596</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6084000000000001</v>
+        <v>-0.6284</v>
       </c>
       <c r="E29" t="n">
         <v>-0.463</v>
@@ -1790,7 +1790,7 @@
         <v>-0.0684</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6359</v>
+        <v>-0.6555</v>
       </c>
       <c r="E30" t="n">
         <v>-0.5311</v>
@@ -1836,7 +1836,7 @@
         <v>-0.0794</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6706</v>
+        <v>-0.6897</v>
       </c>
       <c r="E31" t="n">
         <v>-0.6169</v>
@@ -1882,7 +1882,7 @@
         <v>-0.0796</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6712</v>
+        <v>-0.6903</v>
       </c>
       <c r="E32" t="n">
         <v>-0.6185</v>
@@ -1928,7 +1928,7 @@
         <v>-0.0867</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6933</v>
+        <v>-0.7121</v>
       </c>
       <c r="E33" t="n">
         <v>-0.6731</v>
@@ -1974,7 +1974,7 @@
         <v>-0.1126</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7747000000000001</v>
+        <v>-0.7924</v>
       </c>
       <c r="E34" t="n">
         <v>-0.8746</v>
@@ -2020,7 +2020,7 @@
         <v>-0.1149</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7819</v>
+        <v>-0.7995</v>
       </c>
       <c r="E35" t="n">
         <v>-0.8925</v>
@@ -2066,7 +2066,7 @@
         <v>-0.1621</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.9454</v>
       </c>
       <c r="E36" t="n">
         <v>-1.2588</v>
@@ -2112,7 +2112,7 @@
         <v>-0.1764</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9746</v>
+        <v>-0.9895</v>
       </c>
       <c r="E37" t="n">
         <v>-1.3695</v>
@@ -2158,7 +2158,7 @@
         <v>-0.2064</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0689</v>
+        <v>-1.0825</v>
       </c>
       <c r="E38" t="n">
         <v>-1.6029</v>
@@ -2204,7 +2204,7 @@
         <v>-0.2537</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2174</v>
+        <v>-1.229</v>
       </c>
       <c r="E39" t="n">
         <v>-1.9705</v>
@@ -2250,7 +2250,7 @@
         <v>-0.261</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2401</v>
+        <v>-1.2513</v>
       </c>
       <c r="E40" t="n">
         <v>-2.0267</v>
@@ -2296,7 +2296,7 @@
         <v>-0.2666</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2578</v>
+        <v>-1.2688</v>
       </c>
       <c r="E41" t="n">
         <v>-2.0705</v>

--- a/database/event/6868/event_6868_evp_summary.xlsx
+++ b/database/event/6868/event_6868_evp_summary.xlsx
@@ -492,93 +492,93 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sdy</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.2484</v>
+        <v>5.9416</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8046</v>
+        <v>0.7651</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0455</v>
+        <v>2.0443</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2484</v>
+        <v>5.9416</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0444</v>
+        <v>3.8694</v>
       </c>
       <c r="G2" t="n">
-        <v>3.204</v>
+        <v>2.0722</v>
       </c>
       <c r="H2" t="n">
-        <v>3.0444</v>
+        <v>8.1469</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4676</v>
+        <v>4.236</v>
       </c>
       <c r="J2" t="n">
-        <v>3.204</v>
+        <v>2.0722</v>
       </c>
       <c r="K2" t="n">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="L2" t="n">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="M2" t="n">
-        <v>5.6716</v>
+        <v>6.308199999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>160</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>sdy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.152</v>
+        <v>5.6018</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7922</v>
+        <v>0.7214</v>
       </c>
       <c r="D3" t="n">
-        <v>2.007</v>
+        <v>1.8909</v>
       </c>
       <c r="E3" t="n">
-        <v>6.152</v>
+        <v>5.6018</v>
       </c>
       <c r="F3" t="n">
-        <v>4.3233</v>
+        <v>2.8067</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8287</v>
+        <v>2.7951</v>
       </c>
       <c r="H3" t="n">
-        <v>4.8333</v>
+        <v>4.4026</v>
       </c>
       <c r="I3" t="n">
-        <v>3.9175</v>
+        <v>2.2892</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8287</v>
+        <v>2.7951</v>
       </c>
       <c r="K3" t="n">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="L3" t="n">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="M3" t="n">
-        <v>5.7462</v>
+        <v>5.084300000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>252</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4">
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.8504</v>
+        <v>4.4794</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6246</v>
+        <v>0.5768</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4885</v>
+        <v>1.3842</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8504</v>
+        <v>4.4794</v>
       </c>
       <c r="F4" t="n">
-        <v>4.2604</v>
+        <v>3.7444</v>
       </c>
       <c r="G4" t="n">
-        <v>0.59</v>
+        <v>0.735</v>
       </c>
       <c r="H4" t="n">
-        <v>4.58</v>
+        <v>7.7066</v>
       </c>
       <c r="I4" t="n">
-        <v>3.7122</v>
+        <v>4.0071</v>
       </c>
       <c r="J4" t="n">
-        <v>0.59</v>
+        <v>0.735</v>
       </c>
       <c r="K4" t="n">
         <v>101</v>
@@ -621,7 +621,7 @@
         <v>151</v>
       </c>
       <c r="M4" t="n">
-        <v>4.3022</v>
+        <v>4.742100000000001</v>
       </c>
       <c r="N4" t="n">
         <v>252</v>
@@ -630,219 +630,219 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Calyx</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.2913</v>
+        <v>3.5145</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4238</v>
+        <v>0.4526</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8673</v>
+        <v>0.9486</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2913</v>
+        <v>3.5145</v>
       </c>
       <c r="F5" t="n">
-        <v>3.373</v>
+        <v>2.5566</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.08169999999999999</v>
+        <v>0.9579</v>
       </c>
       <c r="H5" t="n">
-        <v>3.373</v>
+        <v>3.5215</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7339</v>
+        <v>1.831</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.08169999999999999</v>
+        <v>0.9579</v>
       </c>
       <c r="K5" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="L5" t="n">
-        <v>151</v>
+        <v>63</v>
       </c>
       <c r="M5" t="n">
-        <v>2.6522</v>
+        <v>2.7889</v>
       </c>
       <c r="N5" t="n">
-        <v>252</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>br0</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.0154</v>
+        <v>3.4533</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3883</v>
+        <v>0.4447</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7574</v>
+        <v>0.921</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0154</v>
+        <v>3.4533</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0342</v>
+        <v>1.5201</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9812</v>
+        <v>1.9332</v>
       </c>
       <c r="H6" t="n">
-        <v>2.0342</v>
+        <v>1.5201</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6488</v>
+        <v>0.7904</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9812</v>
+        <v>1.9332</v>
       </c>
       <c r="K6" t="n">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="L6" t="n">
-        <v>63</v>
+        <v>121</v>
       </c>
       <c r="M6" t="n">
-        <v>2.63</v>
+        <v>2.7236</v>
       </c>
       <c r="N6" t="n">
-        <v>175</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>insani</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.8933</v>
+        <v>3.3088</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3726</v>
+        <v>0.4261</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7088</v>
+        <v>0.8557</v>
       </c>
       <c r="E7" t="n">
-        <v>2.8933</v>
+        <v>3.3088</v>
       </c>
       <c r="F7" t="n">
-        <v>3.1693</v>
+        <v>2.7595</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.276</v>
+        <v>0.5493</v>
       </c>
       <c r="H7" t="n">
-        <v>3.1693</v>
+        <v>4.2363</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5688</v>
+        <v>2.2027</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.276</v>
+        <v>0.5493</v>
       </c>
       <c r="K7" t="n">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="L7" t="n">
-        <v>93</v>
+        <v>151</v>
       </c>
       <c r="M7" t="n">
-        <v>2.2928</v>
+        <v>2.752</v>
       </c>
       <c r="N7" t="n">
-        <v>162</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>kRaSnaL</t>
+          <t>Calyx</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.8792</v>
+        <v>3.2911</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3708</v>
+        <v>0.4238</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7032</v>
+        <v>0.8478</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8792</v>
+        <v>3.2911</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3592</v>
+        <v>3.3392</v>
       </c>
       <c r="G8" t="n">
-        <v>0.52</v>
+        <v>-0.0481</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3592</v>
+        <v>6.279</v>
       </c>
       <c r="I8" t="n">
-        <v>1.9122</v>
+        <v>3.2648</v>
       </c>
       <c r="J8" t="n">
-        <v>0.52</v>
+        <v>-0.0481</v>
       </c>
       <c r="K8" t="n">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="L8" t="n">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="M8" t="n">
-        <v>2.4322</v>
+        <v>3.2167</v>
       </c>
       <c r="N8" t="n">
-        <v>160</v>
+        <v>252</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>br0</t>
+          <t>kRaSnaL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.8344</v>
+        <v>2.9944</v>
       </c>
       <c r="C9" t="n">
-        <v>0.365</v>
+        <v>0.3856</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6853</v>
+        <v>0.7138</v>
       </c>
       <c r="E9" t="n">
-        <v>2.8344</v>
+        <v>2.9944</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7668</v>
+        <v>2.5334</v>
       </c>
       <c r="G9" t="n">
-        <v>2.0676</v>
+        <v>0.461</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7668</v>
+        <v>3.4399</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6215000000000001</v>
+        <v>1.7886</v>
       </c>
       <c r="J9" t="n">
-        <v>2.0676</v>
+        <v>0.461</v>
       </c>
       <c r="K9" t="n">
         <v>39</v>
@@ -851,7 +851,7 @@
         <v>121</v>
       </c>
       <c r="M9" t="n">
-        <v>2.6891</v>
+        <v>2.2496</v>
       </c>
       <c r="N9" t="n">
         <v>160</v>
@@ -860,173 +860,173 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>insani</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.7961</v>
+        <v>2.7269</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3601</v>
+        <v>0.3511</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6701</v>
+        <v>0.593</v>
       </c>
       <c r="E10" t="n">
-        <v>2.7961</v>
+        <v>2.7269</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2933</v>
+        <v>2.8215</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5028</v>
+        <v>-0.0946</v>
       </c>
       <c r="H10" t="n">
-        <v>2.2933</v>
+        <v>4.4548</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8588</v>
+        <v>2.3163</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5028</v>
+        <v>-0.0946</v>
       </c>
       <c r="K10" t="n">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="L10" t="n">
-        <v>151</v>
+        <v>93</v>
       </c>
       <c r="M10" t="n">
-        <v>2.3616</v>
+        <v>2.2217</v>
       </c>
       <c r="N10" t="n">
-        <v>252</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DemQQ</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.1793</v>
+        <v>2.483</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2806</v>
+        <v>0.3197</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4243</v>
+        <v>0.4829</v>
       </c>
       <c r="E11" t="n">
-        <v>2.1793</v>
+        <v>2.483</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2765</v>
+        <v>1.3192</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.09719999999999999</v>
+        <v>1.1638</v>
       </c>
       <c r="H11" t="n">
-        <v>2.2765</v>
+        <v>1.3192</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8452</v>
+        <v>0.6859</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.09719999999999999</v>
+        <v>1.1638</v>
       </c>
       <c r="K11" t="n">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c r="L11" t="n">
-        <v>121</v>
+        <v>63</v>
       </c>
       <c r="M11" t="n">
-        <v>1.748</v>
+        <v>1.8497</v>
       </c>
       <c r="N11" t="n">
-        <v>160</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>volt</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.161</v>
+        <v>2.4811</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2783</v>
+        <v>0.3195</v>
       </c>
       <c r="D12" t="n">
-        <v>0.417</v>
+        <v>0.4821</v>
       </c>
       <c r="E12" t="n">
-        <v>2.161</v>
+        <v>2.4811</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7035</v>
+        <v>2.4811</v>
       </c>
       <c r="G12" t="n">
-        <v>1.4575</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7035</v>
+        <v>2.4811</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5702</v>
+        <v>2.4811</v>
       </c>
       <c r="J12" t="n">
-        <v>1.4575</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="L12" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.0277</v>
+        <v>2.4811</v>
       </c>
       <c r="N12" t="n">
-        <v>175</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9149</v>
+        <v>2.4062</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2466</v>
+        <v>0.3099</v>
       </c>
       <c r="D13" t="n">
-        <v>0.319</v>
+        <v>0.4483</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9149</v>
+        <v>2.4062</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6515</v>
+        <v>2.8106</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.7366</v>
+        <v>-0.4044</v>
       </c>
       <c r="H13" t="n">
-        <v>2.6515</v>
+        <v>4.4165</v>
       </c>
       <c r="I13" t="n">
-        <v>2.1491</v>
+        <v>2.2964</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.7366</v>
+        <v>-0.4044</v>
       </c>
       <c r="K13" t="n">
         <v>112</v>
@@ -1035,7 +1035,7 @@
         <v>63</v>
       </c>
       <c r="M13" t="n">
-        <v>1.4125</v>
+        <v>1.892</v>
       </c>
       <c r="N13" t="n">
         <v>175</v>
@@ -1044,93 +1044,93 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>DemQQ</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.8867</v>
+        <v>2.3942</v>
       </c>
       <c r="C14" t="n">
-        <v>0.243</v>
+        <v>0.3083</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3078</v>
+        <v>0.4428</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8867</v>
+        <v>2.3942</v>
       </c>
       <c r="F14" t="n">
-        <v>2.656</v>
+        <v>2.5951</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.7693</v>
+        <v>-0.2009</v>
       </c>
       <c r="H14" t="n">
-        <v>2.656</v>
+        <v>3.6572</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1528</v>
+        <v>1.9016</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.7693</v>
+        <v>-0.2009</v>
       </c>
       <c r="K14" t="n">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="L14" t="n">
-        <v>63</v>
+        <v>121</v>
       </c>
       <c r="M14" t="n">
-        <v>1.3835</v>
+        <v>1.7007</v>
       </c>
       <c r="N14" t="n">
-        <v>175</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Djoko</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.7884</v>
+        <v>2.3383</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2303</v>
+        <v>0.3011</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2686</v>
+        <v>0.4176</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7884</v>
+        <v>2.3383</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7884</v>
+        <v>2.7673</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0.429</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7884</v>
+        <v>4.264</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7884</v>
+        <v>2.2171</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0.429</v>
       </c>
       <c r="K15" t="n">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M15" t="n">
-        <v>1.7884</v>
+        <v>1.7881</v>
       </c>
       <c r="N15" t="n">
-        <v>85</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16">
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.6528</v>
+        <v>1.8571</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2128</v>
+        <v>0.2391</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2146</v>
+        <v>0.2004</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6528</v>
+        <v>1.8571</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5311</v>
+        <v>0.9526</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1217</v>
+        <v>0.9045</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5311</v>
+        <v>0.9526</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4305</v>
+        <v>0.4953</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1217</v>
+        <v>0.9045</v>
       </c>
       <c r="K16" t="n">
         <v>69</v>
@@ -1173,7 +1173,7 @@
         <v>93</v>
       </c>
       <c r="M16" t="n">
-        <v>1.5522</v>
+        <v>1.3998</v>
       </c>
       <c r="N16" t="n">
         <v>162</v>
@@ -1182,231 +1182,231 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>volt</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.6244</v>
+        <v>1.8564</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2092</v>
+        <v>0.2391</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2033</v>
+        <v>0.2001</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6244</v>
+        <v>1.8564</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6244</v>
+        <v>1.3811</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.4753</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6244</v>
+        <v>1.3811</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6244</v>
+        <v>0.7181</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.4753</v>
       </c>
       <c r="K17" t="n">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M17" t="n">
-        <v>1.6244</v>
+        <v>1.1934</v>
       </c>
       <c r="N17" t="n">
-        <v>128</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>Djoko</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.2192</v>
+        <v>1.8212</v>
       </c>
       <c r="C18" t="n">
-        <v>0.157</v>
+        <v>0.2345</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0418</v>
+        <v>0.1842</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2192</v>
+        <v>1.8212</v>
       </c>
       <c r="F18" t="n">
-        <v>0.39</v>
+        <v>1.8212</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8292</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.39</v>
+        <v>1.8212</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3161</v>
+        <v>1.8212</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8292</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="L18" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1453</v>
+        <v>1.8212</v>
       </c>
       <c r="N18" t="n">
-        <v>162</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>exit</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9643</v>
+        <v>1.5138</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1242</v>
+        <v>0.1949</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0597</v>
+        <v>0.0454</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9643</v>
+        <v>1.5138</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4846</v>
+        <v>0.8268</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4797</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4846</v>
+        <v>0.8268</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3928</v>
+        <v>0.4299</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4797</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="L19" t="n">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8725000000000001</v>
+        <v>1.1169</v>
       </c>
       <c r="N19" t="n">
-        <v>175</v>
+        <v>162</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ex3rcice</t>
+          <t>acoR</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.824</v>
+        <v>1.2347</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1061</v>
+        <v>0.159</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1156</v>
+        <v>-0.0806</v>
       </c>
       <c r="E20" t="n">
-        <v>0.824</v>
+        <v>1.2347</v>
       </c>
       <c r="F20" t="n">
-        <v>0.824</v>
+        <v>1.2347</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.824</v>
+        <v>1.2347</v>
       </c>
       <c r="I20" t="n">
-        <v>0.824</v>
+        <v>1.2347</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.824</v>
+        <v>1.2347</v>
       </c>
       <c r="N20" t="n">
-        <v>85</v>
+        <v>128</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>acoR</t>
+          <t>Ex3rcice</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8168</v>
+        <v>1.0101</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1052</v>
+        <v>0.1301</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1185</v>
+        <v>-0.182</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8168</v>
+        <v>1.0101</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8168</v>
+        <v>1.0101</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8168</v>
+        <v>1.0101</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8168</v>
+        <v>1.0101</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>128</v>
+        <v>85</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8168</v>
+        <v>1.0101</v>
       </c>
       <c r="N21" t="n">
-        <v>128</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7366</v>
+        <v>0.8424</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0949</v>
+        <v>0.1085</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1504</v>
+        <v>-0.2577</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7366</v>
+        <v>0.8424</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7366</v>
+        <v>0.8424</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7366</v>
+        <v>0.8424</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7366</v>
+        <v>0.8424</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7366</v>
+        <v>0.8424</v>
       </c>
       <c r="N22" t="n">
         <v>83</v>
@@ -1458,93 +1458,93 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4871</v>
+        <v>0.704</v>
       </c>
       <c r="C23" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.0907</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2498</v>
+        <v>-0.3202</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4871</v>
+        <v>0.704</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4871</v>
+        <v>0.704</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4871</v>
+        <v>0.704</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4871</v>
+        <v>0.704</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4871</v>
+        <v>0.704</v>
       </c>
       <c r="N23" t="n">
-        <v>85</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3731</v>
+        <v>0.6587</v>
       </c>
       <c r="C24" t="n">
-        <v>0.048</v>
+        <v>0.0848</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2953</v>
+        <v>-0.3406</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3731</v>
+        <v>0.6587</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3731</v>
+        <v>0.6587</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3731</v>
+        <v>0.6587</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3731</v>
+        <v>0.6587</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>128</v>
+        <v>85</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3731</v>
+        <v>0.6587</v>
       </c>
       <c r="N24" t="n">
-        <v>128</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1542</v>
+        <v>0.4303</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0199</v>
+        <v>0.0554</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3825</v>
+        <v>-0.4438</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1542</v>
+        <v>0.4303</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1542</v>
+        <v>0.4303</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1542</v>
+        <v>0.4303</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1542</v>
+        <v>0.4303</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1542</v>
+        <v>0.4303</v>
       </c>
       <c r="N25" t="n">
         <v>83</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.135</v>
+        <v>0.4148</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0174</v>
+        <v>0.0534</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3901</v>
+        <v>-0.4508</v>
       </c>
       <c r="E26" t="n">
-        <v>0.135</v>
+        <v>0.4148</v>
       </c>
       <c r="F26" t="n">
-        <v>0.135</v>
+        <v>0.4148</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.135</v>
+        <v>0.4148</v>
       </c>
       <c r="I26" t="n">
-        <v>0.135</v>
+        <v>0.4148</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.135</v>
+        <v>0.4148</v>
       </c>
       <c r="N26" t="n">
         <v>83</v>
@@ -1642,415 +1642,415 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>hAdji</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0399</v>
+        <v>0.322</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0051</v>
+        <v>0.0415</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.428</v>
+        <v>-0.4926</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0399</v>
+        <v>0.322</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0399</v>
+        <v>0.2219</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.1001</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0399</v>
+        <v>0.2219</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0399</v>
+        <v>0.1154</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.1001</v>
       </c>
       <c r="K27" t="n">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0399</v>
+        <v>0.2155</v>
       </c>
       <c r="N27" t="n">
-        <v>85</v>
+        <v>252</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>hAdji</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0507</v>
+        <v>0.2731</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0065</v>
+        <v>0.0352</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4641</v>
+        <v>-0.5147</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0507</v>
+        <v>0.2731</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0507</v>
+        <v>0.2731</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.0507</v>
+        <v>0.2731</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0507</v>
+        <v>0.2731</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.0507</v>
+        <v>0.2731</v>
       </c>
       <c r="N28" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.463</v>
+        <v>0.2518</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0596</v>
+        <v>0.0324</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6284</v>
+        <v>-0.5243</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.463</v>
+        <v>0.2518</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.3858</v>
+        <v>0.2518</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.0772</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.3858</v>
+        <v>0.2518</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3127</v>
+        <v>0.2518</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.0772</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="L29" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.3899</v>
+        <v>0.2518</v>
       </c>
       <c r="N29" t="n">
-        <v>252</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kaze</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.5311</v>
+        <v>-0.0126</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0684</v>
+        <v>-0.0016</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6555</v>
+        <v>-0.6437</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.5311</v>
+        <v>-0.0126</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.5311</v>
+        <v>0.6241</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.6367</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.5311</v>
+        <v>0.6241</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.5311</v>
+        <v>0.3245</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.6367</v>
       </c>
       <c r="K30" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.5311</v>
+        <v>-0.3122</v>
       </c>
       <c r="N30" t="n">
-        <v>57</v>
+        <v>162</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Moseyuh</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.6169</v>
+        <v>-0.4104</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0794</v>
+        <v>-0.0528</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6897</v>
+        <v>-0.8233</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.6169</v>
+        <v>-0.4104</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.6169</v>
+        <v>-0.4104</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.6169</v>
+        <v>-0.4104</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6169</v>
+        <v>-0.4104</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.6169</v>
+        <v>-0.4104</v>
       </c>
       <c r="N31" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>kaze</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.6185</v>
+        <v>-0.4363</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0796</v>
+        <v>-0.0562</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6903</v>
+        <v>-0.835</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6185</v>
+        <v>-0.4363</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.6752</v>
+        <v>-0.4363</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0567</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.6752</v>
+        <v>-0.4363</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5473</v>
+        <v>-0.4363</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0567</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="L32" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4906</v>
+        <v>-0.4363</v>
       </c>
       <c r="N32" t="n">
-        <v>162</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>Moseyuh</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6731</v>
+        <v>-0.4694</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0867</v>
+        <v>-0.0604</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7121</v>
+        <v>-0.8499</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6731</v>
+        <v>-0.4694</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3269</v>
+        <v>-0.4694</v>
       </c>
       <c r="G33" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.3269</v>
+        <v>-0.4694</v>
       </c>
       <c r="I33" t="n">
-        <v>0.265</v>
+        <v>-0.4694</v>
       </c>
       <c r="J33" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="L33" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.735</v>
+        <v>-0.4694</v>
       </c>
       <c r="N33" t="n">
-        <v>162</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cJ dA K1nG</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.8746</v>
+        <v>-0.495</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1126</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7924</v>
+        <v>-0.8615</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.8746</v>
+        <v>-0.495</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.8746</v>
+        <v>-0.7724</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.2774</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.8746</v>
+        <v>-0.7724</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.8746</v>
+        <v>-0.4016</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>0.2774</v>
       </c>
       <c r="K34" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.8746</v>
+        <v>-0.1242</v>
       </c>
       <c r="N34" t="n">
-        <v>83</v>
+        <v>162</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>cJ dA K1nG</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.8925</v>
+        <v>-0.659</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1149</v>
+        <v>-0.0849</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7995</v>
+        <v>-0.9355</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.8925</v>
+        <v>-0.659</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.8925</v>
+        <v>-0.659</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.8925</v>
+        <v>-0.659</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.8925</v>
+        <v>-0.659</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.8925</v>
+        <v>-0.659</v>
       </c>
       <c r="N35" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.2588</v>
+        <v>-0.8694</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1621</v>
+        <v>-0.112</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9454</v>
+        <v>-1.0305</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.2588</v>
+        <v>-0.8694</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.2588</v>
+        <v>-0.8694</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.2588</v>
+        <v>-0.8694</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.2588</v>
+        <v>-0.8694</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.2588</v>
+        <v>-0.8694</v>
       </c>
       <c r="N36" t="n">
         <v>57</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.3695</v>
+        <v>-1.1653</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1764</v>
+        <v>-0.1501</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9895</v>
+        <v>-1.1641</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.3695</v>
+        <v>-1.1653</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.3469</v>
+        <v>-0.2612</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.0226</v>
+        <v>-0.9041</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.3469</v>
+        <v>-0.2612</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.2812</v>
+        <v>-0.1358</v>
       </c>
       <c r="J37" t="n">
-        <v>-1.0226</v>
+        <v>-0.9041</v>
       </c>
       <c r="K37" t="n">
         <v>39</v>
@@ -2139,7 +2139,7 @@
         <v>121</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.3038</v>
+        <v>-1.0399</v>
       </c>
       <c r="N37" t="n">
         <v>160</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.6029</v>
+        <v>-1.2718</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2064</v>
+        <v>-0.1638</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0825</v>
+        <v>-1.2122</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.6029</v>
+        <v>-1.2718</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.6029</v>
+        <v>-1.2718</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.6029</v>
+        <v>-1.2718</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.6029</v>
+        <v>-1.2718</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.6029</v>
+        <v>-1.2718</v>
       </c>
       <c r="N38" t="n">
         <v>57</v>
@@ -2194,78 +2194,78 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>nosraC</t>
+          <t>Keoz</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.9705</v>
+        <v>-1.4383</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2537</v>
+        <v>-0.1852</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.229</v>
+        <v>-1.2873</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.9705</v>
+        <v>-1.4383</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.9705</v>
+        <v>-1.4383</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.9705</v>
+        <v>-1.4383</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.9705</v>
+        <v>-1.4383</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>83</v>
+        <v>128</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.9705</v>
+        <v>-1.4383</v>
       </c>
       <c r="N39" t="n">
-        <v>83</v>
+        <v>128</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Keoz</t>
+          <t>isak</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.0267</v>
+        <v>-1.5439</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.261</v>
+        <v>-0.1988</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2513</v>
+        <v>-1.335</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.0267</v>
+        <v>-1.5439</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.0267</v>
+        <v>-1.5439</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.0267</v>
+        <v>-1.5439</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.0267</v>
+        <v>-1.5439</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.0267</v>
+        <v>-1.5439</v>
       </c>
       <c r="N40" t="n">
         <v>128</v>
@@ -2286,47 +2286,47 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>isak</t>
+          <t>nosraC</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.0705</v>
+        <v>-1.5549</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.2666</v>
+        <v>-0.2002</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2688</v>
+        <v>-1.34</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.0705</v>
+        <v>-1.5549</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.0705</v>
+        <v>-1.5549</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.0705</v>
+        <v>-1.5549</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.0705</v>
+        <v>-1.5549</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>128</v>
+        <v>83</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.0705</v>
+        <v>-1.5549</v>
       </c>
       <c r="N41" t="n">
-        <v>128</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -2429,10 +2429,10 @@
         <v>1.34</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9208</v>
+        <v>0.9082</v>
       </c>
       <c r="J2" t="n">
-        <v>21.1784</v>
+        <v>20.8886</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.34</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9208</v>
+        <v>0.9082</v>
       </c>
       <c r="J3" t="n">
-        <v>21.1784</v>
+        <v>20.8886</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.03</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0454</v>
+        <v>0.1015</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0442</v>
+        <v>2.3345</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.98</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1971</v>
+        <v>-0.1272</v>
       </c>
       <c r="J5" t="n">
-        <v>-4.5333</v>
+        <v>-2.9256</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.97</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2351</v>
+        <v>-0.1644</v>
       </c>
       <c r="J6" t="n">
-        <v>-5.4073</v>
+        <v>-3.7812</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.29</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4952</v>
+        <v>0.5869</v>
       </c>
       <c r="J7" t="n">
-        <v>11.3896</v>
+        <v>13.4987</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.18</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3417</v>
+        <v>0.3913</v>
       </c>
       <c r="J8" t="n">
-        <v>7.8591</v>
+        <v>8.9999</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.03</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0653</v>
+        <v>0.0872</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5019</v>
+        <v>2.0056</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.84</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3332</v>
+        <v>-0.2025</v>
       </c>
       <c r="J10" t="n">
-        <v>-7.6636</v>
+        <v>-4.6575</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.84</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3332</v>
+        <v>-0.2025</v>
       </c>
       <c r="J11" t="n">
-        <v>-7.6636</v>
+        <v>-4.6575</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.81</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8335</v>
+        <v>1.5521</v>
       </c>
       <c r="J12" t="n">
-        <v>64.1725</v>
+        <v>54.3235</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.08</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2125</v>
+        <v>0.2603</v>
       </c>
       <c r="J13" t="n">
-        <v>7.4375</v>
+        <v>9.1105</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.95</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3047</v>
+        <v>-0.2333</v>
       </c>
       <c r="J14" t="n">
-        <v>-10.6645</v>
+        <v>-8.1655</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.95</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3047</v>
+        <v>-0.2333</v>
       </c>
       <c r="J15" t="n">
-        <v>-10.6645</v>
+        <v>-8.1655</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.88</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5099</v>
+        <v>-0.4436</v>
       </c>
       <c r="J16" t="n">
-        <v>-17.8465</v>
+        <v>-15.526</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.5</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7442</v>
+        <v>0.9246</v>
       </c>
       <c r="J17" t="n">
-        <v>26.047</v>
+        <v>32.361</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.45</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6861</v>
+        <v>0.845</v>
       </c>
       <c r="J18" t="n">
-        <v>24.0135</v>
+        <v>29.575</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.87</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2929</v>
+        <v>-0.1736</v>
       </c>
       <c r="J19" t="n">
-        <v>-10.2515</v>
+        <v>-6.076</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.8</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3964</v>
+        <v>-0.2458</v>
       </c>
       <c r="J20" t="n">
-        <v>-13.874</v>
+        <v>-8.603</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.68</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5558</v>
+        <v>-0.3615</v>
       </c>
       <c r="J21" t="n">
-        <v>-19.453</v>
+        <v>-12.6525</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.36</v>
       </c>
       <c r="I22" t="n">
-        <v>0.981</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>28.449</v>
+        <v>20.5088</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.12</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3805</v>
+        <v>0.3589</v>
       </c>
       <c r="J23" t="n">
-        <v>11.0345</v>
+        <v>10.4081</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.09</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2699</v>
+        <v>0.2955</v>
       </c>
       <c r="J24" t="n">
-        <v>7.8271</v>
+        <v>8.5695</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.06</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1684</v>
+        <v>0.2076</v>
       </c>
       <c r="J25" t="n">
-        <v>4.8836</v>
+        <v>6.0204</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.88</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4987</v>
+        <v>-0.4349</v>
       </c>
       <c r="J26" t="n">
-        <v>-14.4623</v>
+        <v>-12.6121</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.14</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2985</v>
+        <v>0.3272</v>
       </c>
       <c r="J27" t="n">
-        <v>8.656499999999999</v>
+        <v>9.488799999999999</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.09</v>
       </c>
       <c r="I28" t="n">
-        <v>0.216</v>
+        <v>0.2293</v>
       </c>
       <c r="J28" t="n">
-        <v>6.264</v>
+        <v>6.6497</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.02</v>
       </c>
       <c r="I29" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.0684</v>
       </c>
       <c r="J29" t="n">
-        <v>2.1866</v>
+        <v>1.9836</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.87</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2734</v>
+        <v>-0.1653</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.9286</v>
+        <v>-4.7937</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3657</v>
+        <v>-0.2273</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.6053</v>
+        <v>-6.5917</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.29</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4945</v>
+        <v>0.4015</v>
       </c>
       <c r="J32" t="n">
-        <v>11.3735</v>
+        <v>9.234500000000001</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.08</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1765</v>
+        <v>0.1508</v>
       </c>
       <c r="J33" t="n">
-        <v>4.0595</v>
+        <v>3.4684</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>0.092</v>
+        <v>0.0844</v>
       </c>
       <c r="J34" t="n">
-        <v>2.116</v>
+        <v>1.9412</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.03</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0639</v>
+        <v>0.0665</v>
       </c>
       <c r="J35" t="n">
-        <v>1.4697</v>
+        <v>1.5295</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.75</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.461</v>
+        <v>-0.2926</v>
       </c>
       <c r="J36" t="n">
-        <v>-10.603</v>
+        <v>-6.7298</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.83</v>
       </c>
       <c r="I37" t="n">
-        <v>1.0783</v>
+        <v>0.7266</v>
       </c>
       <c r="J37" t="n">
-        <v>24.8009</v>
+        <v>16.7118</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.39</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5954</v>
+        <v>0.4421</v>
       </c>
       <c r="J38" t="n">
-        <v>13.6942</v>
+        <v>10.1683</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.11</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1836</v>
+        <v>0.1746</v>
       </c>
       <c r="J39" t="n">
-        <v>4.2228</v>
+        <v>4.0158</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.72</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5137</v>
+        <v>-0.3298</v>
       </c>
       <c r="J40" t="n">
-        <v>-11.8151</v>
+        <v>-7.5854</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.55</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.719</v>
+        <v>-0.4852</v>
       </c>
       <c r="J41" t="n">
-        <v>-16.537</v>
+        <v>-11.1596</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.42</v>
       </c>
       <c r="I42" t="n">
-        <v>1.1295</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
-        <v>46.3095</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.3</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8685</v>
+        <v>0.6334</v>
       </c>
       <c r="J43" t="n">
-        <v>35.6085</v>
+        <v>25.9694</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.06</v>
       </c>
       <c r="I44" t="n">
-        <v>0.203</v>
+        <v>0.2149</v>
       </c>
       <c r="J44" t="n">
-        <v>8.323</v>
+        <v>8.8109</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.78</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.7395</v>
+        <v>-0.6914</v>
       </c>
       <c r="J45" t="n">
-        <v>-30.3195</v>
+        <v>-28.3474</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.76</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.7869</v>
+        <v>-0.7423999999999999</v>
       </c>
       <c r="J46" t="n">
-        <v>-32.2629</v>
+        <v>-30.4384</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.34</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5597</v>
+        <v>0.5333</v>
       </c>
       <c r="J47" t="n">
-        <v>22.9477</v>
+        <v>21.8653</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.07</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1584</v>
+        <v>0.1765</v>
       </c>
       <c r="J48" t="n">
-        <v>6.4944</v>
+        <v>7.2365</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.95</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1485</v>
+        <v>-0.0796</v>
       </c>
       <c r="J49" t="n">
-        <v>-6.0885</v>
+        <v>-3.2636</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.93</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1862</v>
+        <v>-0.1039</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.6342</v>
+        <v>-4.2599</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.89</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2551</v>
+        <v>-0.1493</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.4591</v>
+        <v>-6.1213</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.49</v>
       </c>
       <c r="I52" t="n">
-        <v>1.2355</v>
+        <v>0.8723</v>
       </c>
       <c r="J52" t="n">
-        <v>25.9455</v>
+        <v>18.3183</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.39</v>
       </c>
       <c r="I53" t="n">
-        <v>1.0286</v>
+        <v>0.7398</v>
       </c>
       <c r="J53" t="n">
-        <v>21.6006</v>
+        <v>15.5358</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.18</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5309</v>
+        <v>0.4458</v>
       </c>
       <c r="J54" t="n">
-        <v>11.1489</v>
+        <v>9.361800000000001</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.87</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.5366</v>
+        <v>-0.4715</v>
       </c>
       <c r="J55" t="n">
-        <v>-11.2686</v>
+        <v>-9.9015</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.74</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.8522999999999999</v>
+        <v>-0.8109</v>
       </c>
       <c r="J56" t="n">
-        <v>-17.8983</v>
+        <v>-17.0289</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.42</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6774</v>
+        <v>0.6271</v>
       </c>
       <c r="J57" t="n">
-        <v>14.2254</v>
+        <v>13.1691</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.41</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6654</v>
+        <v>0.6172</v>
       </c>
       <c r="J58" t="n">
-        <v>13.9734</v>
+        <v>12.9612</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.79</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3928</v>
+        <v>-0.2464</v>
       </c>
       <c r="J59" t="n">
-        <v>-8.248799999999999</v>
+        <v>-5.1744</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.78</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4071</v>
+        <v>-0.2563</v>
       </c>
       <c r="J60" t="n">
-        <v>-8.549099999999999</v>
+        <v>-5.3823</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.49</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.7727000000000001</v>
+        <v>-0.5263</v>
       </c>
       <c r="J61" t="n">
-        <v>-16.2267</v>
+        <v>-11.0523</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.38</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6652</v>
+        <v>0.5056</v>
       </c>
       <c r="J62" t="n">
-        <v>12.6388</v>
+        <v>9.606400000000001</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.95</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.063</v>
+        <v>-0.0639</v>
       </c>
       <c r="J63" t="n">
-        <v>-1.197</v>
+        <v>-1.2141</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.91</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1413</v>
+        <v>-0.1115</v>
       </c>
       <c r="J64" t="n">
-        <v>-2.6847</v>
+        <v>-2.1185</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.65</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.5608</v>
+        <v>-0.3686</v>
       </c>
       <c r="J65" t="n">
-        <v>-10.6552</v>
+        <v>-7.0034</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.5</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.7478</v>
+        <v>-0.507</v>
       </c>
       <c r="J66" t="n">
-        <v>-14.2082</v>
+        <v>-9.632999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.67</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8568</v>
+        <v>0.5958</v>
       </c>
       <c r="J67" t="n">
-        <v>16.2792</v>
+        <v>11.3202</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.65</v>
       </c>
       <c r="I68" t="n">
-        <v>0.8355</v>
+        <v>0.5837</v>
       </c>
       <c r="J68" t="n">
-        <v>15.8745</v>
+        <v>11.0903</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.16</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1983</v>
+        <v>0.2191</v>
       </c>
       <c r="J69" t="n">
-        <v>3.7677</v>
+        <v>4.1629</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.12</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1384</v>
+        <v>0.1656</v>
       </c>
       <c r="J70" t="n">
-        <v>2.6296</v>
+        <v>3.1464</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.02</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.0366</v>
+        <v>0.0089</v>
       </c>
       <c r="J71" t="n">
-        <v>-0.6954</v>
+        <v>0.1691</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.76</v>
       </c>
       <c r="I72" t="n">
-        <v>1.7163</v>
+        <v>1.2043</v>
       </c>
       <c r="J72" t="n">
-        <v>39.4749</v>
+        <v>27.6989</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.19</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5341</v>
+        <v>0.4562</v>
       </c>
       <c r="J73" t="n">
-        <v>12.2843</v>
+        <v>10.4926</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.02</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0559</v>
       </c>
       <c r="J74" t="n">
-        <v>-0.2024</v>
+        <v>1.2857</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.01</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.0512</v>
+        <v>0.0149</v>
       </c>
       <c r="J75" t="n">
-        <v>-1.1776</v>
+        <v>0.3427</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.85</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5983000000000001</v>
+        <v>-0.5347</v>
       </c>
       <c r="J76" t="n">
-        <v>-13.7609</v>
+        <v>-12.2981</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.21</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4169</v>
+        <v>0.4179</v>
       </c>
       <c r="J77" t="n">
-        <v>9.588699999999999</v>
+        <v>9.611700000000001</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.06</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1774</v>
+        <v>0.1751</v>
       </c>
       <c r="J78" t="n">
-        <v>4.0802</v>
+        <v>4.0273</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.96</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.0767</v>
+        <v>-0.0591</v>
       </c>
       <c r="J79" t="n">
-        <v>-1.7641</v>
+        <v>-1.3593</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.85</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2929</v>
+        <v>-0.1816</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.7367</v>
+        <v>-4.1768</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.65</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5748</v>
+        <v>-0.3771</v>
       </c>
       <c r="J81" t="n">
-        <v>-13.2204</v>
+        <v>-8.673299999999999</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>0.82</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.236</v>
+        <v>-0.1902</v>
       </c>
       <c r="J82" t="n">
-        <v>-3.776</v>
+        <v>-3.0432</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.79</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.2866</v>
+        <v>-0.2204</v>
       </c>
       <c r="J83" t="n">
-        <v>-4.5856</v>
+        <v>-3.5264</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.75</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.3667</v>
+        <v>-0.2578</v>
       </c>
       <c r="J84" t="n">
-        <v>-5.8672</v>
+        <v>-4.1248</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.73</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.4031</v>
+        <v>-0.2762</v>
       </c>
       <c r="J85" t="n">
-        <v>-6.4496</v>
+        <v>-4.4192</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.467</v>
+        <v>-0.3137</v>
       </c>
       <c r="J86" t="n">
-        <v>-7.472</v>
+        <v>-5.0192</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.56</v>
       </c>
       <c r="I87" t="n">
-        <v>1.2319</v>
+        <v>1.1719</v>
       </c>
       <c r="J87" t="n">
-        <v>19.7104</v>
+        <v>18.7504</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.54</v>
       </c>
       <c r="I88" t="n">
-        <v>1.1915</v>
+        <v>1.1481</v>
       </c>
       <c r="J88" t="n">
-        <v>19.064</v>
+        <v>18.3696</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.53</v>
       </c>
       <c r="I89" t="n">
-        <v>1.171</v>
+        <v>1.1362</v>
       </c>
       <c r="J89" t="n">
-        <v>18.736</v>
+        <v>18.1792</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.35</v>
       </c>
       <c r="I90" t="n">
-        <v>0.7499</v>
+        <v>0.8611</v>
       </c>
       <c r="J90" t="n">
-        <v>11.9984</v>
+        <v>13.7776</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>1.17</v>
       </c>
       <c r="I91" t="n">
-        <v>0.3344</v>
+        <v>0.4382</v>
       </c>
       <c r="J91" t="n">
-        <v>5.3504</v>
+        <v>7.0112</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.04</v>
       </c>
       <c r="I92" t="n">
-        <v>0.184</v>
+        <v>0.167</v>
       </c>
       <c r="J92" t="n">
-        <v>4.048</v>
+        <v>3.674</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.9</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1364</v>
+        <v>-0.1166</v>
       </c>
       <c r="J93" t="n">
-        <v>-3.0008</v>
+        <v>-2.5652</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.8</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.3275</v>
+        <v>-0.2186</v>
       </c>
       <c r="J94" t="n">
-        <v>-7.205</v>
+        <v>-4.8092</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.73</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.4372</v>
+        <v>-0.2863</v>
       </c>
       <c r="J95" t="n">
-        <v>-9.618399999999999</v>
+        <v>-6.2986</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4946</v>
+        <v>-0.3246</v>
       </c>
       <c r="J96" t="n">
-        <v>-10.8812</v>
+        <v>-7.1412</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.57</v>
       </c>
       <c r="I97" t="n">
-        <v>1.3433</v>
+        <v>1.2216</v>
       </c>
       <c r="J97" t="n">
-        <v>29.5526</v>
+        <v>26.8752</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.22</v>
       </c>
       <c r="I98" t="n">
-        <v>0.5486</v>
+        <v>0.6025</v>
       </c>
       <c r="J98" t="n">
-        <v>12.0692</v>
+        <v>13.255</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.21</v>
       </c>
       <c r="I99" t="n">
-        <v>0.5205</v>
+        <v>0.5789</v>
       </c>
       <c r="J99" t="n">
-        <v>11.451</v>
+        <v>12.7358</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.13</v>
       </c>
       <c r="I100" t="n">
-        <v>0.3043</v>
+        <v>0.377</v>
       </c>
       <c r="J100" t="n">
-        <v>6.6946</v>
+        <v>8.294</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.04</v>
       </c>
       <c r="I101" t="n">
-        <v>0.0368</v>
+        <v>0.1109</v>
       </c>
       <c r="J101" t="n">
-        <v>0.8096</v>
+        <v>2.4398</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.39</v>
       </c>
       <c r="I102" t="n">
-        <v>0.971</v>
+        <v>0.9764</v>
       </c>
       <c r="J102" t="n">
-        <v>19.42</v>
+        <v>19.528</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.31</v>
       </c>
       <c r="I103" t="n">
-        <v>0.7892</v>
+        <v>0.8051</v>
       </c>
       <c r="J103" t="n">
-        <v>15.784</v>
+        <v>16.102</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.31</v>
       </c>
       <c r="I104" t="n">
-        <v>0.7892</v>
+        <v>0.8051</v>
       </c>
       <c r="J104" t="n">
-        <v>15.784</v>
+        <v>16.102</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.25</v>
       </c>
       <c r="I105" t="n">
-        <v>0.6339</v>
+        <v>0.6694</v>
       </c>
       <c r="J105" t="n">
-        <v>12.678</v>
+        <v>13.388</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.96</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3097</v>
+        <v>-0.2279</v>
       </c>
       <c r="J106" t="n">
-        <v>-6.194</v>
+        <v>-4.558</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.17</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3895</v>
+        <v>0.4353</v>
       </c>
       <c r="J107" t="n">
-        <v>7.79</v>
+        <v>8.706</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.93</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.0959</v>
+        <v>-0.0866</v>
       </c>
       <c r="J108" t="n">
-        <v>-1.918</v>
+        <v>-1.732</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.83</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2927</v>
+        <v>-0.1926</v>
       </c>
       <c r="J109" t="n">
-        <v>-5.854</v>
+        <v>-3.852</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.76</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4039</v>
+        <v>-0.2616</v>
       </c>
       <c r="J110" t="n">
-        <v>-8.077999999999999</v>
+        <v>-5.232</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.63</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5838</v>
+        <v>-0.3855</v>
       </c>
       <c r="J111" t="n">
-        <v>-11.676</v>
+        <v>-7.71</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.24</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6937</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="J112" t="n">
-        <v>15.9551</v>
+        <v>15.5227</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.19</v>
       </c>
       <c r="I113" t="n">
-        <v>0.5663</v>
+        <v>0.5517</v>
       </c>
       <c r="J113" t="n">
-        <v>13.0249</v>
+        <v>12.6891</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.17</v>
       </c>
       <c r="I114" t="n">
-        <v>0.512</v>
+        <v>0.5014</v>
       </c>
       <c r="J114" t="n">
-        <v>11.776</v>
+        <v>11.5322</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.06</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1553</v>
+        <v>0.203</v>
       </c>
       <c r="J115" t="n">
-        <v>3.5719</v>
+        <v>4.669</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.95</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2998</v>
+        <v>-0.2301</v>
       </c>
       <c r="J116" t="n">
-        <v>-6.8954</v>
+        <v>-5.2923</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.13</v>
       </c>
       <c r="I117" t="n">
-        <v>0.2952</v>
+        <v>0.3206</v>
       </c>
       <c r="J117" t="n">
-        <v>6.7896</v>
+        <v>7.3738</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.04</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1355</v>
+        <v>0.1267</v>
       </c>
       <c r="J118" t="n">
-        <v>3.1165</v>
+        <v>2.9141</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1</v>
       </c>
       <c r="I119" t="n">
-        <v>0.03</v>
+        <v>0.0078</v>
       </c>
       <c r="J119" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.1794</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.8</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3715</v>
+        <v>-0.2333</v>
       </c>
       <c r="J120" t="n">
-        <v>-8.544499999999999</v>
+        <v>-5.3659</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.79</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3862</v>
+        <v>-0.2433</v>
       </c>
       <c r="J121" t="n">
-        <v>-8.8826</v>
+        <v>-5.5959</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.21</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4658</v>
+        <v>0.5387</v>
       </c>
       <c r="J122" t="n">
-        <v>10.2476</v>
+        <v>11.8514</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.82</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.2761</v>
+        <v>-0.1982</v>
       </c>
       <c r="J123" t="n">
-        <v>-6.0742</v>
+        <v>-4.3604</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.78</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.3538</v>
+        <v>-0.2363</v>
       </c>
       <c r="J124" t="n">
-        <v>-7.7836</v>
+        <v>-5.1986</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.7</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.476</v>
+        <v>-0.3131</v>
       </c>
       <c r="J125" t="n">
-        <v>-10.472</v>
+        <v>-6.8882</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.58</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.638</v>
+        <v>-0.4259</v>
       </c>
       <c r="J126" t="n">
-        <v>-14.036</v>
+        <v>-9.3698</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.35</v>
       </c>
       <c r="I127" t="n">
-        <v>0.9139</v>
+        <v>0.9117</v>
       </c>
       <c r="J127" t="n">
-        <v>20.1058</v>
+        <v>20.0574</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.33</v>
       </c>
       <c r="I128" t="n">
-        <v>0.8691</v>
+        <v>0.8665</v>
       </c>
       <c r="J128" t="n">
-        <v>19.1202</v>
+        <v>19.063</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.26</v>
       </c>
       <c r="I129" t="n">
-        <v>0.7039</v>
+        <v>0.7043</v>
       </c>
       <c r="J129" t="n">
-        <v>15.4858</v>
+        <v>15.4946</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.01</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.0594</v>
+        <v>0.0098</v>
       </c>
       <c r="J130" t="n">
-        <v>-1.3068</v>
+        <v>0.2156</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.98</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2186</v>
+        <v>-0.1412</v>
       </c>
       <c r="J131" t="n">
-        <v>-4.8092</v>
+        <v>-3.1064</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.93</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.0218</v>
+        <v>-0.0508</v>
       </c>
       <c r="J132" t="n">
-        <v>-0.3706</v>
+        <v>-0.8636</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.83</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.192</v>
+        <v>-0.1686</v>
       </c>
       <c r="J133" t="n">
-        <v>-3.264</v>
+        <v>-2.8662</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.73</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.355</v>
+        <v>-0.2704</v>
       </c>
       <c r="J134" t="n">
-        <v>-6.035</v>
+        <v>-4.5968</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.54</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.6598000000000001</v>
+        <v>-0.4457</v>
       </c>
       <c r="J135" t="n">
-        <v>-11.2166</v>
+        <v>-7.5769</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.48</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.7383</v>
+        <v>-0.5018</v>
       </c>
       <c r="J136" t="n">
-        <v>-12.5511</v>
+        <v>-8.5306</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.72</v>
       </c>
       <c r="I137" t="n">
-        <v>1.5941</v>
+        <v>1.3891</v>
       </c>
       <c r="J137" t="n">
-        <v>27.0997</v>
+        <v>23.6147</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.37</v>
       </c>
       <c r="I138" t="n">
-        <v>0.8968</v>
+        <v>0.9244</v>
       </c>
       <c r="J138" t="n">
-        <v>15.2456</v>
+        <v>15.7148</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.26</v>
       </c>
       <c r="I139" t="n">
-        <v>0.6078</v>
+        <v>0.6843</v>
       </c>
       <c r="J139" t="n">
-        <v>10.3326</v>
+        <v>11.6331</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.2</v>
       </c>
       <c r="I140" t="n">
-        <v>0.4571</v>
+        <v>0.542</v>
       </c>
       <c r="J140" t="n">
-        <v>7.7707</v>
+        <v>9.214</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3882</v>
+        <v>-0.3062</v>
       </c>
       <c r="J141" t="n">
-        <v>-6.5994</v>
+        <v>-5.2054</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.69</v>
       </c>
       <c r="I142" t="n">
-        <v>0.8407</v>
+        <v>0.774</v>
       </c>
       <c r="J142" t="n">
-        <v>14.2919</v>
+        <v>13.158</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.67</v>
       </c>
       <c r="I143" t="n">
-        <v>0.8191000000000001</v>
+        <v>0.7542</v>
       </c>
       <c r="J143" t="n">
-        <v>13.9247</v>
+        <v>12.8214</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.41</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4956</v>
+        <v>0.4935</v>
       </c>
       <c r="J144" t="n">
-        <v>8.4252</v>
+        <v>8.3895</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.36</v>
       </c>
       <c r="I145" t="n">
-        <v>0.4325</v>
+        <v>0.4398</v>
       </c>
       <c r="J145" t="n">
-        <v>7.3525</v>
+        <v>7.4766</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.24</v>
       </c>
       <c r="I146" t="n">
-        <v>0.2794</v>
+        <v>0.3026</v>
       </c>
       <c r="J146" t="n">
-        <v>4.7498</v>
+        <v>5.1442</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.26</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.5309</v>
       </c>
       <c r="J147" t="n">
-        <v>9.691700000000001</v>
+        <v>9.0253</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.67</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.4893</v>
+        <v>-0.3298</v>
       </c>
       <c r="J148" t="n">
-        <v>-8.318099999999999</v>
+        <v>-5.6066</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.65</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.519</v>
+        <v>-0.3485</v>
       </c>
       <c r="J149" t="n">
-        <v>-8.823</v>
+        <v>-5.9245</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.64</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.5335</v>
+        <v>-0.3579</v>
       </c>
       <c r="J150" t="n">
-        <v>-9.0695</v>
+        <v>-6.0843</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.47</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.7592</v>
+        <v>-0.5165</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.9064</v>
+        <v>-8.7805</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.35</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5703</v>
+        <v>0.6869</v>
       </c>
       <c r="J152" t="n">
-        <v>12.5466</v>
+        <v>15.1118</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.2</v>
       </c>
       <c r="I153" t="n">
-        <v>0.369</v>
+        <v>0.4262</v>
       </c>
       <c r="J153" t="n">
-        <v>8.118</v>
+        <v>9.3764</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.13</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2617</v>
+        <v>0.2958</v>
       </c>
       <c r="J154" t="n">
-        <v>5.7574</v>
+        <v>6.5076</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.78</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4208</v>
+        <v>-0.2637</v>
       </c>
       <c r="J155" t="n">
-        <v>-9.2576</v>
+        <v>-5.8014</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.75</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4618</v>
+        <v>-0.293</v>
       </c>
       <c r="J156" t="n">
-        <v>-10.1596</v>
+        <v>-6.446</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.44</v>
       </c>
       <c r="I157" t="n">
-        <v>1.1223</v>
+        <v>1.0745</v>
       </c>
       <c r="J157" t="n">
-        <v>24.6906</v>
+        <v>23.639</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.21</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5962</v>
+        <v>0.5923</v>
       </c>
       <c r="J158" t="n">
-        <v>13.1164</v>
+        <v>13.0306</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.15</v>
       </c>
       <c r="I159" t="n">
-        <v>0.4132</v>
+        <v>0.4451</v>
       </c>
       <c r="J159" t="n">
-        <v>9.090400000000001</v>
+        <v>9.792199999999999</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.14</v>
       </c>
       <c r="I160" t="n">
-        <v>0.3812</v>
+        <v>0.4198</v>
       </c>
       <c r="J160" t="n">
-        <v>8.3864</v>
+        <v>9.2356</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.84</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.6207</v>
+        <v>-0.5591</v>
       </c>
       <c r="J161" t="n">
-        <v>-13.6554</v>
+        <v>-12.3002</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.14</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3044</v>
+        <v>0.3346</v>
       </c>
       <c r="J162" t="n">
-        <v>7.3056</v>
+        <v>8.0304</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.13</v>
       </c>
       <c r="I163" t="n">
-        <v>0.2886</v>
+        <v>0.3149</v>
       </c>
       <c r="J163" t="n">
-        <v>6.9264</v>
+        <v>7.5576</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.01</v>
       </c>
       <c r="I164" t="n">
-        <v>0.057</v>
+        <v>0.0427</v>
       </c>
       <c r="J164" t="n">
-        <v>1.368</v>
+        <v>1.0248</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.87</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2684</v>
+        <v>-0.1634</v>
       </c>
       <c r="J165" t="n">
-        <v>-6.4416</v>
+        <v>-3.9216</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.7</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.3328</v>
       </c>
       <c r="J166" t="n">
-        <v>-12.3504</v>
+        <v>-7.9872</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.49</v>
       </c>
       <c r="I167" t="n">
-        <v>1.2511</v>
+        <v>1.1551</v>
       </c>
       <c r="J167" t="n">
-        <v>30.0264</v>
+        <v>27.7224</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.43</v>
       </c>
       <c r="I168" t="n">
-        <v>1.1287</v>
+        <v>1.0752</v>
       </c>
       <c r="J168" t="n">
-        <v>27.0888</v>
+        <v>25.8048</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.3</v>
       </c>
       <c r="I169" t="n">
-        <v>0.8461</v>
+        <v>0.8255</v>
       </c>
       <c r="J169" t="n">
-        <v>20.3064</v>
+        <v>19.812</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.73</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.8672</v>
+        <v>-0.8282</v>
       </c>
       <c r="J170" t="n">
-        <v>-20.8128</v>
+        <v>-19.8768</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.57</v>
       </c>
       <c r="I171" t="n">
-        <v>-1.208</v>
+        <v>-1.2112</v>
       </c>
       <c r="J171" t="n">
-        <v>-28.992</v>
+        <v>-29.0688</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.32</v>
       </c>
       <c r="I172" t="n">
-        <v>0.5488</v>
+        <v>0.655</v>
       </c>
       <c r="J172" t="n">
-        <v>25.7936</v>
+        <v>30.785</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.25</v>
       </c>
       <c r="I173" t="n">
-        <v>0.4564</v>
+        <v>0.532</v>
       </c>
       <c r="J173" t="n">
-        <v>21.4508</v>
+        <v>25.004</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.07</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1776</v>
+        <v>0.1854</v>
       </c>
       <c r="J174" t="n">
-        <v>8.347200000000001</v>
+        <v>8.713800000000001</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.72</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4924</v>
+        <v>-0.3163</v>
       </c>
       <c r="J175" t="n">
-        <v>-23.1428</v>
+        <v>-14.8661</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.6</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6447000000000001</v>
+        <v>-0.4284</v>
       </c>
       <c r="J176" t="n">
-        <v>-30.3009</v>
+        <v>-20.1348</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.26</v>
       </c>
       <c r="I177" t="n">
-        <v>0.7538</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="J177" t="n">
-        <v>35.4286</v>
+        <v>34.3241</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.17</v>
       </c>
       <c r="I178" t="n">
-        <v>0.526</v>
+        <v>0.5065</v>
       </c>
       <c r="J178" t="n">
-        <v>24.722</v>
+        <v>23.8055</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.12</v>
       </c>
       <c r="I179" t="n">
-        <v>0.3805</v>
+        <v>0.3761</v>
       </c>
       <c r="J179" t="n">
-        <v>17.8835</v>
+        <v>17.6767</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.02</v>
       </c>
       <c r="I180" t="n">
-        <v>0.0225</v>
+        <v>0.0721</v>
       </c>
       <c r="J180" t="n">
-        <v>1.0575</v>
+        <v>3.3887</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3237</v>
+        <v>-0.2569</v>
       </c>
       <c r="J181" t="n">
-        <v>-15.2139</v>
+        <v>-12.0743</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.73</v>
       </c>
       <c r="I182" t="n">
-        <v>1.6286</v>
+        <v>1.4108</v>
       </c>
       <c r="J182" t="n">
-        <v>34.2006</v>
+        <v>29.6268</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.41</v>
       </c>
       <c r="I183" t="n">
-        <v>1.0049</v>
+        <v>1.0068</v>
       </c>
       <c r="J183" t="n">
-        <v>21.1029</v>
+        <v>21.1428</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.36</v>
       </c>
       <c r="I184" t="n">
-        <v>0.8948</v>
+        <v>0.9117</v>
       </c>
       <c r="J184" t="n">
-        <v>18.7908</v>
+        <v>19.1457</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.03</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.0077</v>
+        <v>0.0693</v>
       </c>
       <c r="J185" t="n">
-        <v>-0.1617</v>
+        <v>1.4553</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.78</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.7904</v>
+        <v>-0.7403</v>
       </c>
       <c r="J186" t="n">
-        <v>-16.5984</v>
+        <v>-15.5463</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.22</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4149</v>
+        <v>0.4779</v>
       </c>
       <c r="J187" t="n">
-        <v>8.712899999999999</v>
+        <v>10.0359</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.11</v>
       </c>
       <c r="I188" t="n">
-        <v>0.2478</v>
+        <v>0.2687</v>
       </c>
       <c r="J188" t="n">
-        <v>5.2038</v>
+        <v>5.6427</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.02</v>
       </c>
       <c r="I189" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.0674</v>
       </c>
       <c r="J189" t="n">
-        <v>1.5204</v>
+        <v>1.4154</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.95</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.132</v>
+        <v>-0.0751</v>
       </c>
       <c r="J190" t="n">
-        <v>-2.772</v>
+        <v>-1.5771</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.66</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5702</v>
+        <v>-0.373</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.9742</v>
+        <v>-7.833</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.89</v>
       </c>
       <c r="I192" t="n">
-        <v>1.9244</v>
+        <v>1.6239</v>
       </c>
       <c r="J192" t="n">
-        <v>42.3368</v>
+        <v>35.7258</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.12</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2936</v>
+        <v>0.3578</v>
       </c>
       <c r="J193" t="n">
-        <v>6.4592</v>
+        <v>7.8716</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.04</v>
       </c>
       <c r="I194" t="n">
-        <v>0.05</v>
+        <v>0.1192</v>
       </c>
       <c r="J194" t="n">
-        <v>1.1</v>
+        <v>2.6224</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.98</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2236</v>
+        <v>-0.1447</v>
       </c>
       <c r="J195" t="n">
-        <v>-4.9192</v>
+        <v>-3.1834</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.97</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.261</v>
+        <v>-0.182</v>
       </c>
       <c r="J196" t="n">
-        <v>-5.742</v>
+        <v>-4.004</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.16</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3519</v>
+        <v>0.3897</v>
       </c>
       <c r="J197" t="n">
-        <v>7.7418</v>
+        <v>8.573399999999999</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.15</v>
       </c>
       <c r="I198" t="n">
-        <v>0.3367</v>
+        <v>0.3701</v>
       </c>
       <c r="J198" t="n">
-        <v>7.4074</v>
+        <v>8.142200000000001</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.83</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.3173</v>
+        <v>-0.1996</v>
       </c>
       <c r="J199" t="n">
-        <v>-6.9806</v>
+        <v>-4.3912</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.77</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4076</v>
+        <v>-0.2596</v>
       </c>
       <c r="J200" t="n">
-        <v>-8.9672</v>
+        <v>-5.7112</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.71</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4914</v>
+        <v>-0.3177</v>
       </c>
       <c r="J201" t="n">
-        <v>-10.8108</v>
+        <v>-6.9894</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.63</v>
       </c>
       <c r="I202" t="n">
-        <v>1.4662</v>
+        <v>1.3012</v>
       </c>
       <c r="J202" t="n">
-        <v>32.2564</v>
+        <v>28.6264</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.35</v>
       </c>
       <c r="I203" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.9025</v>
       </c>
       <c r="J203" t="n">
-        <v>19.7494</v>
+        <v>19.855</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.16</v>
       </c>
       <c r="I204" t="n">
-        <v>0.3958</v>
+        <v>0.4594</v>
       </c>
       <c r="J204" t="n">
-        <v>8.707599999999999</v>
+        <v>10.1068</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.14</v>
       </c>
       <c r="I205" t="n">
-        <v>0.3409</v>
+        <v>0.4076</v>
       </c>
       <c r="J205" t="n">
-        <v>7.4998</v>
+        <v>8.9672</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.8</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.7337</v>
+        <v>-0.6788999999999999</v>
       </c>
       <c r="J206" t="n">
-        <v>-16.1414</v>
+        <v>-14.9358</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.11</v>
       </c>
       <c r="I207" t="n">
-        <v>0.2902</v>
+        <v>0.3061</v>
       </c>
       <c r="J207" t="n">
-        <v>6.3844</v>
+        <v>6.7342</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.99</v>
       </c>
       <c r="I208" t="n">
-        <v>0.0265</v>
+        <v>-0.0069</v>
       </c>
       <c r="J208" t="n">
-        <v>0.583</v>
+        <v>-0.1518</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.92</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1231</v>
+        <v>-0.1004</v>
       </c>
       <c r="J209" t="n">
-        <v>-2.7082</v>
+        <v>-2.2088</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.8</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3486</v>
+        <v>-0.2244</v>
       </c>
       <c r="J210" t="n">
-        <v>-7.6692</v>
+        <v>-4.9368</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.58</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6506999999999999</v>
+        <v>-0.434</v>
       </c>
       <c r="J211" t="n">
-        <v>-14.3154</v>
+        <v>-9.548</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.41</v>
       </c>
       <c r="I212" t="n">
-        <v>1.0901</v>
+        <v>1.0495</v>
       </c>
       <c r="J212" t="n">
-        <v>26.1624</v>
+        <v>25.188</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.24</v>
       </c>
       <c r="I213" t="n">
-        <v>0.7079</v>
+        <v>0.6829</v>
       </c>
       <c r="J213" t="n">
-        <v>16.9896</v>
+        <v>16.3896</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.16</v>
       </c>
       <c r="I214" t="n">
-        <v>0.5013</v>
+        <v>0.4819</v>
       </c>
       <c r="J214" t="n">
-        <v>12.0312</v>
+        <v>11.5656</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.92</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3835</v>
+        <v>-0.3176</v>
       </c>
       <c r="J215" t="n">
-        <v>-9.204000000000001</v>
+        <v>-7.6224</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.76</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.7969000000000001</v>
+        <v>-0.7516</v>
       </c>
       <c r="J216" t="n">
-        <v>-19.1256</v>
+        <v>-18.0384</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.46</v>
       </c>
       <c r="I217" t="n">
-        <v>0.7081</v>
+        <v>0.8748</v>
       </c>
       <c r="J217" t="n">
-        <v>16.9944</v>
+        <v>20.9952</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.09</v>
       </c>
       <c r="I218" t="n">
-        <v>0.1992</v>
+        <v>0.2196</v>
       </c>
       <c r="J218" t="n">
-        <v>4.7808</v>
+        <v>5.2704</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.99</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0551</v>
+        <v>-0.0229</v>
       </c>
       <c r="J219" t="n">
-        <v>-1.3224</v>
+        <v>-0.5496</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.9</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2363</v>
+        <v>-0.1373</v>
       </c>
       <c r="J220" t="n">
-        <v>-5.6712</v>
+        <v>-3.2952</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.7</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5252</v>
+        <v>-0.3393</v>
       </c>
       <c r="J221" t="n">
-        <v>-12.6048</v>
+        <v>-8.1432</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.72</v>
       </c>
       <c r="I222" t="n">
-        <v>1.5728</v>
+        <v>1.3775</v>
       </c>
       <c r="J222" t="n">
-        <v>28.3104</v>
+        <v>24.795</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.36</v>
       </c>
       <c r="I223" t="n">
-        <v>0.8403</v>
+        <v>0.8948</v>
       </c>
       <c r="J223" t="n">
-        <v>15.1254</v>
+        <v>16.1064</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.28</v>
       </c>
       <c r="I224" t="n">
-        <v>0.6292</v>
+        <v>0.7211</v>
       </c>
       <c r="J224" t="n">
-        <v>11.3256</v>
+        <v>12.9798</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.23</v>
       </c>
       <c r="I225" t="n">
-        <v>0.5092</v>
+        <v>0.6045</v>
       </c>
       <c r="J225" t="n">
-        <v>9.1656</v>
+        <v>10.881</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.14</v>
       </c>
       <c r="I226" t="n">
-        <v>0.2858</v>
+        <v>0.3783</v>
       </c>
       <c r="J226" t="n">
-        <v>5.1444</v>
+        <v>6.8094</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.06</v>
       </c>
       <c r="I227" t="n">
-        <v>0.2218</v>
+        <v>0.2149</v>
       </c>
       <c r="J227" t="n">
-        <v>3.9924</v>
+        <v>3.8682</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.063</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="J228" t="n">
-        <v>-1.134</v>
+        <v>-1.251</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.91</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1191</v>
+        <v>-0.1055</v>
       </c>
       <c r="J229" t="n">
-        <v>-2.1438</v>
+        <v>-1.899</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.65</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.55</v>
+        <v>-0.3627</v>
       </c>
       <c r="J230" t="n">
-        <v>-9.9</v>
+        <v>-6.5286</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.61</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6029</v>
+        <v>-0.4002</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.8522</v>
+        <v>-7.2036</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/6868/event_6868_evp_summary.xlsx
+++ b/database/event/6868/event_6868_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.9416</v>
+        <v>5.8107</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7651</v>
+        <v>0.7483</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0443</v>
+        <v>2.0209</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9416</v>
+        <v>5.8107</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8694</v>
+        <v>3.7623</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0722</v>
+        <v>2.0484</v>
       </c>
       <c r="H2" t="n">
-        <v>8.1469</v>
+        <v>7.5192</v>
       </c>
       <c r="I2" t="n">
-        <v>4.236</v>
+        <v>4.0603</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0722</v>
+        <v>2.0484</v>
       </c>
       <c r="K2" t="n">
         <v>101</v>
@@ -529,7 +529,7 @@
         <v>151</v>
       </c>
       <c r="M2" t="n">
-        <v>6.308199999999999</v>
+        <v>6.1087</v>
       </c>
       <c r="N2" t="n">
         <v>252</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.6018</v>
+        <v>5.674</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7214</v>
+        <v>0.7307</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8909</v>
+        <v>1.9587</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6018</v>
+        <v>5.674</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8067</v>
+        <v>2.7305</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7951</v>
+        <v>2.9435</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4026</v>
+        <v>4.1149</v>
       </c>
       <c r="I3" t="n">
-        <v>2.2892</v>
+        <v>2.222</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7951</v>
+        <v>2.9435</v>
       </c>
       <c r="K3" t="n">
         <v>39</v>
@@ -575,7 +575,7 @@
         <v>121</v>
       </c>
       <c r="M3" t="n">
-        <v>5.084300000000001</v>
+        <v>5.1655</v>
       </c>
       <c r="N3" t="n">
         <v>160</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.4794</v>
+        <v>4.4706</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5768</v>
+        <v>0.5757</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3842</v>
+        <v>1.4109</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4794</v>
+        <v>4.4706</v>
       </c>
       <c r="F4" t="n">
-        <v>3.7444</v>
+        <v>3.6677</v>
       </c>
       <c r="G4" t="n">
-        <v>0.735</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>7.7066</v>
+        <v>7.2068</v>
       </c>
       <c r="I4" t="n">
-        <v>4.0071</v>
+        <v>3.8916</v>
       </c>
       <c r="J4" t="n">
-        <v>0.735</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="K4" t="n">
         <v>101</v>
@@ -621,7 +621,7 @@
         <v>151</v>
       </c>
       <c r="M4" t="n">
-        <v>4.742100000000001</v>
+        <v>4.6945</v>
       </c>
       <c r="N4" t="n">
         <v>252</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.5145</v>
+        <v>3.5227</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4526</v>
+        <v>0.4536</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9486</v>
+        <v>0.9794</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5145</v>
+        <v>3.5227</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5566</v>
+        <v>2.4692</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9579</v>
+        <v>1.0535</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5215</v>
+        <v>3.2526</v>
       </c>
       <c r="I5" t="n">
-        <v>1.831</v>
+        <v>1.7564</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9579</v>
+        <v>1.0535</v>
       </c>
       <c r="K5" t="n">
         <v>112</v>
@@ -667,7 +667,7 @@
         <v>63</v>
       </c>
       <c r="M5" t="n">
-        <v>2.7889</v>
+        <v>2.8099</v>
       </c>
       <c r="N5" t="n">
         <v>175</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.4533</v>
+        <v>3.485</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4447</v>
+        <v>0.4488</v>
       </c>
       <c r="D6" t="n">
-        <v>0.921</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4533</v>
+        <v>3.485</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5201</v>
+        <v>1.4593</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9332</v>
+        <v>2.0257</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5201</v>
+        <v>1.4593</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7904</v>
+        <v>0.788</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9332</v>
+        <v>2.0257</v>
       </c>
       <c r="K6" t="n">
         <v>39</v>
@@ -713,7 +713,7 @@
         <v>121</v>
       </c>
       <c r="M6" t="n">
-        <v>2.7236</v>
+        <v>2.8137</v>
       </c>
       <c r="N6" t="n">
         <v>160</v>
@@ -722,35 +722,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>Calyx</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.3088</v>
+        <v>3.2926</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4261</v>
+        <v>0.424</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8557</v>
+        <v>0.8747</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3088</v>
+        <v>3.2926</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7595</v>
+        <v>3.2542</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5493</v>
+        <v>0.0384</v>
       </c>
       <c r="H7" t="n">
-        <v>4.2363</v>
+        <v>5.8425</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2027</v>
+        <v>3.1549</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5493</v>
+        <v>0.0384</v>
       </c>
       <c r="K7" t="n">
         <v>101</v>
@@ -759,7 +759,7 @@
         <v>151</v>
       </c>
       <c r="M7" t="n">
-        <v>2.752</v>
+        <v>3.1933</v>
       </c>
       <c r="N7" t="n">
         <v>252</v>
@@ -768,35 +768,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Calyx</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2911</v>
+        <v>3.2905</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4238</v>
+        <v>0.4237</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8478</v>
+        <v>0.8737</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2911</v>
+        <v>3.2905</v>
       </c>
       <c r="F8" t="n">
-        <v>3.3392</v>
+        <v>2.6845</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0481</v>
+        <v>0.606</v>
       </c>
       <c r="H8" t="n">
-        <v>6.279</v>
+        <v>3.963</v>
       </c>
       <c r="I8" t="n">
-        <v>3.2648</v>
+        <v>2.14</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0481</v>
+        <v>0.606</v>
       </c>
       <c r="K8" t="n">
         <v>101</v>
@@ -805,7 +805,7 @@
         <v>151</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2167</v>
+        <v>2.746</v>
       </c>
       <c r="N8" t="n">
         <v>252</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9944</v>
+        <v>3.0845</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3856</v>
+        <v>0.3972</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7138</v>
+        <v>0.7799</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9944</v>
+        <v>3.0845</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5334</v>
+        <v>2.4829</v>
       </c>
       <c r="G9" t="n">
-        <v>0.461</v>
+        <v>0.6016</v>
       </c>
       <c r="H9" t="n">
-        <v>3.4399</v>
+        <v>3.2978</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7886</v>
+        <v>1.7808</v>
       </c>
       <c r="J9" t="n">
-        <v>0.461</v>
+        <v>0.6016</v>
       </c>
       <c r="K9" t="n">
         <v>39</v>
@@ -851,7 +851,7 @@
         <v>121</v>
       </c>
       <c r="M9" t="n">
-        <v>2.2496</v>
+        <v>2.3824</v>
       </c>
       <c r="N9" t="n">
         <v>160</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.7269</v>
+        <v>2.6745</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3511</v>
+        <v>0.3444</v>
       </c>
       <c r="D10" t="n">
-        <v>0.593</v>
+        <v>0.5933</v>
       </c>
       <c r="E10" t="n">
-        <v>2.7269</v>
+        <v>2.6745</v>
       </c>
       <c r="F10" t="n">
-        <v>2.8215</v>
+        <v>2.7773</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0946</v>
+        <v>-0.1028</v>
       </c>
       <c r="H10" t="n">
-        <v>4.4548</v>
+        <v>4.2691</v>
       </c>
       <c r="I10" t="n">
-        <v>2.3163</v>
+        <v>2.3053</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0946</v>
+        <v>-0.1028</v>
       </c>
       <c r="K10" t="n">
         <v>69</v>
@@ -897,7 +897,7 @@
         <v>93</v>
       </c>
       <c r="M10" t="n">
-        <v>2.2217</v>
+        <v>2.2025</v>
       </c>
       <c r="N10" t="n">
         <v>162</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.483</v>
+        <v>2.607</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3197</v>
+        <v>0.3357</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4829</v>
+        <v>0.5626</v>
       </c>
       <c r="E11" t="n">
-        <v>2.483</v>
+        <v>2.607</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3192</v>
+        <v>1.2932</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1638</v>
+        <v>1.3138</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3192</v>
+        <v>1.2932</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6859</v>
+        <v>0.6983</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1638</v>
+        <v>1.3138</v>
       </c>
       <c r="K11" t="n">
         <v>112</v>
@@ -943,7 +943,7 @@
         <v>63</v>
       </c>
       <c r="M11" t="n">
-        <v>1.8497</v>
+        <v>2.0121</v>
       </c>
       <c r="N11" t="n">
         <v>175</v>
@@ -952,47 +952,47 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>volt</t>
+          <t>DemQQ</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.4811</v>
+        <v>2.4278</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3195</v>
+        <v>0.3126</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4821</v>
+        <v>0.481</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4811</v>
+        <v>2.4278</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4811</v>
+        <v>2.4947</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0.0669</v>
       </c>
       <c r="H12" t="n">
-        <v>2.4811</v>
+        <v>3.3367</v>
       </c>
       <c r="I12" t="n">
-        <v>2.4811</v>
+        <v>1.8018</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0.0669</v>
       </c>
       <c r="K12" t="n">
-        <v>128</v>
+        <v>39</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="M12" t="n">
-        <v>2.4811</v>
+        <v>1.7349</v>
       </c>
       <c r="N12" t="n">
-        <v>128</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.4062</v>
+        <v>2.3247</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3099</v>
+        <v>0.2994</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4483</v>
+        <v>0.434</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4062</v>
+        <v>2.3247</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8106</v>
+        <v>2.7328</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.4044</v>
+        <v>-0.4081</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4165</v>
+        <v>4.1225</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2964</v>
+        <v>2.2261</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4044</v>
+        <v>-0.4081</v>
       </c>
       <c r="K13" t="n">
         <v>112</v>
@@ -1035,7 +1035,7 @@
         <v>63</v>
       </c>
       <c r="M13" t="n">
-        <v>1.892</v>
+        <v>1.818</v>
       </c>
       <c r="N13" t="n">
         <v>175</v>
@@ -1044,47 +1044,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DemQQ</t>
+          <t>volt</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3942</v>
+        <v>2.3055</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3083</v>
+        <v>0.2969</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4428</v>
+        <v>0.4253</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3942</v>
+        <v>2.3055</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5951</v>
+        <v>2.3055</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2009</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3.6572</v>
+        <v>2.321</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9016</v>
+        <v>2.321</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2009</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="L14" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7007</v>
+        <v>2.321</v>
       </c>
       <c r="N14" t="n">
-        <v>160</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.3383</v>
+        <v>2.2366</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3011</v>
+        <v>0.288</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4176</v>
+        <v>0.3939</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3383</v>
+        <v>2.2366</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7673</v>
+        <v>2.6776</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.429</v>
+        <v>-0.441</v>
       </c>
       <c r="H15" t="n">
-        <v>4.264</v>
+        <v>3.9401</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2171</v>
+        <v>2.1276</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.429</v>
+        <v>-0.441</v>
       </c>
       <c r="K15" t="n">
         <v>112</v>
@@ -1127,7 +1127,7 @@
         <v>63</v>
       </c>
       <c r="M15" t="n">
-        <v>1.7881</v>
+        <v>1.6866</v>
       </c>
       <c r="N15" t="n">
         <v>175</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8571</v>
+        <v>1.9466</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2391</v>
+        <v>0.2507</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2004</v>
+        <v>0.2619</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8571</v>
+        <v>1.9466</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9526</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9045</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9526</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4953</v>
+        <v>0.5114</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9045</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="K16" t="n">
         <v>69</v>
@@ -1173,7 +1173,7 @@
         <v>93</v>
       </c>
       <c r="M16" t="n">
-        <v>1.3998</v>
+        <v>1.5109</v>
       </c>
       <c r="N16" t="n">
         <v>162</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.8564</v>
+        <v>1.8371</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2391</v>
+        <v>0.2366</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2001</v>
+        <v>0.2121</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8564</v>
+        <v>1.8371</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3811</v>
+        <v>1.2376</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4753</v>
+        <v>0.5995</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3811</v>
+        <v>1.2376</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7181</v>
+        <v>0.6683</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4753</v>
+        <v>0.5995</v>
       </c>
       <c r="K17" t="n">
         <v>112</v>
@@ -1219,7 +1219,7 @@
         <v>63</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1934</v>
+        <v>1.2678</v>
       </c>
       <c r="N17" t="n">
         <v>175</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8212</v>
+        <v>1.8138</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2345</v>
+        <v>0.2336</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1842</v>
+        <v>0.2015</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8212</v>
+        <v>1.8138</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8212</v>
+        <v>1.8138</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.8212</v>
+        <v>1.8138</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8212</v>
+        <v>1.8138</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.8212</v>
+        <v>1.8138</v>
       </c>
       <c r="N18" t="n">
         <v>85</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.5138</v>
+        <v>1.5883</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1949</v>
+        <v>0.2045</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0454</v>
+        <v>0.0988</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5138</v>
+        <v>1.5883</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8268</v>
+        <v>0.8259</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.7624</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8268</v>
+        <v>0.8259</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4299</v>
+        <v>0.446</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.7624</v>
       </c>
       <c r="K19" t="n">
         <v>69</v>
@@ -1311,7 +1311,7 @@
         <v>93</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1169</v>
+        <v>1.2084</v>
       </c>
       <c r="N19" t="n">
         <v>162</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.2347</v>
+        <v>1.1251</v>
       </c>
       <c r="C20" t="n">
-        <v>0.159</v>
+        <v>0.1449</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0806</v>
+        <v>-0.112</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2347</v>
+        <v>1.1251</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2347</v>
+        <v>1.1251</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2347</v>
+        <v>1.1251</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2347</v>
+        <v>1.1251</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2347</v>
+        <v>1.1251</v>
       </c>
       <c r="N20" t="n">
         <v>128</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.0101</v>
+        <v>0.9799</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1301</v>
+        <v>0.1262</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.182</v>
+        <v>-0.1781</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0101</v>
+        <v>0.9799</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0101</v>
+        <v>0.9799</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0101</v>
+        <v>0.9799</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0101</v>
+        <v>0.9799</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.0101</v>
+        <v>0.9799</v>
       </c>
       <c r="N21" t="n">
         <v>85</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8424</v>
+        <v>0.7892</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1085</v>
+        <v>0.1016</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2577</v>
+        <v>-0.2649</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8424</v>
+        <v>0.7892</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8424</v>
+        <v>0.7892</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8424</v>
+        <v>0.7892</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8424</v>
+        <v>0.7892</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8424</v>
+        <v>0.7892</v>
       </c>
       <c r="N22" t="n">
         <v>83</v>
@@ -1458,139 +1458,139 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.704</v>
+        <v>0.6591</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0907</v>
+        <v>0.0849</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3202</v>
+        <v>-0.3242</v>
       </c>
       <c r="E23" t="n">
-        <v>0.704</v>
+        <v>0.6591</v>
       </c>
       <c r="F23" t="n">
-        <v>0.704</v>
+        <v>0.6591</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.704</v>
+        <v>0.6591</v>
       </c>
       <c r="I23" t="n">
-        <v>0.704</v>
+        <v>0.6591</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>128</v>
+        <v>85</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.704</v>
+        <v>0.6591</v>
       </c>
       <c r="N23" t="n">
-        <v>128</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6587</v>
+        <v>0.6469</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0848</v>
+        <v>0.0833</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3406</v>
+        <v>-0.3297</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6587</v>
+        <v>0.6469</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6587</v>
+        <v>0.6469</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6587</v>
+        <v>0.6469</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6587</v>
+        <v>0.6469</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6587</v>
+        <v>0.6469</v>
       </c>
       <c r="N24" t="n">
-        <v>85</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MarKE</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4303</v>
+        <v>0.5044</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0554</v>
+        <v>0.065</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4438</v>
+        <v>-0.3946</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4303</v>
+        <v>0.5044</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4303</v>
+        <v>0.3193</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.1851</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4303</v>
+        <v>0.3193</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4303</v>
+        <v>0.1724</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>0.1851</v>
       </c>
       <c r="K25" t="n">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4303</v>
+        <v>0.3575</v>
       </c>
       <c r="N25" t="n">
-        <v>83</v>
+        <v>252</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4148</v>
+        <v>0.3589</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0534</v>
+        <v>0.0462</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4508</v>
+        <v>-0.4608</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4148</v>
+        <v>0.3589</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4148</v>
+        <v>0.3589</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4148</v>
+        <v>0.3589</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4148</v>
+        <v>0.3589</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4148</v>
+        <v>0.3589</v>
       </c>
       <c r="N26" t="n">
         <v>83</v>
@@ -1642,47 +1642,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>MarKE</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.322</v>
+        <v>0.3277</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0415</v>
+        <v>0.0422</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4926</v>
+        <v>-0.475</v>
       </c>
       <c r="E27" t="n">
-        <v>0.322</v>
+        <v>0.3277</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2219</v>
+        <v>0.3277</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1001</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2219</v>
+        <v>0.3277</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1154</v>
+        <v>0.3277</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1001</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="L27" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2155</v>
+        <v>0.3277</v>
       </c>
       <c r="N27" t="n">
-        <v>252</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2731</v>
+        <v>0.2692</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0352</v>
+        <v>0.0347</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5147</v>
+        <v>-0.5017</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2731</v>
+        <v>0.2692</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2731</v>
+        <v>0.2692</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2731</v>
+        <v>0.2692</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2731</v>
+        <v>0.2692</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2731</v>
+        <v>0.2692</v>
       </c>
       <c r="N28" t="n">
         <v>85</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2518</v>
+        <v>0.208</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0324</v>
+        <v>0.0268</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5243</v>
+        <v>-0.5295</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2518</v>
+        <v>0.208</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2518</v>
+        <v>0.208</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.2518</v>
+        <v>0.208</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2518</v>
+        <v>0.208</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.2518</v>
+        <v>0.208</v>
       </c>
       <c r="N29" t="n">
         <v>57</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0126</v>
+        <v>-0.0751</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0016</v>
+        <v>-0.0097</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6437</v>
+        <v>-0.6584</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0126</v>
+        <v>-0.0751</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6241</v>
+        <v>0.5941</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.6367</v>
+        <v>-0.6692</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6241</v>
+        <v>0.5941</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3245</v>
+        <v>0.3208</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.6367</v>
+        <v>-0.6692</v>
       </c>
       <c r="K30" t="n">
         <v>69</v>
@@ -1817,7 +1817,7 @@
         <v>93</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.3122</v>
+        <v>-0.3484</v>
       </c>
       <c r="N30" t="n">
         <v>162</v>
@@ -1826,124 +1826,124 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4104</v>
+        <v>-0.3715</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0528</v>
+        <v>-0.0478</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8233</v>
+        <v>-0.7933</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4104</v>
+        <v>-0.3715</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.4104</v>
+        <v>-0.7124</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>0.3409</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.4104</v>
+        <v>-0.7124</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4104</v>
+        <v>-0.3847</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.3409</v>
       </c>
       <c r="K31" t="n">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4104</v>
+        <v>-0.04380000000000001</v>
       </c>
       <c r="N31" t="n">
-        <v>85</v>
+        <v>162</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kaze</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4363</v>
+        <v>-0.4329</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0562</v>
+        <v>-0.0557</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.835</v>
+        <v>-0.8213</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4363</v>
+        <v>-0.4329</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.4363</v>
+        <v>-0.4329</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4363</v>
+        <v>-0.4329</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4363</v>
+        <v>-0.4329</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4363</v>
+        <v>-0.4329</v>
       </c>
       <c r="N32" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Moseyuh</t>
+          <t>kaze</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4694</v>
+        <v>-0.4925</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0604</v>
+        <v>-0.0634</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8499</v>
+        <v>-0.8484</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4694</v>
+        <v>-0.4925</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.4694</v>
+        <v>-0.4925</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4694</v>
+        <v>-0.4925</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4694</v>
+        <v>-0.4925</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4694</v>
+        <v>-0.4925</v>
       </c>
       <c r="N33" t="n">
         <v>57</v>
@@ -1964,47 +1964,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>Moseyuh</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.495</v>
+        <v>-0.5248</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.06370000000000001</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8615</v>
+        <v>-0.8631</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.495</v>
+        <v>-0.5248</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.7724</v>
+        <v>-0.5248</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2774</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.7724</v>
+        <v>-0.5248</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4016</v>
+        <v>-0.5248</v>
       </c>
       <c r="J34" t="n">
-        <v>0.2774</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="L34" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.1242</v>
+        <v>-0.5248</v>
       </c>
       <c r="N34" t="n">
-        <v>162</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.659</v>
+        <v>-0.6794</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0849</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9355</v>
+        <v>-0.9335</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.659</v>
+        <v>-0.6794</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.659</v>
+        <v>-0.6794</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.659</v>
+        <v>-0.6794</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.659</v>
+        <v>-0.6794</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.659</v>
+        <v>-0.6794</v>
       </c>
       <c r="N35" t="n">
         <v>83</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8694</v>
+        <v>-0.9224</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.112</v>
+        <v>-0.1188</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0305</v>
+        <v>-1.0441</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8694</v>
+        <v>-0.9224</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.8694</v>
+        <v>-0.9224</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.8694</v>
+        <v>-0.9224</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8694</v>
+        <v>-0.9224</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8694</v>
+        <v>-0.9224</v>
       </c>
       <c r="N36" t="n">
         <v>57</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.1653</v>
+        <v>-1.0583</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1501</v>
+        <v>-0.1363</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1641</v>
+        <v>-1.106</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.1653</v>
+        <v>-1.0583</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.2612</v>
+        <v>-0.1665</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.9041</v>
+        <v>-0.8918</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.2612</v>
+        <v>-0.1665</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.1358</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.9041</v>
+        <v>-0.8918</v>
       </c>
       <c r="K37" t="n">
         <v>39</v>
@@ -2139,7 +2139,7 @@
         <v>121</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.0399</v>
+        <v>-0.9817</v>
       </c>
       <c r="N37" t="n">
         <v>160</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2718</v>
+        <v>-1.3095</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1638</v>
+        <v>-0.1686</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2122</v>
+        <v>-1.2203</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2718</v>
+        <v>-1.3095</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.2718</v>
+        <v>-1.3095</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2718</v>
+        <v>-1.3095</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2718</v>
+        <v>-1.3095</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2718</v>
+        <v>-1.3095</v>
       </c>
       <c r="N38" t="n">
         <v>57</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.4383</v>
+        <v>-1.4209</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1852</v>
+        <v>-0.183</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2873</v>
+        <v>-1.271</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.4383</v>
+        <v>-1.4209</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.4383</v>
+        <v>-1.4209</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.4383</v>
+        <v>-1.4209</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.4383</v>
+        <v>-1.4209</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.4383</v>
+        <v>-1.4209</v>
       </c>
       <c r="N39" t="n">
         <v>128</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.5439</v>
+        <v>-1.4864</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1988</v>
+        <v>-0.1914</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.335</v>
+        <v>-1.3008</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.5439</v>
+        <v>-1.4864</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.5439</v>
+        <v>-1.4864</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.5439</v>
+        <v>-1.4864</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.5439</v>
+        <v>-1.4864</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.5439</v>
+        <v>-1.4864</v>
       </c>
       <c r="N40" t="n">
         <v>128</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.5549</v>
+        <v>-1.5462</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.2002</v>
+        <v>-0.1991</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.34</v>
+        <v>-1.3281</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.5549</v>
+        <v>-1.5462</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.5549</v>
+        <v>-1.5462</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.5549</v>
+        <v>-1.5462</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.5549</v>
+        <v>-1.5462</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.5549</v>
+        <v>-1.5462</v>
       </c>
       <c r="N41" t="n">
         <v>83</v>
@@ -2429,10 +2429,10 @@
         <v>1.34</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9082</v>
+        <v>0.8495</v>
       </c>
       <c r="J2" t="n">
-        <v>20.8886</v>
+        <v>19.5385</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.34</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9082</v>
+        <v>0.8495</v>
       </c>
       <c r="J3" t="n">
-        <v>20.8886</v>
+        <v>19.5385</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.03</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1015</v>
+        <v>0.116</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3345</v>
+        <v>2.668</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.98</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1272</v>
+        <v>-0.1226</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.9256</v>
+        <v>-2.8198</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.97</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1644</v>
+        <v>-0.1592</v>
       </c>
       <c r="J6" t="n">
-        <v>-3.7812</v>
+        <v>-3.6616</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.29</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5869</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>13.4987</v>
+        <v>13.1583</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.18</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3913</v>
+        <v>0.3917</v>
       </c>
       <c r="J8" t="n">
-        <v>8.9999</v>
+        <v>9.0091</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.03</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0872</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>2.0056</v>
+        <v>2.2241</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.84</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2025</v>
+        <v>-0.2151</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.6575</v>
+        <v>-4.9473</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.84</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2025</v>
+        <v>-0.2151</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.6575</v>
+        <v>-4.9473</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.81</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5521</v>
+        <v>1.675</v>
       </c>
       <c r="J12" t="n">
-        <v>54.3235</v>
+        <v>58.625</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.08</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2603</v>
+        <v>0.2674</v>
       </c>
       <c r="J13" t="n">
-        <v>9.1105</v>
+        <v>9.359</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.95</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2333</v>
+        <v>-0.2253</v>
       </c>
       <c r="J14" t="n">
-        <v>-8.1655</v>
+        <v>-7.8855</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.95</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2333</v>
+        <v>-0.2253</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.1655</v>
+        <v>-7.8855</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.88</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4436</v>
+        <v>-0.4204</v>
       </c>
       <c r="J16" t="n">
-        <v>-15.526</v>
+        <v>-14.714</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.5</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9246</v>
+        <v>0.878</v>
       </c>
       <c r="J17" t="n">
-        <v>32.361</v>
+        <v>30.73</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.45</v>
       </c>
       <c r="I18" t="n">
-        <v>0.845</v>
+        <v>0.8063</v>
       </c>
       <c r="J18" t="n">
-        <v>29.575</v>
+        <v>28.2205</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.87</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1736</v>
+        <v>-0.1854</v>
       </c>
       <c r="J19" t="n">
-        <v>-6.076</v>
+        <v>-6.489</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.8</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2458</v>
+        <v>-0.2577</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.603</v>
+        <v>-9.019500000000001</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.68</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3615</v>
+        <v>-0.371</v>
       </c>
       <c r="J21" t="n">
-        <v>-12.6525</v>
+        <v>-12.985</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.36</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7072000000000001</v>
+        <v>0.7786999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>20.5088</v>
+        <v>22.5823</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.12</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3589</v>
+        <v>0.3736</v>
       </c>
       <c r="J23" t="n">
-        <v>10.4081</v>
+        <v>10.8344</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.09</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2955</v>
+        <v>0.2986</v>
       </c>
       <c r="J24" t="n">
-        <v>8.5695</v>
+        <v>8.6594</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.06</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2076</v>
+        <v>0.2159</v>
       </c>
       <c r="J25" t="n">
-        <v>6.0204</v>
+        <v>6.2611</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.88</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4349</v>
+        <v>-0.4144</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.6121</v>
+        <v>-12.0176</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.14</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3272</v>
+        <v>0.331</v>
       </c>
       <c r="J27" t="n">
-        <v>9.488799999999999</v>
+        <v>9.599</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.09</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2293</v>
+        <v>0.2352</v>
       </c>
       <c r="J28" t="n">
-        <v>6.6497</v>
+        <v>6.8208</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.02</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0684</v>
+        <v>0.0751</v>
       </c>
       <c r="J29" t="n">
-        <v>1.9836</v>
+        <v>2.1779</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.87</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1653</v>
+        <v>-0.1789</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.7937</v>
+        <v>-5.1881</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2273</v>
+        <v>-0.2412</v>
       </c>
       <c r="J31" t="n">
-        <v>-6.5917</v>
+        <v>-6.9948</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.29</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4015</v>
+        <v>0.4436</v>
       </c>
       <c r="J32" t="n">
-        <v>9.234500000000001</v>
+        <v>10.2028</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.08</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1508</v>
+        <v>0.1619</v>
       </c>
       <c r="J33" t="n">
-        <v>3.4684</v>
+        <v>3.7237</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0844</v>
+        <v>0.0944</v>
       </c>
       <c r="J34" t="n">
-        <v>1.9412</v>
+        <v>2.1712</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.03</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0665</v>
+        <v>0.0756</v>
       </c>
       <c r="J35" t="n">
-        <v>1.5295</v>
+        <v>1.7388</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.75</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2926</v>
+        <v>-0.3043</v>
       </c>
       <c r="J36" t="n">
-        <v>-6.7298</v>
+        <v>-6.9989</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.83</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7266</v>
+        <v>0.8299</v>
       </c>
       <c r="J37" t="n">
-        <v>16.7118</v>
+        <v>19.0877</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.39</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4421</v>
+        <v>0.5008</v>
       </c>
       <c r="J38" t="n">
-        <v>10.1683</v>
+        <v>11.5184</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.11</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1746</v>
+        <v>0.1906</v>
       </c>
       <c r="J39" t="n">
-        <v>4.0158</v>
+        <v>4.3838</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.72</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3298</v>
+        <v>-0.3391</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.5854</v>
+        <v>-7.7993</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.55</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4852</v>
+        <v>-0.4889</v>
       </c>
       <c r="J41" t="n">
-        <v>-11.1596</v>
+        <v>-11.2447</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.42</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>0.877</v>
       </c>
       <c r="J42" t="n">
-        <v>32.8</v>
+        <v>35.957</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.3</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6334</v>
+        <v>0.6962</v>
       </c>
       <c r="J43" t="n">
-        <v>25.9694</v>
+        <v>28.5442</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.06</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2149</v>
+        <v>0.2208</v>
       </c>
       <c r="J44" t="n">
-        <v>8.8109</v>
+        <v>9.0528</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.78</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.6914</v>
+        <v>-0.6462</v>
       </c>
       <c r="J45" t="n">
-        <v>-28.3474</v>
+        <v>-26.4942</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.76</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.7423999999999999</v>
+        <v>-0.6911</v>
       </c>
       <c r="J46" t="n">
-        <v>-30.4384</v>
+        <v>-28.3351</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.34</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5333</v>
+        <v>0.5946</v>
       </c>
       <c r="J47" t="n">
-        <v>21.8653</v>
+        <v>24.3786</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.07</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1765</v>
+        <v>0.1865</v>
       </c>
       <c r="J48" t="n">
-        <v>7.2365</v>
+        <v>7.6465</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.95</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0796</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>-3.2636</v>
+        <v>-3.6449</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.93</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1039</v>
+        <v>-0.1145</v>
       </c>
       <c r="J50" t="n">
-        <v>-4.2599</v>
+        <v>-4.6945</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.89</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1493</v>
+        <v>-0.1614</v>
       </c>
       <c r="J51" t="n">
-        <v>-6.1213</v>
+        <v>-6.6174</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.49</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8723</v>
+        <v>0.9586</v>
       </c>
       <c r="J52" t="n">
-        <v>18.3183</v>
+        <v>20.1306</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.39</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7398</v>
+        <v>0.8158</v>
       </c>
       <c r="J53" t="n">
-        <v>15.5358</v>
+        <v>17.1318</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.18</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4458</v>
+        <v>0.491</v>
       </c>
       <c r="J54" t="n">
-        <v>9.361800000000001</v>
+        <v>10.311</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.87</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4715</v>
+        <v>-0.4458</v>
       </c>
       <c r="J55" t="n">
-        <v>-9.9015</v>
+        <v>-9.361800000000001</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.74</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.8109</v>
+        <v>-0.7481</v>
       </c>
       <c r="J56" t="n">
-        <v>-17.0289</v>
+        <v>-15.7101</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.42</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6271</v>
+        <v>0.6975</v>
       </c>
       <c r="J57" t="n">
-        <v>13.1691</v>
+        <v>14.6475</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.41</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6172</v>
+        <v>0.6864</v>
       </c>
       <c r="J58" t="n">
-        <v>12.9612</v>
+        <v>14.4144</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.79</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2464</v>
+        <v>-0.2603</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.1744</v>
+        <v>-5.4663</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.78</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2563</v>
+        <v>-0.2701</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.3823</v>
+        <v>-5.6721</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.49</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5263</v>
+        <v>-0.5296999999999999</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.0523</v>
+        <v>-11.1237</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.38</v>
       </c>
       <c r="I62" t="n">
-        <v>0.5056</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="J62" t="n">
-        <v>9.606400000000001</v>
+        <v>10.621</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.95</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0639</v>
+        <v>-0.077</v>
       </c>
       <c r="J63" t="n">
-        <v>-1.2141</v>
+        <v>-1.463</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.91</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1115</v>
+        <v>-0.1266</v>
       </c>
       <c r="J64" t="n">
-        <v>-2.1185</v>
+        <v>-2.4054</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.65</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3686</v>
+        <v>-0.3816</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.0034</v>
+        <v>-7.2504</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.5</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.507</v>
+        <v>-0.5131</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.632999999999999</v>
+        <v>-9.748900000000001</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.67</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5958</v>
+        <v>0.6857</v>
       </c>
       <c r="J67" t="n">
-        <v>11.3202</v>
+        <v>13.0283</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.65</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5837</v>
+        <v>0.6717</v>
       </c>
       <c r="J68" t="n">
-        <v>11.0903</v>
+        <v>12.7623</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.16</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2191</v>
+        <v>0.2404</v>
       </c>
       <c r="J69" t="n">
-        <v>4.1629</v>
+        <v>4.5676</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.12</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1656</v>
+        <v>0.1873</v>
       </c>
       <c r="J70" t="n">
-        <v>3.1464</v>
+        <v>3.5587</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.02</v>
       </c>
       <c r="I71" t="n">
-        <v>0.0089</v>
+        <v>0.0257</v>
       </c>
       <c r="J71" t="n">
-        <v>0.1691</v>
+        <v>0.4883</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.76</v>
       </c>
       <c r="I72" t="n">
-        <v>1.2043</v>
+        <v>1.3121</v>
       </c>
       <c r="J72" t="n">
-        <v>27.6989</v>
+        <v>30.1783</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.19</v>
       </c>
       <c r="I73" t="n">
-        <v>0.4562</v>
+        <v>0.504</v>
       </c>
       <c r="J73" t="n">
-        <v>10.4926</v>
+        <v>11.592</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.02</v>
       </c>
       <c r="I74" t="n">
-        <v>0.0559</v>
+        <v>0.0736</v>
       </c>
       <c r="J74" t="n">
-        <v>1.2857</v>
+        <v>1.6928</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.01</v>
       </c>
       <c r="I75" t="n">
-        <v>0.0149</v>
+        <v>0.0322</v>
       </c>
       <c r="J75" t="n">
-        <v>0.3427</v>
+        <v>0.7406</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.85</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5347</v>
+        <v>-0.5013</v>
       </c>
       <c r="J76" t="n">
-        <v>-12.2981</v>
+        <v>-11.5299</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.21</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4179</v>
+        <v>0.4575</v>
       </c>
       <c r="J77" t="n">
-        <v>9.611700000000001</v>
+        <v>10.5225</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.06</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1751</v>
+        <v>0.1798</v>
       </c>
       <c r="J78" t="n">
-        <v>4.0273</v>
+        <v>4.1354</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.96</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.0591</v>
+        <v>-0.0694</v>
       </c>
       <c r="J79" t="n">
-        <v>-1.3593</v>
+        <v>-1.5962</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.85</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1816</v>
+        <v>-0.1966</v>
       </c>
       <c r="J80" t="n">
-        <v>-4.1768</v>
+        <v>-4.5218</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.65</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3771</v>
+        <v>-0.3882</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.673299999999999</v>
+        <v>-8.928599999999999</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>0.82</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.1902</v>
+        <v>-0.2103</v>
       </c>
       <c r="J82" t="n">
-        <v>-3.0432</v>
+        <v>-3.3648</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.79</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.2204</v>
+        <v>-0.2402</v>
       </c>
       <c r="J83" t="n">
-        <v>-3.5264</v>
+        <v>-3.8432</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.75</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2578</v>
+        <v>-0.2773</v>
       </c>
       <c r="J84" t="n">
-        <v>-4.1248</v>
+        <v>-4.4368</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.73</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2762</v>
+        <v>-0.2954</v>
       </c>
       <c r="J85" t="n">
-        <v>-4.4192</v>
+        <v>-4.7264</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3137</v>
+        <v>-0.3318</v>
       </c>
       <c r="J86" t="n">
-        <v>-5.0192</v>
+        <v>-5.3088</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.56</v>
       </c>
       <c r="I87" t="n">
-        <v>1.1719</v>
+        <v>1.1456</v>
       </c>
       <c r="J87" t="n">
-        <v>18.7504</v>
+        <v>18.3296</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.54</v>
       </c>
       <c r="I88" t="n">
-        <v>1.1481</v>
+        <v>1.1199</v>
       </c>
       <c r="J88" t="n">
-        <v>18.3696</v>
+        <v>17.9184</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.53</v>
       </c>
       <c r="I89" t="n">
-        <v>1.1362</v>
+        <v>1.1071</v>
       </c>
       <c r="J89" t="n">
-        <v>18.1792</v>
+        <v>17.7136</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.35</v>
       </c>
       <c r="I90" t="n">
-        <v>0.8611</v>
+        <v>0.8209</v>
       </c>
       <c r="J90" t="n">
-        <v>13.7776</v>
+        <v>13.1344</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>1.17</v>
       </c>
       <c r="I91" t="n">
-        <v>0.4382</v>
+        <v>0.4453</v>
       </c>
       <c r="J91" t="n">
-        <v>7.0112</v>
+        <v>7.1248</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.04</v>
       </c>
       <c r="I92" t="n">
-        <v>0.167</v>
+        <v>0.1617</v>
       </c>
       <c r="J92" t="n">
-        <v>3.674</v>
+        <v>3.5574</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.9</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1166</v>
+        <v>-0.1335</v>
       </c>
       <c r="J93" t="n">
-        <v>-2.5652</v>
+        <v>-2.937</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.8</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2186</v>
+        <v>-0.2366</v>
       </c>
       <c r="J94" t="n">
-        <v>-4.8092</v>
+        <v>-5.2052</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.73</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2863</v>
+        <v>-0.3032</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.2986</v>
+        <v>-6.6704</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3246</v>
+        <v>-0.3403</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.1412</v>
+        <v>-7.4866</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.57</v>
       </c>
       <c r="I97" t="n">
-        <v>1.2216</v>
+        <v>1.1916</v>
       </c>
       <c r="J97" t="n">
-        <v>26.8752</v>
+        <v>26.2152</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.22</v>
       </c>
       <c r="I98" t="n">
-        <v>0.6025</v>
+        <v>0.5845</v>
       </c>
       <c r="J98" t="n">
-        <v>13.255</v>
+        <v>12.859</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.21</v>
       </c>
       <c r="I99" t="n">
-        <v>0.5789</v>
+        <v>0.5633</v>
       </c>
       <c r="J99" t="n">
-        <v>12.7358</v>
+        <v>12.3926</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.13</v>
       </c>
       <c r="I100" t="n">
-        <v>0.377</v>
+        <v>0.3805</v>
       </c>
       <c r="J100" t="n">
-        <v>8.294</v>
+        <v>8.371</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.04</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1109</v>
+        <v>0.132</v>
       </c>
       <c r="J101" t="n">
-        <v>2.4398</v>
+        <v>2.904</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.39</v>
       </c>
       <c r="I102" t="n">
-        <v>0.9764</v>
+        <v>0.9207</v>
       </c>
       <c r="J102" t="n">
-        <v>19.528</v>
+        <v>18.414</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.31</v>
       </c>
       <c r="I103" t="n">
-        <v>0.8051</v>
+        <v>0.7653</v>
       </c>
       <c r="J103" t="n">
-        <v>16.102</v>
+        <v>15.306</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.31</v>
       </c>
       <c r="I104" t="n">
-        <v>0.8051</v>
+        <v>0.7653</v>
       </c>
       <c r="J104" t="n">
-        <v>16.102</v>
+        <v>15.306</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.25</v>
       </c>
       <c r="I105" t="n">
-        <v>0.6694</v>
+        <v>0.6449</v>
       </c>
       <c r="J105" t="n">
-        <v>13.388</v>
+        <v>12.898</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.96</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2279</v>
+        <v>-0.213</v>
       </c>
       <c r="J106" t="n">
-        <v>-4.558</v>
+        <v>-4.26</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.17</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4353</v>
+        <v>0.4202</v>
       </c>
       <c r="J107" t="n">
-        <v>8.706</v>
+        <v>8.404</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.93</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.0866</v>
+        <v>-0.1012</v>
       </c>
       <c r="J108" t="n">
-        <v>-1.732</v>
+        <v>-2.024</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.83</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1926</v>
+        <v>-0.2098</v>
       </c>
       <c r="J109" t="n">
-        <v>-3.852</v>
+        <v>-4.196</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.76</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2616</v>
+        <v>-0.2782</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.232</v>
+        <v>-5.564</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.63</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3855</v>
+        <v>-0.3981</v>
       </c>
       <c r="J111" t="n">
-        <v>-7.71</v>
+        <v>-7.962</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.24</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6749000000000001</v>
+        <v>0.6439</v>
       </c>
       <c r="J112" t="n">
-        <v>15.5227</v>
+        <v>14.8097</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.19</v>
       </c>
       <c r="I113" t="n">
-        <v>0.5517</v>
+        <v>0.5341</v>
       </c>
       <c r="J113" t="n">
-        <v>12.6891</v>
+        <v>12.2843</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.17</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5014</v>
+        <v>0.4888</v>
       </c>
       <c r="J114" t="n">
-        <v>11.5322</v>
+        <v>11.2424</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.06</v>
       </c>
       <c r="I115" t="n">
-        <v>0.203</v>
+        <v>0.2127</v>
       </c>
       <c r="J115" t="n">
-        <v>4.669</v>
+        <v>4.8921</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.95</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2301</v>
+        <v>-0.2231</v>
       </c>
       <c r="J116" t="n">
-        <v>-5.2923</v>
+        <v>-5.1313</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.13</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3206</v>
+        <v>0.3201</v>
       </c>
       <c r="J117" t="n">
-        <v>7.3738</v>
+        <v>7.3623</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.04</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1267</v>
+        <v>0.1323</v>
       </c>
       <c r="J118" t="n">
-        <v>2.9141</v>
+        <v>3.0429</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0078</v>
+        <v>0.0055</v>
       </c>
       <c r="J119" t="n">
-        <v>0.1794</v>
+        <v>0.1265</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.8</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2333</v>
+        <v>-0.248</v>
       </c>
       <c r="J120" t="n">
-        <v>-5.3659</v>
+        <v>-5.704</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.79</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2433</v>
+        <v>-0.2578</v>
       </c>
       <c r="J121" t="n">
-        <v>-5.5959</v>
+        <v>-5.9294</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.21</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5387</v>
+        <v>0.5109</v>
       </c>
       <c r="J122" t="n">
-        <v>11.8514</v>
+        <v>11.2398</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.82</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.1982</v>
+        <v>-0.2164</v>
       </c>
       <c r="J123" t="n">
-        <v>-4.3604</v>
+        <v>-4.7608</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.78</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2363</v>
+        <v>-0.2545</v>
       </c>
       <c r="J124" t="n">
-        <v>-5.1986</v>
+        <v>-5.599</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.7</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3131</v>
+        <v>-0.3295</v>
       </c>
       <c r="J125" t="n">
-        <v>-6.8882</v>
+        <v>-7.249</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.58</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4259</v>
+        <v>-0.4376</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.3698</v>
+        <v>-9.6272</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.35</v>
       </c>
       <c r="I127" t="n">
-        <v>0.9117</v>
+        <v>0.856</v>
       </c>
       <c r="J127" t="n">
-        <v>20.0574</v>
+        <v>18.832</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.33</v>
       </c>
       <c r="I128" t="n">
-        <v>0.8665</v>
+        <v>0.8162</v>
       </c>
       <c r="J128" t="n">
-        <v>19.063</v>
+        <v>17.9564</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.26</v>
       </c>
       <c r="I129" t="n">
-        <v>0.7043</v>
+        <v>0.6735</v>
       </c>
       <c r="J129" t="n">
-        <v>15.4946</v>
+        <v>14.817</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.01</v>
       </c>
       <c r="I130" t="n">
-        <v>0.0098</v>
+        <v>0.0287</v>
       </c>
       <c r="J130" t="n">
-        <v>0.2156</v>
+        <v>0.6314</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.98</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.1412</v>
+        <v>-0.1324</v>
       </c>
       <c r="J131" t="n">
-        <v>-3.1064</v>
+        <v>-2.9128</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.93</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.0508</v>
+        <v>-0.0733</v>
       </c>
       <c r="J132" t="n">
-        <v>-0.8636</v>
+        <v>-1.2461</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.83</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.1686</v>
+        <v>-0.1913</v>
       </c>
       <c r="J133" t="n">
-        <v>-2.8662</v>
+        <v>-3.2521</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.73</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.2704</v>
+        <v>-0.291</v>
       </c>
       <c r="J134" t="n">
-        <v>-4.5968</v>
+        <v>-4.947</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.54</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.4457</v>
+        <v>-0.4591</v>
       </c>
       <c r="J135" t="n">
-        <v>-7.5769</v>
+        <v>-7.8047</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.48</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5018</v>
+        <v>-0.5118</v>
       </c>
       <c r="J136" t="n">
-        <v>-8.5306</v>
+        <v>-8.7006</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.72</v>
       </c>
       <c r="I137" t="n">
-        <v>1.3891</v>
+        <v>1.3723</v>
       </c>
       <c r="J137" t="n">
-        <v>23.6147</v>
+        <v>23.3291</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.37</v>
       </c>
       <c r="I138" t="n">
-        <v>0.9244</v>
+        <v>0.8731</v>
       </c>
       <c r="J138" t="n">
-        <v>15.7148</v>
+        <v>14.8427</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.26</v>
       </c>
       <c r="I139" t="n">
-        <v>0.6843</v>
+        <v>0.66</v>
       </c>
       <c r="J139" t="n">
-        <v>11.6331</v>
+        <v>11.22</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.2</v>
       </c>
       <c r="I140" t="n">
-        <v>0.542</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="J140" t="n">
-        <v>9.214</v>
+        <v>9.057600000000001</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3062</v>
+        <v>-0.2843</v>
       </c>
       <c r="J141" t="n">
-        <v>-5.2054</v>
+        <v>-4.8331</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.69</v>
       </c>
       <c r="I142" t="n">
-        <v>0.774</v>
+        <v>0.7725</v>
       </c>
       <c r="J142" t="n">
-        <v>13.158</v>
+        <v>13.1325</v>
       </c>
     </row>
     <row r="143">
@@ -8109,10 +8109,10 @@
         <v>1.41</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4935</v>
+        <v>0.5089</v>
       </c>
       <c r="J144" t="n">
-        <v>8.3895</v>
+        <v>8.651300000000001</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.36</v>
       </c>
       <c r="I145" t="n">
-        <v>0.4398</v>
+        <v>0.4577</v>
       </c>
       <c r="J145" t="n">
-        <v>7.4766</v>
+        <v>7.7809</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.24</v>
       </c>
       <c r="I146" t="n">
-        <v>0.3026</v>
+        <v>0.3256</v>
       </c>
       <c r="J146" t="n">
-        <v>5.1442</v>
+        <v>5.5352</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.26</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5309</v>
+        <v>0.503</v>
       </c>
       <c r="J147" t="n">
-        <v>9.0253</v>
+        <v>8.551</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.67</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.3298</v>
+        <v>-0.3479</v>
       </c>
       <c r="J148" t="n">
-        <v>-5.6066</v>
+        <v>-5.9143</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.65</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.3485</v>
+        <v>-0.3659</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.9245</v>
+        <v>-6.2203</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.64</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3579</v>
+        <v>-0.3749</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.0843</v>
+        <v>-6.3733</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.47</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5165</v>
+        <v>-0.5248</v>
       </c>
       <c r="J151" t="n">
-        <v>-8.7805</v>
+        <v>-8.9216</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.35</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6869</v>
+        <v>0.6633</v>
       </c>
       <c r="J152" t="n">
-        <v>15.1118</v>
+        <v>14.5926</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.2</v>
       </c>
       <c r="I153" t="n">
-        <v>0.4262</v>
+        <v>0.4246</v>
       </c>
       <c r="J153" t="n">
-        <v>9.3764</v>
+        <v>9.341200000000001</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.13</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2958</v>
+        <v>0.302</v>
       </c>
       <c r="J154" t="n">
-        <v>6.5076</v>
+        <v>6.644</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.78</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2637</v>
+        <v>-0.2758</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.8014</v>
+        <v>-6.0676</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.75</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.293</v>
+        <v>-0.3046</v>
       </c>
       <c r="J156" t="n">
-        <v>-6.446</v>
+        <v>-6.7012</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.44</v>
       </c>
       <c r="I157" t="n">
-        <v>1.0745</v>
+        <v>1.0274</v>
       </c>
       <c r="J157" t="n">
-        <v>23.639</v>
+        <v>22.6028</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.21</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5923</v>
+        <v>0.5723</v>
       </c>
       <c r="J158" t="n">
-        <v>13.0306</v>
+        <v>12.5906</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.15</v>
       </c>
       <c r="I159" t="n">
-        <v>0.4451</v>
+        <v>0.439</v>
       </c>
       <c r="J159" t="n">
-        <v>9.792199999999999</v>
+        <v>9.657999999999999</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.14</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4198</v>
+        <v>0.4158</v>
       </c>
       <c r="J160" t="n">
-        <v>9.2356</v>
+        <v>9.147600000000001</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.84</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5591</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="J161" t="n">
-        <v>-12.3002</v>
+        <v>-11.5214</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.14</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3346</v>
+        <v>0.3345</v>
       </c>
       <c r="J162" t="n">
-        <v>8.0304</v>
+        <v>8.028</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.13</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3149</v>
+        <v>0.3159</v>
       </c>
       <c r="J163" t="n">
-        <v>7.5576</v>
+        <v>7.5816</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.01</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0427</v>
+        <v>0.0469</v>
       </c>
       <c r="J164" t="n">
-        <v>1.0248</v>
+        <v>1.1256</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.87</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1634</v>
+        <v>-0.1775</v>
       </c>
       <c r="J165" t="n">
-        <v>-3.9216</v>
+        <v>-4.26</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.7</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3328</v>
+        <v>-0.345</v>
       </c>
       <c r="J166" t="n">
-        <v>-7.9872</v>
+        <v>-8.279999999999999</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.49</v>
       </c>
       <c r="I167" t="n">
-        <v>1.1551</v>
+        <v>1.1138</v>
       </c>
       <c r="J167" t="n">
-        <v>27.7224</v>
+        <v>26.7312</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.43</v>
       </c>
       <c r="I168" t="n">
-        <v>1.0752</v>
+        <v>1.0253</v>
       </c>
       <c r="J168" t="n">
-        <v>25.8048</v>
+        <v>24.6072</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.3</v>
       </c>
       <c r="I169" t="n">
-        <v>0.8255</v>
+        <v>0.7752</v>
       </c>
       <c r="J169" t="n">
-        <v>19.812</v>
+        <v>18.6048</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.73</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.8282</v>
+        <v>-0.7645999999999999</v>
       </c>
       <c r="J170" t="n">
-        <v>-19.8768</v>
+        <v>-18.3504</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.57</v>
       </c>
       <c r="I171" t="n">
-        <v>-1.2112</v>
+        <v>-1.0957</v>
       </c>
       <c r="J171" t="n">
-        <v>-29.0688</v>
+        <v>-26.2968</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.32</v>
       </c>
       <c r="I172" t="n">
-        <v>0.655</v>
+        <v>0.6312</v>
       </c>
       <c r="J172" t="n">
-        <v>30.785</v>
+        <v>29.6664</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.25</v>
       </c>
       <c r="I173" t="n">
-        <v>0.532</v>
+        <v>0.5192</v>
       </c>
       <c r="J173" t="n">
-        <v>25.004</v>
+        <v>24.4024</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.07</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1854</v>
+        <v>0.1929</v>
       </c>
       <c r="J174" t="n">
-        <v>8.713800000000001</v>
+        <v>9.0663</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.72</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3163</v>
+        <v>-0.3285</v>
       </c>
       <c r="J175" t="n">
-        <v>-14.8661</v>
+        <v>-15.4395</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.6</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4284</v>
+        <v>-0.4366</v>
       </c>
       <c r="J176" t="n">
-        <v>-20.1348</v>
+        <v>-20.5202</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.26</v>
       </c>
       <c r="I177" t="n">
-        <v>0.7302999999999999</v>
+        <v>0.6915</v>
       </c>
       <c r="J177" t="n">
-        <v>34.3241</v>
+        <v>32.5005</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.17</v>
       </c>
       <c r="I178" t="n">
-        <v>0.5065</v>
+        <v>0.4923</v>
       </c>
       <c r="J178" t="n">
-        <v>23.8055</v>
+        <v>23.1381</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.12</v>
       </c>
       <c r="I179" t="n">
-        <v>0.3761</v>
+        <v>0.3736</v>
       </c>
       <c r="J179" t="n">
-        <v>17.6767</v>
+        <v>17.5592</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.02</v>
       </c>
       <c r="I180" t="n">
-        <v>0.0721</v>
+        <v>0.0848</v>
       </c>
       <c r="J180" t="n">
-        <v>3.3887</v>
+        <v>3.9856</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2569</v>
+        <v>-0.2498</v>
       </c>
       <c r="J181" t="n">
-        <v>-12.0743</v>
+        <v>-11.7406</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.73</v>
       </c>
       <c r="I182" t="n">
-        <v>1.4108</v>
+        <v>1.3936</v>
       </c>
       <c r="J182" t="n">
-        <v>29.6268</v>
+        <v>29.2656</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.41</v>
       </c>
       <c r="I183" t="n">
-        <v>1.0068</v>
+        <v>0.9537</v>
       </c>
       <c r="J183" t="n">
-        <v>21.1428</v>
+        <v>20.0277</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.36</v>
       </c>
       <c r="I184" t="n">
-        <v>0.9117</v>
+        <v>0.86</v>
       </c>
       <c r="J184" t="n">
-        <v>19.1457</v>
+        <v>18.06</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.03</v>
       </c>
       <c r="I185" t="n">
-        <v>0.0693</v>
+        <v>0.0936</v>
       </c>
       <c r="J185" t="n">
-        <v>1.4553</v>
+        <v>1.9656</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.78</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.7403</v>
+        <v>-0.6807</v>
       </c>
       <c r="J186" t="n">
-        <v>-15.5463</v>
+        <v>-14.2947</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.22</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4779</v>
+        <v>0.4695</v>
       </c>
       <c r="J187" t="n">
-        <v>10.0359</v>
+        <v>9.859500000000001</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.11</v>
       </c>
       <c r="I188" t="n">
-        <v>0.2687</v>
+        <v>0.2734</v>
       </c>
       <c r="J188" t="n">
-        <v>5.6427</v>
+        <v>5.7414</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.02</v>
       </c>
       <c r="I189" t="n">
-        <v>0.0674</v>
+        <v>0.0743</v>
       </c>
       <c r="J189" t="n">
-        <v>1.4154</v>
+        <v>1.5603</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.95</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.0751</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="J190" t="n">
-        <v>-1.5771</v>
+        <v>-1.7955</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.66</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.373</v>
+        <v>-0.3833</v>
       </c>
       <c r="J191" t="n">
-        <v>-7.833</v>
+        <v>-8.049300000000001</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.89</v>
       </c>
       <c r="I192" t="n">
-        <v>1.6239</v>
+        <v>1.6138</v>
       </c>
       <c r="J192" t="n">
-        <v>35.7258</v>
+        <v>35.5036</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.12</v>
       </c>
       <c r="I193" t="n">
-        <v>0.3578</v>
+        <v>0.3612</v>
       </c>
       <c r="J193" t="n">
-        <v>7.8716</v>
+        <v>7.9464</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.04</v>
       </c>
       <c r="I194" t="n">
-        <v>0.1192</v>
+        <v>0.1378</v>
       </c>
       <c r="J194" t="n">
-        <v>2.6224</v>
+        <v>3.0316</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.98</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1447</v>
+        <v>-0.1349</v>
       </c>
       <c r="J195" t="n">
-        <v>-3.1834</v>
+        <v>-2.9678</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.97</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.182</v>
+        <v>-0.1715</v>
       </c>
       <c r="J196" t="n">
-        <v>-4.004</v>
+        <v>-3.773</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.16</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3897</v>
+        <v>0.3829</v>
       </c>
       <c r="J197" t="n">
-        <v>8.573399999999999</v>
+        <v>8.4238</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.15</v>
       </c>
       <c r="I198" t="n">
-        <v>0.3701</v>
+        <v>0.3646</v>
       </c>
       <c r="J198" t="n">
-        <v>8.142200000000001</v>
+        <v>8.0212</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.83</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1996</v>
+        <v>-0.2152</v>
       </c>
       <c r="J199" t="n">
-        <v>-4.3912</v>
+        <v>-4.7344</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.77</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2596</v>
+        <v>-0.2746</v>
       </c>
       <c r="J200" t="n">
-        <v>-5.7112</v>
+        <v>-6.0412</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.71</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3177</v>
+        <v>-0.3313</v>
       </c>
       <c r="J201" t="n">
-        <v>-6.9894</v>
+        <v>-7.2886</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.63</v>
       </c>
       <c r="I202" t="n">
-        <v>1.3012</v>
+        <v>1.2754</v>
       </c>
       <c r="J202" t="n">
-        <v>28.6264</v>
+        <v>28.0588</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.35</v>
       </c>
       <c r="I203" t="n">
-        <v>0.9025</v>
+        <v>0.8494</v>
       </c>
       <c r="J203" t="n">
-        <v>19.855</v>
+        <v>18.6868</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.16</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4594</v>
+        <v>0.4546</v>
       </c>
       <c r="J204" t="n">
-        <v>10.1068</v>
+        <v>10.0012</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.14</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4076</v>
+        <v>0.4075</v>
       </c>
       <c r="J205" t="n">
-        <v>8.9672</v>
+        <v>8.965</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.8</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.6788999999999999</v>
+        <v>-0.628</v>
       </c>
       <c r="J206" t="n">
-        <v>-14.9358</v>
+        <v>-13.816</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.11</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3061</v>
+        <v>0.3008</v>
       </c>
       <c r="J207" t="n">
-        <v>6.7342</v>
+        <v>6.6176</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.99</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.0069</v>
+        <v>-0.0148</v>
       </c>
       <c r="J208" t="n">
-        <v>-0.1518</v>
+        <v>-0.3256</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.92</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1004</v>
+        <v>-0.1151</v>
       </c>
       <c r="J209" t="n">
-        <v>-2.2088</v>
+        <v>-2.5322</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.8</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2244</v>
+        <v>-0.241</v>
       </c>
       <c r="J210" t="n">
-        <v>-4.9368</v>
+        <v>-5.302</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.58</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.434</v>
+        <v>-0.444</v>
       </c>
       <c r="J211" t="n">
-        <v>-9.548</v>
+        <v>-9.768000000000001</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.41</v>
       </c>
       <c r="I212" t="n">
-        <v>1.0495</v>
+        <v>0.9937</v>
       </c>
       <c r="J212" t="n">
-        <v>25.188</v>
+        <v>23.8488</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.24</v>
       </c>
       <c r="I213" t="n">
-        <v>0.6829</v>
+        <v>0.6495</v>
       </c>
       <c r="J213" t="n">
-        <v>16.3896</v>
+        <v>15.588</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.16</v>
       </c>
       <c r="I214" t="n">
-        <v>0.4819</v>
+        <v>0.4699</v>
       </c>
       <c r="J214" t="n">
-        <v>11.5656</v>
+        <v>11.2776</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.92</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3176</v>
+        <v>-0.3068</v>
       </c>
       <c r="J215" t="n">
-        <v>-7.6224</v>
+        <v>-7.3632</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.76</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.7516</v>
+        <v>-0.6976</v>
       </c>
       <c r="J216" t="n">
-        <v>-18.0384</v>
+        <v>-16.7424</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.46</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8748</v>
+        <v>0.8308</v>
       </c>
       <c r="J217" t="n">
-        <v>20.9952</v>
+        <v>19.9392</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.09</v>
       </c>
       <c r="I218" t="n">
-        <v>0.2196</v>
+        <v>0.2282</v>
       </c>
       <c r="J218" t="n">
-        <v>5.2704</v>
+        <v>5.4768</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.99</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0229</v>
+        <v>-0.027</v>
       </c>
       <c r="J219" t="n">
-        <v>-0.5496</v>
+        <v>-0.648</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.9</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1373</v>
+        <v>-0.1493</v>
       </c>
       <c r="J220" t="n">
-        <v>-3.2952</v>
+        <v>-3.5832</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.7</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3393</v>
+        <v>-0.3501</v>
       </c>
       <c r="J221" t="n">
-        <v>-8.1432</v>
+        <v>-8.4024</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.72</v>
       </c>
       <c r="I222" t="n">
-        <v>1.3775</v>
+        <v>1.362</v>
       </c>
       <c r="J222" t="n">
-        <v>24.795</v>
+        <v>24.516</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.36</v>
       </c>
       <c r="I223" t="n">
-        <v>0.8948</v>
+        <v>0.8481</v>
       </c>
       <c r="J223" t="n">
-        <v>16.1064</v>
+        <v>15.2658</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.28</v>
       </c>
       <c r="I224" t="n">
-        <v>0.7211</v>
+        <v>0.6944</v>
       </c>
       <c r="J224" t="n">
-        <v>12.9798</v>
+        <v>12.4992</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.23</v>
       </c>
       <c r="I225" t="n">
-        <v>0.6045</v>
+        <v>0.5908</v>
       </c>
       <c r="J225" t="n">
-        <v>10.881</v>
+        <v>10.6344</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.14</v>
       </c>
       <c r="I226" t="n">
-        <v>0.3783</v>
+        <v>0.3872</v>
       </c>
       <c r="J226" t="n">
-        <v>6.8094</v>
+        <v>6.9696</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.06</v>
       </c>
       <c r="I227" t="n">
-        <v>0.2149</v>
+        <v>0.2089</v>
       </c>
       <c r="J227" t="n">
-        <v>3.8682</v>
+        <v>3.7602</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.0848</v>
       </c>
       <c r="J228" t="n">
-        <v>-1.251</v>
+        <v>-1.5264</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.91</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1055</v>
+        <v>-0.122</v>
       </c>
       <c r="J229" t="n">
-        <v>-1.899</v>
+        <v>-2.196</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.65</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3627</v>
+        <v>-0.3769</v>
       </c>
       <c r="J230" t="n">
-        <v>-6.5286</v>
+        <v>-6.7842</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.61</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4002</v>
+        <v>-0.4128</v>
       </c>
       <c r="J231" t="n">
-        <v>-7.2036</v>
+        <v>-7.4304</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/6868/event_6868_evp_summary.xlsx
+++ b/database/event/6868/event_6868_evp_summary.xlsx
@@ -492,93 +492,93 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>sdy</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.8107</v>
+        <v>6.093</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7483</v>
+        <v>0.7846</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0209</v>
+        <v>2.1078</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8107</v>
+        <v>6.093</v>
       </c>
       <c r="F2" t="n">
-        <v>3.7623</v>
+        <v>2.7305</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0484</v>
+        <v>2.9435</v>
       </c>
       <c r="H2" t="n">
-        <v>7.5192</v>
+        <v>4.1149</v>
       </c>
       <c r="I2" t="n">
-        <v>4.0603</v>
+        <v>2.222</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0484</v>
+        <v>2.9435</v>
       </c>
       <c r="K2" t="n">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="L2" t="n">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="M2" t="n">
-        <v>6.1087</v>
+        <v>5.1655</v>
       </c>
       <c r="N2" t="n">
-        <v>252</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sdy</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.674</v>
+        <v>6.0879</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7307</v>
+        <v>0.784</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9587</v>
+        <v>2.1055</v>
       </c>
       <c r="E3" t="n">
-        <v>5.674</v>
+        <v>6.0879</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7305</v>
+        <v>3.7623</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9435</v>
+        <v>2.0484</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1149</v>
+        <v>7.5192</v>
       </c>
       <c r="I3" t="n">
-        <v>2.222</v>
+        <v>4.0603</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9435</v>
+        <v>2.0484</v>
       </c>
       <c r="K3" t="n">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="L3" t="n">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="M3" t="n">
-        <v>5.1655</v>
+        <v>6.1087</v>
       </c>
       <c r="N3" t="n">
-        <v>160</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4">
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.4706</v>
+        <v>4.6115</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5757</v>
+        <v>0.5938</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4109</v>
+        <v>1.446</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4706</v>
+        <v>4.6115</v>
       </c>
       <c r="F4" t="n">
         <v>3.6677</v>
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.5227</v>
+        <v>3.5976</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4536</v>
+        <v>0.4633</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9794</v>
+        <v>0.9931</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5227</v>
+        <v>3.5976</v>
       </c>
       <c r="F5" t="n">
         <v>2.4692</v>
@@ -680,16 +680,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.485</v>
+        <v>3.5613</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4488</v>
+        <v>0.4586</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.9769</v>
       </c>
       <c r="E6" t="n">
-        <v>3.485</v>
+        <v>3.5613</v>
       </c>
       <c r="F6" t="n">
         <v>1.4593</v>
@@ -722,35 +722,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Calyx</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.2926</v>
+        <v>3.2543</v>
       </c>
       <c r="C7" t="n">
-        <v>0.424</v>
+        <v>0.4191</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8747</v>
+        <v>0.8398</v>
       </c>
       <c r="E7" t="n">
-        <v>3.2926</v>
+        <v>3.2543</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2542</v>
+        <v>2.6845</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0384</v>
+        <v>0.606</v>
       </c>
       <c r="H7" t="n">
-        <v>5.8425</v>
+        <v>3.963</v>
       </c>
       <c r="I7" t="n">
-        <v>3.1549</v>
+        <v>2.14</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0384</v>
+        <v>0.606</v>
       </c>
       <c r="K7" t="n">
         <v>101</v>
@@ -759,7 +759,7 @@
         <v>151</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1933</v>
+        <v>2.746</v>
       </c>
       <c r="N7" t="n">
         <v>252</v>
@@ -768,35 +768,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>Calyx</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2905</v>
+        <v>3.1443</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4237</v>
+        <v>0.4049</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8737</v>
+        <v>0.7907</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2905</v>
+        <v>3.1443</v>
       </c>
       <c r="F8" t="n">
-        <v>2.6845</v>
+        <v>3.2542</v>
       </c>
       <c r="G8" t="n">
-        <v>0.606</v>
+        <v>0.0384</v>
       </c>
       <c r="H8" t="n">
-        <v>3.963</v>
+        <v>5.8425</v>
       </c>
       <c r="I8" t="n">
-        <v>2.14</v>
+        <v>3.1549</v>
       </c>
       <c r="J8" t="n">
-        <v>0.606</v>
+        <v>0.0384</v>
       </c>
       <c r="K8" t="n">
         <v>101</v>
@@ -805,7 +805,7 @@
         <v>151</v>
       </c>
       <c r="M8" t="n">
-        <v>2.746</v>
+        <v>3.1933</v>
       </c>
       <c r="N8" t="n">
         <v>252</v>
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.0845</v>
+        <v>3.1357</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3972</v>
+        <v>0.4038</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7799</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0845</v>
+        <v>3.1357</v>
       </c>
       <c r="F9" t="n">
         <v>2.4829</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6745</v>
+        <v>2.8016</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3444</v>
+        <v>0.3608</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5933</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6745</v>
+        <v>2.8016</v>
       </c>
       <c r="F10" t="n">
-        <v>2.7773</v>
+        <v>2.7644</v>
       </c>
       <c r="G10" t="n">
         <v>-0.1028</v>
       </c>
       <c r="H10" t="n">
-        <v>4.2691</v>
+        <v>4.2265</v>
       </c>
       <c r="I10" t="n">
-        <v>2.3053</v>
+        <v>2.2823</v>
       </c>
       <c r="J10" t="n">
         <v>-0.1028</v>
@@ -897,7 +897,7 @@
         <v>93</v>
       </c>
       <c r="M10" t="n">
-        <v>2.2025</v>
+        <v>2.1795</v>
       </c>
       <c r="N10" t="n">
         <v>162</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>volt</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.607</v>
+        <v>2.4811</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3357</v>
+        <v>0.3195</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5626</v>
+        <v>0.4944</v>
       </c>
       <c r="E11" t="n">
-        <v>2.607</v>
+        <v>2.4811</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2932</v>
+        <v>2.3362</v>
       </c>
       <c r="G11" t="n">
-        <v>1.3138</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2932</v>
+        <v>2.3883</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6983</v>
+        <v>2.3883</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3138</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="L11" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.0121</v>
+        <v>2.3883</v>
       </c>
       <c r="N11" t="n">
-        <v>175</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DemQQ</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.4278</v>
+        <v>2.4539</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3126</v>
+        <v>0.316</v>
       </c>
       <c r="D12" t="n">
-        <v>0.481</v>
+        <v>0.4823</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4278</v>
+        <v>2.4539</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4947</v>
+        <v>1.2932</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0669</v>
+        <v>1.3138</v>
       </c>
       <c r="H12" t="n">
-        <v>3.3367</v>
+        <v>1.2932</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8018</v>
+        <v>0.6983</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.0669</v>
+        <v>1.3138</v>
       </c>
       <c r="K12" t="n">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c r="L12" t="n">
-        <v>121</v>
+        <v>63</v>
       </c>
       <c r="M12" t="n">
-        <v>1.7349</v>
+        <v>2.0121</v>
       </c>
       <c r="N12" t="n">
-        <v>160</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -1002,16 +1002,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.3247</v>
+        <v>2.4052</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2994</v>
+        <v>0.3097</v>
       </c>
       <c r="D13" t="n">
-        <v>0.434</v>
+        <v>0.4605</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3247</v>
+        <v>2.4052</v>
       </c>
       <c r="F13" t="n">
         <v>2.7328</v>
@@ -1044,47 +1044,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>volt</t>
+          <t>DemQQ</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3055</v>
+        <v>2.2708</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2969</v>
+        <v>0.2924</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4253</v>
+        <v>0.4005</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3055</v>
+        <v>2.2708</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3055</v>
+        <v>2.4947</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.0669</v>
       </c>
       <c r="H14" t="n">
-        <v>2.321</v>
+        <v>3.3367</v>
       </c>
       <c r="I14" t="n">
-        <v>2.321</v>
+        <v>1.8018</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.0669</v>
       </c>
       <c r="K14" t="n">
-        <v>128</v>
+        <v>39</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="M14" t="n">
-        <v>2.321</v>
+        <v>1.7349</v>
       </c>
       <c r="N14" t="n">
-        <v>128</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15">
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2366</v>
+        <v>2.2683</v>
       </c>
       <c r="C15" t="n">
-        <v>0.288</v>
+        <v>0.2921</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3939</v>
+        <v>0.3994</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2366</v>
+        <v>2.2683</v>
       </c>
       <c r="F15" t="n">
         <v>2.6776</v>
@@ -1136,139 +1136,139 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>brnz4n</t>
+          <t>Djoko</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.9466</v>
+        <v>1.9891</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2507</v>
+        <v>0.2561</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2619</v>
+        <v>0.2747</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9466</v>
+        <v>1.9891</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9471000000000001</v>
+        <v>1.8138</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9995000000000001</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9471000000000001</v>
+        <v>1.8138</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5114</v>
+        <v>1.8138</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9995000000000001</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="L16" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.5109</v>
+        <v>1.8138</v>
       </c>
       <c r="N16" t="n">
-        <v>162</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>brnz4n</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.8371</v>
+        <v>1.9707</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2366</v>
+        <v>0.2538</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2121</v>
+        <v>0.2664</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8371</v>
+        <v>1.9707</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2376</v>
+        <v>0.8641</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5995</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2376</v>
+        <v>0.8641</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6683</v>
+        <v>0.4666</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5995</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="L17" t="n">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="M17" t="n">
-        <v>1.2678</v>
+        <v>1.4661</v>
       </c>
       <c r="N17" t="n">
-        <v>175</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Djoko</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8138</v>
+        <v>1.6602</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2336</v>
+        <v>0.2138</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2015</v>
+        <v>0.1278</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8138</v>
+        <v>1.6602</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8138</v>
+        <v>1.2376</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.5995</v>
       </c>
       <c r="H18" t="n">
-        <v>1.8138</v>
+        <v>1.2376</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8138</v>
+        <v>0.6683</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.5995</v>
       </c>
       <c r="K18" t="n">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M18" t="n">
-        <v>1.8138</v>
+        <v>1.2678</v>
       </c>
       <c r="N18" t="n">
-        <v>85</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19">
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.5883</v>
+        <v>1.6169</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2045</v>
+        <v>0.2082</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0988</v>
+        <v>0.1084</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5883</v>
+        <v>1.6169</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8259</v>
+        <v>0.8276</v>
       </c>
       <c r="G19" t="n">
         <v>0.7624</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8259</v>
+        <v>0.8276</v>
       </c>
       <c r="I19" t="n">
-        <v>0.446</v>
+        <v>0.4469</v>
       </c>
       <c r="J19" t="n">
         <v>0.7624</v>
@@ -1311,7 +1311,7 @@
         <v>93</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2084</v>
+        <v>1.2093</v>
       </c>
       <c r="N19" t="n">
         <v>162</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>acoR</t>
+          <t>Ex3rcice</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.1251</v>
+        <v>1.3091</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1449</v>
+        <v>0.1686</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.112</v>
+        <v>-0.0291</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1251</v>
+        <v>1.3091</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1251</v>
+        <v>0.9799</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1251</v>
+        <v>0.9799</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1251</v>
+        <v>0.9799</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>128</v>
+        <v>85</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1251</v>
+        <v>0.9799</v>
       </c>
       <c r="N20" t="n">
-        <v>128</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ex3rcice</t>
+          <t>acoR</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9799</v>
+        <v>0.9908</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1262</v>
+        <v>0.1276</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1781</v>
+        <v>-0.1713</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9799</v>
+        <v>0.9908</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9799</v>
+        <v>1.1236</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9799</v>
+        <v>1.1236</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9799</v>
+        <v>1.1236</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9799</v>
+        <v>1.1236</v>
       </c>
       <c r="N21" t="n">
-        <v>85</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22">
@@ -1416,16 +1416,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7892</v>
+        <v>0.8074</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1016</v>
+        <v>0.104</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2649</v>
+        <v>-0.2532</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7892</v>
+        <v>0.8074</v>
       </c>
       <c r="F22" t="n">
         <v>0.7892</v>
@@ -1458,139 +1458,139 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6591</v>
+        <v>0.7236</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0849</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3242</v>
+        <v>-0.2906</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6591</v>
+        <v>0.7236</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6591</v>
+        <v>0.6783</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6591</v>
+        <v>0.6783</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6591</v>
+        <v>0.6783</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6591</v>
+        <v>0.6783</v>
       </c>
       <c r="N23" t="n">
-        <v>85</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>MarKE</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6469</v>
+        <v>0.6041</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0833</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3297</v>
+        <v>-0.344</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6469</v>
+        <v>0.6041</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6469</v>
+        <v>0.3277</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6469</v>
+        <v>0.3277</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6469</v>
+        <v>0.3277</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>128</v>
+        <v>83</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6469</v>
+        <v>0.3277</v>
       </c>
       <c r="N24" t="n">
-        <v>128</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5044</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="C25" t="n">
-        <v>0.065</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3946</v>
+        <v>-0.3543</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5044</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3193</v>
+        <v>0.6591</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1851</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3193</v>
+        <v>0.6591</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1724</v>
+        <v>0.6591</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1851</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="L25" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3575</v>
+        <v>0.6591</v>
       </c>
       <c r="N25" t="n">
-        <v>252</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26">
@@ -1600,16 +1600,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3589</v>
+        <v>0.4799</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0462</v>
+        <v>0.0618</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4608</v>
+        <v>-0.3995</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3589</v>
+        <v>0.4799</v>
       </c>
       <c r="F26" t="n">
         <v>0.3589</v>
@@ -1642,47 +1642,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MarKE</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3277</v>
+        <v>0.2452</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0422</v>
+        <v>0.0316</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.475</v>
+        <v>-0.5043</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3277</v>
+        <v>0.2452</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3277</v>
+        <v>0.3193</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.1851</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3277</v>
+        <v>0.3193</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3277</v>
+        <v>0.1724</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.1851</v>
       </c>
       <c r="K27" t="n">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3277</v>
+        <v>0.3575</v>
       </c>
       <c r="N27" t="n">
-        <v>83</v>
+        <v>252</v>
       </c>
     </row>
     <row r="28">
@@ -1692,16 +1692,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2692</v>
+        <v>0.1297</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0347</v>
+        <v>0.0167</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5017</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2692</v>
+        <v>0.1297</v>
       </c>
       <c r="F28" t="n">
         <v>0.2692</v>
@@ -1738,16 +1738,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.208</v>
+        <v>0.0781</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0268</v>
+        <v>0.0101</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5295</v>
+        <v>-0.5789</v>
       </c>
       <c r="E29" t="n">
-        <v>0.208</v>
+        <v>0.0781</v>
       </c>
       <c r="F29" t="n">
         <v>0.208</v>
@@ -1780,35 +1780,35 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>drop</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0751</v>
+        <v>-0.0316</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0097</v>
+        <v>-0.0041</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6584</v>
+        <v>-0.6279</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0751</v>
+        <v>-0.0316</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5941</v>
+        <v>-0.7106</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.6692</v>
+        <v>0.3409</v>
       </c>
       <c r="H30" t="n">
-        <v>0.5941</v>
+        <v>-0.7106</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3208</v>
+        <v>-0.3837</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.6692</v>
+        <v>0.3409</v>
       </c>
       <c r="K30" t="n">
         <v>69</v>
@@ -1817,7 +1817,7 @@
         <v>93</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.3484</v>
+        <v>-0.0428</v>
       </c>
       <c r="N30" t="n">
         <v>162</v>
@@ -1826,35 +1826,35 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>drop</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3715</v>
+        <v>-0.3245</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0478</v>
+        <v>-0.0418</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7933</v>
+        <v>-0.7588</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3715</v>
+        <v>-0.3245</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.7124</v>
+        <v>0.5961</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3409</v>
+        <v>-0.6692</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.7124</v>
+        <v>0.5961</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3847</v>
+        <v>0.3219</v>
       </c>
       <c r="J31" t="n">
-        <v>0.3409</v>
+        <v>-0.6692</v>
       </c>
       <c r="K31" t="n">
         <v>69</v>
@@ -1863,7 +1863,7 @@
         <v>93</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.04380000000000001</v>
+        <v>-0.3473</v>
       </c>
       <c r="N31" t="n">
         <v>162</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>kaze</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4329</v>
+        <v>-0.4759</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0557</v>
+        <v>-0.0613</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8213</v>
+        <v>-0.8264</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4329</v>
+        <v>-0.4759</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.4329</v>
+        <v>-0.4925</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4329</v>
+        <v>-0.4925</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4329</v>
+        <v>-0.4925</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4329</v>
+        <v>-0.4925</v>
       </c>
       <c r="N32" t="n">
-        <v>85</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kaze</t>
+          <t>cJ dA K1nG</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4925</v>
+        <v>-0.7254</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0634</v>
+        <v>-0.0934</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8484</v>
+        <v>-0.9378</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4925</v>
+        <v>-0.7254</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.4925</v>
+        <v>-0.6794</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4925</v>
+        <v>-0.6794</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4925</v>
+        <v>-0.6794</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4925</v>
+        <v>-0.6794</v>
       </c>
       <c r="N33" t="n">
-        <v>57</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34">
@@ -1968,16 +1968,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.5248</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0965</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8631</v>
+        <v>-0.9486</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5248</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="F34" t="n">
         <v>-0.5248</v>
@@ -2010,47 +2010,47 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cJ dA K1nG</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6794</v>
+        <v>-0.8389</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-0.108</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9335</v>
+        <v>-0.9885</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6794</v>
+        <v>-0.8389</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6794</v>
+        <v>-0.4329</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6794</v>
+        <v>-0.4329</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6794</v>
+        <v>-0.4329</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6794</v>
+        <v>-0.4329</v>
       </c>
       <c r="N35" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36">
@@ -2060,16 +2060,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9224</v>
+        <v>-0.9725</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1188</v>
+        <v>-0.1252</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0441</v>
+        <v>-1.0482</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.9224</v>
+        <v>-0.9725</v>
       </c>
       <c r="F36" t="n">
         <v>-0.9224</v>
@@ -2106,16 +2106,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.0583</v>
+        <v>-1.0879</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1363</v>
+        <v>-0.1401</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.106</v>
+        <v>-1.0998</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.0583</v>
+        <v>-1.0879</v>
       </c>
       <c r="F37" t="n">
         <v>-0.1665</v>
@@ -2148,47 +2148,47 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>advent</t>
+          <t>nosraC</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.3095</v>
+        <v>-1.5126</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1686</v>
+        <v>-0.1948</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2203</v>
+        <v>-1.2895</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.3095</v>
+        <v>-1.5126</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.3095</v>
+        <v>-1.5462</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.3095</v>
+        <v>-1.5462</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.3095</v>
+        <v>-1.5462</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.3095</v>
+        <v>-1.5462</v>
       </c>
       <c r="N38" t="n">
-        <v>57</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.4209</v>
+        <v>-1.5223</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.183</v>
+        <v>-0.196</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.271</v>
+        <v>-1.2938</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.4209</v>
+        <v>-1.5223</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.4209</v>
+        <v>-1.4128</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.4209</v>
+        <v>-1.4128</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.4209</v>
+        <v>-1.4128</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.4209</v>
+        <v>-1.4128</v>
       </c>
       <c r="N39" t="n">
         <v>128</v>
@@ -2240,93 +2240,93 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>isak</t>
+          <t>advent</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.4864</v>
+        <v>-1.5326</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1914</v>
+        <v>-0.1974</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3008</v>
+        <v>-1.2984</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.4864</v>
+        <v>-1.5326</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.4864</v>
+        <v>-1.3095</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.4864</v>
+        <v>-1.3095</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.4864</v>
+        <v>-1.3095</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>128</v>
+        <v>57</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.4864</v>
+        <v>-1.3095</v>
       </c>
       <c r="N40" t="n">
-        <v>128</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>nosraC</t>
+          <t>isak</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.5462</v>
+        <v>-1.6517</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.1991</v>
+        <v>-0.2127</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3281</v>
+        <v>-1.3516</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.5462</v>
+        <v>-1.6517</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.5462</v>
+        <v>-1.4787</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.5462</v>
+        <v>-1.4787</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.5462</v>
+        <v>-1.4787</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>83</v>
+        <v>128</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.5462</v>
+        <v>-1.4787</v>
       </c>
       <c r="N41" t="n">
-        <v>83</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -9429,10 +9429,10 @@
         <v>1.26</v>
       </c>
       <c r="I177" t="n">
-        <v>0.6915</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="J177" t="n">
-        <v>32.5005</v>
+        <v>32.477</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.17</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4923</v>
+        <v>0.492</v>
       </c>
       <c r="J178" t="n">
-        <v>23.1381</v>
+        <v>23.124</v>
       </c>
     </row>
     <row r="179">
@@ -9506,13 +9506,13 @@
         <v>47</v>
       </c>
       <c r="H179" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="I179" t="n">
-        <v>0.3736</v>
+        <v>0.3976</v>
       </c>
       <c r="J179" t="n">
-        <v>17.5592</v>
+        <v>18.6872</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.02</v>
       </c>
       <c r="I180" t="n">
-        <v>0.0848</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="J180" t="n">
-        <v>3.9856</v>
+        <v>3.9715</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2498</v>
+        <v>-0.2502</v>
       </c>
       <c r="J181" t="n">
-        <v>-11.7406</v>
+        <v>-11.7594</v>
       </c>
     </row>
     <row r="182">
@@ -10026,13 +10026,13 @@
         <v>22</v>
       </c>
       <c r="H192" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="I192" t="n">
-        <v>1.6138</v>
+        <v>1.5913</v>
       </c>
       <c r="J192" t="n">
-        <v>35.5036</v>
+        <v>35.0086</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.12</v>
       </c>
       <c r="I193" t="n">
-        <v>0.3612</v>
+        <v>0.3624</v>
       </c>
       <c r="J193" t="n">
-        <v>7.9464</v>
+        <v>7.9728</v>
       </c>
     </row>
     <row r="194">
@@ -10106,13 +10106,13 @@
         <v>22</v>
       </c>
       <c r="H194" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="I194" t="n">
-        <v>0.1378</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="J194" t="n">
-        <v>3.0316</v>
+        <v>1.518</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.98</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1349</v>
+        <v>-0.1335</v>
       </c>
       <c r="J195" t="n">
-        <v>-2.9678</v>
+        <v>-2.937</v>
       </c>
     </row>
     <row r="196">
@@ -10189,16 +10189,16 @@
         <v>0.97</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.1715</v>
+        <v>-0.1701</v>
       </c>
       <c r="J196" t="n">
-        <v>-3.773</v>
+        <v>-3.7422</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>volt</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -10226,19 +10226,19 @@
         <v>22</v>
       </c>
       <c r="H197" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3829</v>
+        <v>0.4319</v>
       </c>
       <c r="J197" t="n">
-        <v>8.4238</v>
+        <v>9.501799999999999</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>volt</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -10266,13 +10266,13 @@
         <v>22</v>
       </c>
       <c r="H198" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="I198" t="n">
-        <v>0.3646</v>
+        <v>0.4143</v>
       </c>
       <c r="J198" t="n">
-        <v>8.0212</v>
+        <v>9.114599999999999</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.83</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2152</v>
+        <v>-0.2167</v>
       </c>
       <c r="J199" t="n">
-        <v>-4.7344</v>
+        <v>-4.7674</v>
       </c>
     </row>
     <row r="200">
@@ -10346,13 +10346,13 @@
         <v>22</v>
       </c>
       <c r="H200" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2746</v>
+        <v>-0.2665</v>
       </c>
       <c r="J200" t="n">
-        <v>-6.0412</v>
+        <v>-5.863</v>
       </c>
     </row>
     <row r="201">
@@ -10386,13 +10386,13 @@
         <v>22</v>
       </c>
       <c r="H201" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3313</v>
+        <v>-0.3236</v>
       </c>
       <c r="J201" t="n">
-        <v>-7.2886</v>
+        <v>-7.1192</v>
       </c>
     </row>
     <row r="202">

--- a/database/event/6868/event_6868_evp_summary.xlsx
+++ b/database/event/6868/event_6868_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.093</v>
+        <v>6.184</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7846</v>
+        <v>0.7963</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1078</v>
+        <v>2.2113</v>
       </c>
       <c r="E2" t="n">
-        <v>6.093</v>
+        <v>6.184</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7305</v>
+        <v>2.7723</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9435</v>
+        <v>2.9928</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1149</v>
+        <v>3.9657</v>
       </c>
       <c r="I2" t="n">
-        <v>2.222</v>
+        <v>2.2266</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9435</v>
+        <v>2.9928</v>
       </c>
       <c r="K2" t="n">
         <v>39</v>
@@ -529,7 +529,7 @@
         <v>121</v>
       </c>
       <c r="M2" t="n">
-        <v>5.1655</v>
+        <v>5.2194</v>
       </c>
       <c r="N2" t="n">
         <v>160</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.0879</v>
+        <v>5.7209</v>
       </c>
       <c r="C3" t="n">
-        <v>0.784</v>
+        <v>0.7367</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1055</v>
+        <v>2.0004</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0879</v>
+        <v>5.7209</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7623</v>
+        <v>3.5924</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0484</v>
+        <v>1.8513</v>
       </c>
       <c r="H3" t="n">
-        <v>7.5192</v>
+        <v>7.0447</v>
       </c>
       <c r="I3" t="n">
-        <v>4.0603</v>
+        <v>3.9554</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0484</v>
+        <v>1.8513</v>
       </c>
       <c r="K3" t="n">
         <v>101</v>
@@ -575,7 +575,7 @@
         <v>151</v>
       </c>
       <c r="M3" t="n">
-        <v>6.1087</v>
+        <v>5.8067</v>
       </c>
       <c r="N3" t="n">
         <v>252</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.6115</v>
+        <v>4.4652</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5938</v>
+        <v>0.575</v>
       </c>
       <c r="D4" t="n">
-        <v>1.446</v>
+        <v>1.4283</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6115</v>
+        <v>4.4652</v>
       </c>
       <c r="F4" t="n">
-        <v>3.6677</v>
+        <v>3.5582</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8028999999999999</v>
+        <v>0.7661</v>
       </c>
       <c r="H4" t="n">
-        <v>7.2068</v>
+        <v>6.9165</v>
       </c>
       <c r="I4" t="n">
-        <v>3.8916</v>
+        <v>3.8834</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8028999999999999</v>
+        <v>0.7661</v>
       </c>
       <c r="K4" t="n">
         <v>101</v>
@@ -621,7 +621,7 @@
         <v>151</v>
       </c>
       <c r="M4" t="n">
-        <v>4.6945</v>
+        <v>4.6495</v>
       </c>
       <c r="N4" t="n">
         <v>252</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.5976</v>
+        <v>3.5298</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4633</v>
+        <v>0.4545</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9931</v>
+        <v>1.0022</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5976</v>
+        <v>3.5298</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4692</v>
+        <v>2.5095</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0535</v>
+        <v>0.9454</v>
       </c>
       <c r="H5" t="n">
-        <v>3.2526</v>
+        <v>2.9792</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7564</v>
+        <v>1.6727</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0535</v>
+        <v>0.9454</v>
       </c>
       <c r="K5" t="n">
         <v>112</v>
@@ -667,7 +667,7 @@
         <v>63</v>
       </c>
       <c r="M5" t="n">
-        <v>2.8099</v>
+        <v>2.6181</v>
       </c>
       <c r="N5" t="n">
         <v>175</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.5613</v>
+        <v>3.4875</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4586</v>
+        <v>0.4491</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9769</v>
+        <v>0.9829</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5613</v>
+        <v>3.4875</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4593</v>
+        <v>1.3265</v>
       </c>
       <c r="G6" t="n">
-        <v>2.0257</v>
+        <v>2.0847</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4593</v>
+        <v>1.3265</v>
       </c>
       <c r="I6" t="n">
-        <v>0.788</v>
+        <v>0.7448</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0257</v>
+        <v>2.0847</v>
       </c>
       <c r="K6" t="n">
         <v>39</v>
@@ -713,7 +713,7 @@
         <v>121</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8137</v>
+        <v>2.8295</v>
       </c>
       <c r="N6" t="n">
         <v>160</v>
@@ -722,81 +722,81 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>kRaSnaL</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.2543</v>
+        <v>3.2452</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4191</v>
+        <v>0.4179</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8398</v>
+        <v>0.8726</v>
       </c>
       <c r="E7" t="n">
-        <v>3.2543</v>
+        <v>3.2452</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6845</v>
+        <v>2.5577</v>
       </c>
       <c r="G7" t="n">
-        <v>0.606</v>
+        <v>0.6363</v>
       </c>
       <c r="H7" t="n">
-        <v>3.963</v>
+        <v>3.1601</v>
       </c>
       <c r="I7" t="n">
-        <v>2.14</v>
+        <v>1.7743</v>
       </c>
       <c r="J7" t="n">
-        <v>0.606</v>
+        <v>0.6363</v>
       </c>
       <c r="K7" t="n">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="L7" t="n">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="M7" t="n">
-        <v>2.746</v>
+        <v>2.4106</v>
       </c>
       <c r="N7" t="n">
-        <v>252</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Calyx</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.1443</v>
+        <v>3.2409</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4049</v>
+        <v>0.4173</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7907</v>
+        <v>0.8706</v>
       </c>
       <c r="E8" t="n">
-        <v>3.1443</v>
+        <v>3.2409</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2542</v>
+        <v>2.69</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0384</v>
+        <v>0.5871</v>
       </c>
       <c r="H8" t="n">
-        <v>5.8425</v>
+        <v>3.6568</v>
       </c>
       <c r="I8" t="n">
-        <v>3.1549</v>
+        <v>2.0532</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0384</v>
+        <v>0.5871</v>
       </c>
       <c r="K8" t="n">
         <v>101</v>
@@ -805,7 +805,7 @@
         <v>151</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1933</v>
+        <v>2.6403</v>
       </c>
       <c r="N8" t="n">
         <v>252</v>
@@ -814,47 +814,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kRaSnaL</t>
+          <t>Calyx</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.1357</v>
+        <v>3.1399</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4038</v>
+        <v>0.4043</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7868000000000001</v>
+        <v>0.8246</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1357</v>
+        <v>3.1399</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4829</v>
+        <v>3.2044</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6016</v>
+        <v>0.0838</v>
       </c>
       <c r="H9" t="n">
-        <v>3.2978</v>
+        <v>5.5882</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7808</v>
+        <v>3.1376</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6016</v>
+        <v>0.0838</v>
       </c>
       <c r="K9" t="n">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="L9" t="n">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="M9" t="n">
-        <v>2.3824</v>
+        <v>3.2214</v>
       </c>
       <c r="N9" t="n">
-        <v>160</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.8016</v>
+        <v>2.8397</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3608</v>
+        <v>0.3657</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6375999999999999</v>
+        <v>0.6878</v>
       </c>
       <c r="E10" t="n">
-        <v>2.8016</v>
+        <v>2.8397</v>
       </c>
       <c r="F10" t="n">
-        <v>2.7644</v>
+        <v>2.8046</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1028</v>
+        <v>-0.1049</v>
       </c>
       <c r="H10" t="n">
-        <v>4.2265</v>
+        <v>4.087</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2823</v>
+        <v>2.2947</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1028</v>
+        <v>-0.1049</v>
       </c>
       <c r="K10" t="n">
         <v>69</v>
@@ -897,7 +897,7 @@
         <v>93</v>
       </c>
       <c r="M10" t="n">
-        <v>2.1795</v>
+        <v>2.1898</v>
       </c>
       <c r="N10" t="n">
         <v>162</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.4811</v>
+        <v>2.4663</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3195</v>
+        <v>0.3176</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4944</v>
+        <v>0.5177</v>
       </c>
       <c r="E11" t="n">
-        <v>2.4811</v>
+        <v>2.4663</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3362</v>
+        <v>2.3214</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.3883</v>
+        <v>2.3699</v>
       </c>
       <c r="I11" t="n">
-        <v>2.3883</v>
+        <v>2.3699</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.3883</v>
+        <v>2.3699</v>
       </c>
       <c r="N11" t="n">
         <v>128</v>
@@ -952,47 +952,47 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>DemQQ</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.4539</v>
+        <v>2.3934</v>
       </c>
       <c r="C12" t="n">
-        <v>0.316</v>
+        <v>0.3082</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4823</v>
+        <v>0.4845</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4539</v>
+        <v>2.3934</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2932</v>
+        <v>2.5596</v>
       </c>
       <c r="G12" t="n">
-        <v>1.3138</v>
+        <v>-0.0092</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2932</v>
+        <v>3.1674</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6983</v>
+        <v>1.7784</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3138</v>
+        <v>-0.0092</v>
       </c>
       <c r="K12" t="n">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="L12" t="n">
-        <v>63</v>
+        <v>121</v>
       </c>
       <c r="M12" t="n">
-        <v>2.0121</v>
+        <v>1.7692</v>
       </c>
       <c r="N12" t="n">
-        <v>175</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.4052</v>
+        <v>2.358</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3097</v>
+        <v>0.3036</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4605</v>
+        <v>0.4684</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4052</v>
+        <v>2.358</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7328</v>
+        <v>2.6981</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.4081</v>
+        <v>-0.4206</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1225</v>
+        <v>3.6873</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2261</v>
+        <v>2.0703</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4081</v>
+        <v>-0.4206</v>
       </c>
       <c r="K13" t="n">
         <v>112</v>
@@ -1035,7 +1035,7 @@
         <v>63</v>
       </c>
       <c r="M13" t="n">
-        <v>1.818</v>
+        <v>1.6497</v>
       </c>
       <c r="N13" t="n">
         <v>175</v>
@@ -1044,81 +1044,81 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DemQQ</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.2708</v>
+        <v>2.3257</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2924</v>
+        <v>0.2995</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4005</v>
+        <v>0.4537</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2708</v>
+        <v>2.3257</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4947</v>
+        <v>2.7066</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0669</v>
+        <v>-0.4126</v>
       </c>
       <c r="H14" t="n">
-        <v>3.3367</v>
+        <v>3.719</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8018</v>
+        <v>2.0881</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0669</v>
+        <v>-0.4126</v>
       </c>
       <c r="K14" t="n">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c r="L14" t="n">
-        <v>121</v>
+        <v>63</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7349</v>
+        <v>1.6755</v>
       </c>
       <c r="N14" t="n">
-        <v>160</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2683</v>
+        <v>2.251</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2921</v>
+        <v>0.2899</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3994</v>
+        <v>0.4196</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2683</v>
+        <v>2.251</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6776</v>
+        <v>1.1532</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.441</v>
+        <v>1.2509</v>
       </c>
       <c r="H15" t="n">
-        <v>3.9401</v>
+        <v>1.1532</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1276</v>
+        <v>0.6475</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.441</v>
+        <v>1.2509</v>
       </c>
       <c r="K15" t="n">
         <v>112</v>
@@ -1127,7 +1127,7 @@
         <v>63</v>
       </c>
       <c r="M15" t="n">
-        <v>1.6866</v>
+        <v>1.8984</v>
       </c>
       <c r="N15" t="n">
         <v>175</v>
@@ -1136,93 +1136,93 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Djoko</t>
+          <t>brnz4n</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.9891</v>
+        <v>1.759</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2561</v>
+        <v>0.2265</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2747</v>
+        <v>0.1955</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9891</v>
+        <v>1.759</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8138</v>
+        <v>0.7329</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.919</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8138</v>
+        <v>0.7329</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8138</v>
+        <v>0.4115</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.919</v>
       </c>
       <c r="K16" t="n">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="M16" t="n">
-        <v>1.8138</v>
+        <v>1.3305</v>
       </c>
       <c r="N16" t="n">
-        <v>85</v>
+        <v>162</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>brnz4n</t>
+          <t>Djoko</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9707</v>
+        <v>1.7492</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2538</v>
+        <v>0.2252</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2664</v>
+        <v>0.1911</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9707</v>
+        <v>1.7492</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8641</v>
+        <v>1.5739</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9995000000000001</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8641</v>
+        <v>1.5739</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4666</v>
+        <v>1.5739</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9995000000000001</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="L17" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4661</v>
+        <v>1.5739</v>
       </c>
       <c r="N17" t="n">
-        <v>162</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18">
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.6602</v>
+        <v>1.5045</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2138</v>
+        <v>0.1937</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1278</v>
+        <v>0.0796</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6602</v>
+        <v>1.5045</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2376</v>
+        <v>1.181</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5995</v>
+        <v>0.5004</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2376</v>
+        <v>1.181</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6683</v>
+        <v>0.6631</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5995</v>
+        <v>0.5004</v>
       </c>
       <c r="K18" t="n">
         <v>112</v>
@@ -1265,7 +1265,7 @@
         <v>63</v>
       </c>
       <c r="M18" t="n">
-        <v>1.2678</v>
+        <v>1.1635</v>
       </c>
       <c r="N18" t="n">
         <v>175</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.6169</v>
+        <v>1.3857</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2082</v>
+        <v>0.1784</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1084</v>
+        <v>0.0255</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6169</v>
+        <v>1.3857</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8276</v>
+        <v>0.7037</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7624</v>
+        <v>0.6551</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8276</v>
+        <v>0.7037</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4469</v>
+        <v>0.3951</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7624</v>
+        <v>0.6551</v>
       </c>
       <c r="K19" t="n">
         <v>69</v>
@@ -1311,7 +1311,7 @@
         <v>93</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2093</v>
+        <v>1.0502</v>
       </c>
       <c r="N19" t="n">
         <v>162</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.3091</v>
+        <v>1.2064</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1686</v>
+        <v>0.1554</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0291</v>
+        <v>-0.0562</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3091</v>
+        <v>1.2064</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9799</v>
+        <v>0.8772</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9799</v>
+        <v>0.8772</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9799</v>
+        <v>0.8772</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9799</v>
+        <v>0.8772</v>
       </c>
       <c r="N20" t="n">
         <v>85</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9908</v>
+        <v>0.9659</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1276</v>
+        <v>0.1244</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1713</v>
+        <v>-0.1658</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9908</v>
+        <v>0.9659</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1236</v>
+        <v>1.0987</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1236</v>
+        <v>1.0987</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1236</v>
+        <v>1.0987</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1236</v>
+        <v>1.0987</v>
       </c>
       <c r="N21" t="n">
         <v>128</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8074</v>
+        <v>0.7035</v>
       </c>
       <c r="C22" t="n">
-        <v>0.104</v>
+        <v>0.0906</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2532</v>
+        <v>-0.2853</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8074</v>
+        <v>0.7035</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7892</v>
+        <v>0.6853</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7892</v>
+        <v>0.6853</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7892</v>
+        <v>0.6853</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7892</v>
+        <v>0.6853</v>
       </c>
       <c r="N22" t="n">
         <v>83</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7236</v>
+        <v>0.6872</v>
       </c>
       <c r="C23" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.0885</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2906</v>
+        <v>-0.2927</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7236</v>
+        <v>0.6872</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6783</v>
+        <v>0.6419</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6783</v>
+        <v>0.6419</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6783</v>
+        <v>0.6419</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6783</v>
+        <v>0.6419</v>
       </c>
       <c r="N23" t="n">
         <v>128</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6041</v>
+        <v>0.6492</v>
       </c>
       <c r="C24" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.344</v>
+        <v>-0.31</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6041</v>
+        <v>0.6492</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3277</v>
+        <v>0.3728</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3277</v>
+        <v>0.3728</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3277</v>
+        <v>0.3728</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3277</v>
+        <v>0.3728</v>
       </c>
       <c r="N24" t="n">
         <v>83</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.445</v>
       </c>
       <c r="C25" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0573</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3543</v>
+        <v>-0.4031</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.445</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6591</v>
+        <v>0.523</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6591</v>
+        <v>0.523</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6591</v>
+        <v>0.523</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6591</v>
+        <v>0.523</v>
       </c>
       <c r="N25" t="n">
         <v>85</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4799</v>
+        <v>0.4105</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0618</v>
+        <v>0.0529</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3995</v>
+        <v>-0.4188</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4799</v>
+        <v>0.4105</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3589</v>
+        <v>0.2895</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3589</v>
+        <v>0.2895</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3589</v>
+        <v>0.2895</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3589</v>
+        <v>0.2895</v>
       </c>
       <c r="N26" t="n">
         <v>83</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2452</v>
+        <v>0.1853</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0316</v>
+        <v>0.0239</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5043</v>
+        <v>-0.5214</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2452</v>
+        <v>0.1853</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3193</v>
+        <v>0.2924</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1851</v>
+        <v>0.1521</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3193</v>
+        <v>0.2924</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1724</v>
+        <v>0.1642</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1851</v>
+        <v>0.1521</v>
       </c>
       <c r="K27" t="n">
         <v>101</v>
@@ -1679,7 +1679,7 @@
         <v>151</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3575</v>
+        <v>0.3163</v>
       </c>
       <c r="N27" t="n">
         <v>252</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1297</v>
+        <v>0.0578</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0167</v>
+        <v>0.0074</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.5795</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1297</v>
+        <v>0.0578</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2692</v>
+        <v>0.1973</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2692</v>
+        <v>0.1973</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2692</v>
+        <v>0.1973</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2692</v>
+        <v>0.1973</v>
       </c>
       <c r="N28" t="n">
         <v>85</v>
@@ -1734,93 +1734,93 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0781</v>
+        <v>0.0389</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0101</v>
+        <v>0.005</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5789</v>
+        <v>-0.5881</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0781</v>
+        <v>0.0389</v>
       </c>
       <c r="F29" t="n">
-        <v>0.208</v>
+        <v>-0.5655</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.2663</v>
       </c>
       <c r="H29" t="n">
-        <v>0.208</v>
+        <v>-0.5655</v>
       </c>
       <c r="I29" t="n">
-        <v>0.208</v>
+        <v>-0.3175</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.2663</v>
       </c>
       <c r="K29" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="M29" t="n">
-        <v>0.208</v>
+        <v>-0.05120000000000002</v>
       </c>
       <c r="N29" t="n">
-        <v>57</v>
+        <v>162</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0316</v>
+        <v>-0.0121</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0041</v>
+        <v>-0.0016</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6279</v>
+        <v>-0.6113</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0316</v>
+        <v>-0.0121</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.7106</v>
+        <v>0.1178</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3409</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.7106</v>
+        <v>0.1178</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3837</v>
+        <v>0.1178</v>
       </c>
       <c r="J30" t="n">
-        <v>0.3409</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="L30" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.0428</v>
+        <v>0.1178</v>
       </c>
       <c r="N30" t="n">
-        <v>162</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31">
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3245</v>
+        <v>-0.3111</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0418</v>
+        <v>-0.0401</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7588</v>
+        <v>-0.7475000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3245</v>
+        <v>-0.3111</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5961</v>
+        <v>0.5587</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.6692</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5961</v>
+        <v>0.5587</v>
       </c>
       <c r="I31" t="n">
-        <v>0.3219</v>
+        <v>0.3137</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.6692</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="K31" t="n">
         <v>69</v>
@@ -1863,7 +1863,7 @@
         <v>93</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3473</v>
+        <v>-0.3047</v>
       </c>
       <c r="N31" t="n">
         <v>162</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4759</v>
+        <v>-0.4296</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0613</v>
+        <v>-0.0553</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8264</v>
+        <v>-0.8015</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4759</v>
+        <v>-0.4296</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.4925</v>
+        <v>-0.4462</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4925</v>
+        <v>-0.4462</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4925</v>
+        <v>-0.4462</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4925</v>
+        <v>-0.4462</v>
       </c>
       <c r="N32" t="n">
         <v>57</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.7254</v>
+        <v>-0.6713</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0934</v>
+        <v>-0.0864</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9378</v>
+        <v>-0.9116</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.7254</v>
+        <v>-0.6713</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6794</v>
+        <v>-0.6253</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6794</v>
+        <v>-0.6253</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6794</v>
+        <v>-0.6253</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.6794</v>
+        <v>-0.6253</v>
       </c>
       <c r="N33" t="n">
         <v>83</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-0.7027</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0965</v>
+        <v>-0.0905</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9486</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-0.7027</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.5248</v>
+        <v>-0.478</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.5248</v>
+        <v>-0.478</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5248</v>
+        <v>-0.478</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.5248</v>
+        <v>-0.478</v>
       </c>
       <c r="N34" t="n">
         <v>57</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.8389</v>
+        <v>-0.8467</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.108</v>
+        <v>-0.109</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9885</v>
+        <v>-0.9915</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.8389</v>
+        <v>-0.8467</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.4329</v>
+        <v>-0.4407</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.4329</v>
+        <v>-0.4407</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4329</v>
+        <v>-0.4407</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.4329</v>
+        <v>-0.4407</v>
       </c>
       <c r="N35" t="n">
         <v>85</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9725</v>
+        <v>-0.9271</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1252</v>
+        <v>-0.1194</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0482</v>
+        <v>-1.0281</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.9725</v>
+        <v>-0.9271</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.9224</v>
+        <v>-0.877</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.9224</v>
+        <v>-0.877</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9224</v>
+        <v>-0.877</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9224</v>
+        <v>-0.877</v>
       </c>
       <c r="N36" t="n">
         <v>57</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.0879</v>
+        <v>-1.0803</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1401</v>
+        <v>-0.1391</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0998</v>
+        <v>-1.0979</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.0879</v>
+        <v>-1.0803</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.1665</v>
+        <v>-0.1574</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.8918</v>
+        <v>-0.8933</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.1665</v>
+        <v>-0.1574</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.08989999999999999</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.8918</v>
+        <v>-0.8933</v>
       </c>
       <c r="K37" t="n">
         <v>39</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.5126</v>
+        <v>-1.4383</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1948</v>
+        <v>-0.1852</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2895</v>
+        <v>-1.261</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.5126</v>
+        <v>-1.4383</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.5462</v>
+        <v>-1.4719</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.5462</v>
+        <v>-1.4719</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.5462</v>
+        <v>-1.4719</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.5462</v>
+        <v>-1.4719</v>
       </c>
       <c r="N38" t="n">
         <v>83</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.5223</v>
+        <v>-1.4986</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.196</v>
+        <v>-0.193</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2938</v>
+        <v>-1.2885</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.5223</v>
+        <v>-1.4986</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.4128</v>
+        <v>-1.3891</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.4128</v>
+        <v>-1.3891</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.4128</v>
+        <v>-1.3891</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.4128</v>
+        <v>-1.3891</v>
       </c>
       <c r="N39" t="n">
         <v>128</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.5326</v>
+        <v>-1.5081</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1974</v>
+        <v>-0.1942</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2984</v>
+        <v>-1.2928</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.5326</v>
+        <v>-1.5081</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.3095</v>
+        <v>-1.285</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.3095</v>
+        <v>-1.285</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.3095</v>
+        <v>-1.285</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.3095</v>
+        <v>-1.285</v>
       </c>
       <c r="N40" t="n">
         <v>57</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.6517</v>
+        <v>-1.6905</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.2127</v>
+        <v>-0.2177</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3516</v>
+        <v>-1.3759</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.6517</v>
+        <v>-1.6905</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.4787</v>
+        <v>-1.5175</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.4787</v>
+        <v>-1.5175</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.4787</v>
+        <v>-1.5175</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.4787</v>
+        <v>-1.5175</v>
       </c>
       <c r="N41" t="n">
         <v>128</v>
@@ -2429,10 +2429,10 @@
         <v>1.34</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8495</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>19.5385</v>
+        <v>19.0233</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.34</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8495</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>19.5385</v>
+        <v>19.0233</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.03</v>
       </c>
       <c r="I4" t="n">
-        <v>0.116</v>
+        <v>0.0946</v>
       </c>
       <c r="J4" t="n">
-        <v>2.668</v>
+        <v>2.1758</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.98</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1226</v>
+        <v>-0.0955</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.8198</v>
+        <v>-2.1965</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.97</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1592</v>
+        <v>-0.1277</v>
       </c>
       <c r="J6" t="n">
-        <v>-3.6616</v>
+        <v>-2.9371</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.29</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5721000000000001</v>
+        <v>0.5124</v>
       </c>
       <c r="J7" t="n">
-        <v>13.1583</v>
+        <v>11.7852</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.18</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3917</v>
+        <v>0.336</v>
       </c>
       <c r="J8" t="n">
-        <v>9.0091</v>
+        <v>7.728</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.03</v>
       </c>
       <c r="I9" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.0723</v>
       </c>
       <c r="J9" t="n">
-        <v>2.2241</v>
+        <v>1.6629</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.84</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2151</v>
+        <v>-0.1945</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.9473</v>
+        <v>-4.4735</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.84</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2151</v>
+        <v>-0.1945</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.9473</v>
+        <v>-4.4735</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.81</v>
       </c>
       <c r="I12" t="n">
-        <v>1.675</v>
+        <v>1.7147</v>
       </c>
       <c r="J12" t="n">
-        <v>58.625</v>
+        <v>60.0145</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.08</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2674</v>
+        <v>0.2344</v>
       </c>
       <c r="J13" t="n">
-        <v>9.359</v>
+        <v>8.204000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.95</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2253</v>
+        <v>-0.1883</v>
       </c>
       <c r="J14" t="n">
-        <v>-7.8855</v>
+        <v>-6.5905</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.95</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2253</v>
+        <v>-0.1883</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.8855</v>
+        <v>-6.5905</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.88</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4204</v>
+        <v>-0.3781</v>
       </c>
       <c r="J16" t="n">
-        <v>-14.714</v>
+        <v>-13.2335</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.5</v>
       </c>
       <c r="I17" t="n">
-        <v>0.878</v>
+        <v>0.8287</v>
       </c>
       <c r="J17" t="n">
-        <v>30.73</v>
+        <v>29.0045</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.45</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8063</v>
+        <v>0.7527</v>
       </c>
       <c r="J18" t="n">
-        <v>28.2205</v>
+        <v>26.3445</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.87</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1854</v>
+        <v>-0.1648</v>
       </c>
       <c r="J19" t="n">
-        <v>-6.489</v>
+        <v>-5.768</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.8</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2577</v>
+        <v>-0.2382</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.019500000000001</v>
+        <v>-8.337</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.68</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.371</v>
+        <v>-0.3587</v>
       </c>
       <c r="J21" t="n">
-        <v>-12.985</v>
+        <v>-12.5545</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.36</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7786999999999999</v>
+        <v>0.7625999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>22.5823</v>
+        <v>22.1154</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.12</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3736</v>
+        <v>0.335</v>
       </c>
       <c r="J23" t="n">
-        <v>10.8344</v>
+        <v>9.715</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.09</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2986</v>
+        <v>0.2627</v>
       </c>
       <c r="J24" t="n">
-        <v>8.6594</v>
+        <v>7.6183</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.06</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2159</v>
+        <v>0.1848</v>
       </c>
       <c r="J25" t="n">
-        <v>6.2611</v>
+        <v>5.3592</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.88</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4144</v>
+        <v>-0.3716</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.0176</v>
+        <v>-10.7764</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.14</v>
       </c>
       <c r="I27" t="n">
-        <v>0.331</v>
+        <v>0.2782</v>
       </c>
       <c r="J27" t="n">
-        <v>9.599</v>
+        <v>8.0678</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.09</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2352</v>
+        <v>0.1902</v>
       </c>
       <c r="J28" t="n">
-        <v>6.8208</v>
+        <v>5.5158</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.02</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0751</v>
+        <v>0.0534</v>
       </c>
       <c r="J29" t="n">
-        <v>2.1779</v>
+        <v>1.5486</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.87</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1789</v>
+        <v>-0.1586</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.1881</v>
+        <v>-4.5994</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2412</v>
+        <v>-0.221</v>
       </c>
       <c r="J31" t="n">
-        <v>-6.9948</v>
+        <v>-6.409</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.29</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4436</v>
+        <v>0.45</v>
       </c>
       <c r="J32" t="n">
-        <v>10.2028</v>
+        <v>10.35</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.08</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1619</v>
+        <v>0.1459</v>
       </c>
       <c r="J33" t="n">
-        <v>3.7237</v>
+        <v>3.3557</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.04</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0944</v>
+        <v>0.0809</v>
       </c>
       <c r="J34" t="n">
-        <v>2.1712</v>
+        <v>1.8607</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.03</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0756</v>
+        <v>0.0635</v>
       </c>
       <c r="J35" t="n">
-        <v>1.7388</v>
+        <v>1.4605</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.75</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3043</v>
+        <v>-0.2869</v>
       </c>
       <c r="J36" t="n">
-        <v>-6.9989</v>
+        <v>-6.5987</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.83</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8299</v>
+        <v>0.7819</v>
       </c>
       <c r="J37" t="n">
-        <v>19.0877</v>
+        <v>17.9837</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.39</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5008</v>
+        <v>0.4535</v>
       </c>
       <c r="J38" t="n">
-        <v>11.5184</v>
+        <v>10.4305</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.11</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1906</v>
+        <v>0.1499</v>
       </c>
       <c r="J39" t="n">
-        <v>4.3838</v>
+        <v>3.4477</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.72</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3391</v>
+        <v>-0.3248</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.7993</v>
+        <v>-7.4704</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.55</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4889</v>
+        <v>-0.4906</v>
       </c>
       <c r="J41" t="n">
-        <v>-11.2447</v>
+        <v>-11.2838</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.42</v>
       </c>
       <c r="I42" t="n">
-        <v>0.877</v>
+        <v>0.8627</v>
       </c>
       <c r="J42" t="n">
-        <v>35.957</v>
+        <v>35.3707</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.3</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6962</v>
+        <v>0.6807</v>
       </c>
       <c r="J43" t="n">
-        <v>28.5442</v>
+        <v>27.9087</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.06</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2208</v>
+        <v>0.1877</v>
       </c>
       <c r="J44" t="n">
-        <v>9.0528</v>
+        <v>7.6957</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.78</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.6462</v>
+        <v>-0.6106</v>
       </c>
       <c r="J45" t="n">
-        <v>-26.4942</v>
+        <v>-25.0346</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.76</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6911</v>
+        <v>-0.6584</v>
       </c>
       <c r="J46" t="n">
-        <v>-28.3351</v>
+        <v>-26.9944</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.34</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5946</v>
+        <v>0.5667</v>
       </c>
       <c r="J47" t="n">
-        <v>24.3786</v>
+        <v>23.2347</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.07</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1865</v>
+        <v>0.1482</v>
       </c>
       <c r="J48" t="n">
-        <v>7.6465</v>
+        <v>6.0762</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.95</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-0.0726</v>
       </c>
       <c r="J49" t="n">
-        <v>-3.6449</v>
+        <v>-2.9766</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.93</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1145</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="J50" t="n">
-        <v>-4.6945</v>
+        <v>-3.9442</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.89</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1614</v>
+        <v>-0.1411</v>
       </c>
       <c r="J51" t="n">
-        <v>-6.6174</v>
+        <v>-5.7851</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.49</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9586</v>
+        <v>0.9453</v>
       </c>
       <c r="J52" t="n">
-        <v>20.1306</v>
+        <v>19.8513</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.39</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8158</v>
+        <v>0.7997</v>
       </c>
       <c r="J53" t="n">
-        <v>17.1318</v>
+        <v>16.7937</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.18</v>
       </c>
       <c r="I54" t="n">
-        <v>0.491</v>
+        <v>0.4713</v>
       </c>
       <c r="J54" t="n">
-        <v>10.311</v>
+        <v>9.8973</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.87</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4458</v>
+        <v>-0.4038</v>
       </c>
       <c r="J55" t="n">
-        <v>-9.361800000000001</v>
+        <v>-8.479799999999999</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.74</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.7481</v>
+        <v>-0.7214</v>
       </c>
       <c r="J56" t="n">
-        <v>-15.7101</v>
+        <v>-15.1494</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.42</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6975</v>
+        <v>0.6663</v>
       </c>
       <c r="J57" t="n">
-        <v>14.6475</v>
+        <v>13.9923</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.41</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6864</v>
+        <v>0.6555</v>
       </c>
       <c r="J58" t="n">
-        <v>14.4144</v>
+        <v>13.7655</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.79</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2603</v>
+        <v>-0.2406</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.4663</v>
+        <v>-5.0526</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.78</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2701</v>
+        <v>-0.2507</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.6721</v>
+        <v>-5.2647</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.49</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-0.5354</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.1237</v>
+        <v>-11.2434</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.38</v>
       </c>
       <c r="I62" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.5975</v>
       </c>
       <c r="J62" t="n">
-        <v>10.621</v>
+        <v>11.3525</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.95</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.077</v>
+        <v>-0.0644</v>
       </c>
       <c r="J63" t="n">
-        <v>-1.463</v>
+        <v>-1.2236</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.91</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1266</v>
+        <v>-0.1105</v>
       </c>
       <c r="J64" t="n">
-        <v>-2.4054</v>
+        <v>-2.0995</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.65</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3816</v>
+        <v>-0.3687</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.2504</v>
+        <v>-7.0053</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.5</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5131</v>
+        <v>-0.515</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.748900000000001</v>
+        <v>-9.785</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.67</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6857</v>
+        <v>0.6412</v>
       </c>
       <c r="J67" t="n">
-        <v>13.0283</v>
+        <v>12.1828</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.65</v>
       </c>
       <c r="I68" t="n">
-        <v>0.6717</v>
+        <v>0.6283</v>
       </c>
       <c r="J68" t="n">
-        <v>12.7623</v>
+        <v>11.9377</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.16</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2404</v>
+        <v>0.1963</v>
       </c>
       <c r="J69" t="n">
-        <v>4.5676</v>
+        <v>3.7297</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.12</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1873</v>
+        <v>0.1493</v>
       </c>
       <c r="J70" t="n">
-        <v>3.5587</v>
+        <v>2.8367</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.02</v>
       </c>
       <c r="I71" t="n">
-        <v>0.0257</v>
+        <v>0.0144</v>
       </c>
       <c r="J71" t="n">
-        <v>0.4883</v>
+        <v>0.2736</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.76</v>
       </c>
       <c r="I72" t="n">
-        <v>1.3121</v>
+        <v>1.3205</v>
       </c>
       <c r="J72" t="n">
-        <v>30.1783</v>
+        <v>30.3715</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.19</v>
       </c>
       <c r="I73" t="n">
-        <v>0.504</v>
+        <v>0.4898</v>
       </c>
       <c r="J73" t="n">
-        <v>11.592</v>
+        <v>11.2654</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.02</v>
       </c>
       <c r="I74" t="n">
-        <v>0.0736</v>
+        <v>0.0572</v>
       </c>
       <c r="J74" t="n">
-        <v>1.6928</v>
+        <v>1.3156</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.01</v>
       </c>
       <c r="I75" t="n">
-        <v>0.0322</v>
+        <v>0.0223</v>
       </c>
       <c r="J75" t="n">
-        <v>0.7406</v>
+        <v>0.5129</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.85</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5013</v>
+        <v>-0.461</v>
       </c>
       <c r="J76" t="n">
-        <v>-11.5299</v>
+        <v>-10.603</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.21</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4575</v>
+        <v>0.4075</v>
       </c>
       <c r="J77" t="n">
-        <v>10.5225</v>
+        <v>9.3725</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.06</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1798</v>
+        <v>0.1406</v>
       </c>
       <c r="J78" t="n">
-        <v>4.1354</v>
+        <v>3.2338</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.96</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.0694</v>
+        <v>-0.0566</v>
       </c>
       <c r="J79" t="n">
-        <v>-1.5962</v>
+        <v>-1.3018</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.85</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1966</v>
+        <v>-0.1763</v>
       </c>
       <c r="J80" t="n">
-        <v>-4.5218</v>
+        <v>-4.0549</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.65</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3882</v>
+        <v>-0.3763</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.928599999999999</v>
+        <v>-8.6549</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>0.82</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.2103</v>
+        <v>-0.1944</v>
       </c>
       <c r="J82" t="n">
-        <v>-3.3648</v>
+        <v>-3.1104</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.79</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.2402</v>
+        <v>-0.2242</v>
       </c>
       <c r="J83" t="n">
-        <v>-3.8432</v>
+        <v>-3.5872</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.75</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2773</v>
+        <v>-0.2612</v>
       </c>
       <c r="J84" t="n">
-        <v>-4.4368</v>
+        <v>-4.1792</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.73</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2954</v>
+        <v>-0.2794</v>
       </c>
       <c r="J85" t="n">
-        <v>-4.7264</v>
+        <v>-4.4704</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3318</v>
+        <v>-0.3166</v>
       </c>
       <c r="J86" t="n">
-        <v>-5.3088</v>
+        <v>-5.0656</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.56</v>
       </c>
       <c r="I87" t="n">
-        <v>1.1456</v>
+        <v>1.1616</v>
       </c>
       <c r="J87" t="n">
-        <v>18.3296</v>
+        <v>18.5856</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.54</v>
       </c>
       <c r="I88" t="n">
-        <v>1.1199</v>
+        <v>1.1356</v>
       </c>
       <c r="J88" t="n">
-        <v>17.9184</v>
+        <v>18.1696</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.53</v>
       </c>
       <c r="I89" t="n">
-        <v>1.1071</v>
+        <v>1.1225</v>
       </c>
       <c r="J89" t="n">
-        <v>17.7136</v>
+        <v>17.96</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.35</v>
       </c>
       <c r="I90" t="n">
-        <v>0.8209</v>
+        <v>0.8087</v>
       </c>
       <c r="J90" t="n">
-        <v>13.1344</v>
+        <v>12.9392</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>1.17</v>
       </c>
       <c r="I91" t="n">
-        <v>0.4453</v>
+        <v>0.4145</v>
       </c>
       <c r="J91" t="n">
-        <v>7.1248</v>
+        <v>6.632</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.04</v>
       </c>
       <c r="I92" t="n">
-        <v>0.1617</v>
+        <v>0.1276</v>
       </c>
       <c r="J92" t="n">
-        <v>3.5574</v>
+        <v>2.8072</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.9</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1335</v>
+        <v>-0.1178</v>
       </c>
       <c r="J93" t="n">
-        <v>-2.937</v>
+        <v>-2.5916</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.8</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2366</v>
+        <v>-0.2181</v>
       </c>
       <c r="J94" t="n">
-        <v>-5.2052</v>
+        <v>-4.7982</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.73</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3032</v>
+        <v>-0.2858</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.6704</v>
+        <v>-6.2876</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3403</v>
+        <v>-0.3245</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.4866</v>
+        <v>-7.139</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.57</v>
       </c>
       <c r="I97" t="n">
-        <v>1.1916</v>
+        <v>1.2061</v>
       </c>
       <c r="J97" t="n">
-        <v>26.2152</v>
+        <v>26.5342</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.22</v>
       </c>
       <c r="I98" t="n">
-        <v>0.5845</v>
+        <v>0.5528</v>
       </c>
       <c r="J98" t="n">
-        <v>12.859</v>
+        <v>12.1616</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.21</v>
       </c>
       <c r="I99" t="n">
-        <v>0.5633</v>
+        <v>0.5312</v>
       </c>
       <c r="J99" t="n">
-        <v>12.3926</v>
+        <v>11.6864</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.13</v>
       </c>
       <c r="I100" t="n">
-        <v>0.3805</v>
+        <v>0.3473</v>
       </c>
       <c r="J100" t="n">
-        <v>8.371</v>
+        <v>7.6406</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.04</v>
       </c>
       <c r="I101" t="n">
-        <v>0.132</v>
+        <v>0.1084</v>
       </c>
       <c r="J101" t="n">
-        <v>2.904</v>
+        <v>2.3848</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.39</v>
       </c>
       <c r="I102" t="n">
-        <v>0.9207</v>
+        <v>0.907</v>
       </c>
       <c r="J102" t="n">
-        <v>18.414</v>
+        <v>18.14</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.31</v>
       </c>
       <c r="I103" t="n">
-        <v>0.7653</v>
+        <v>0.7407</v>
       </c>
       <c r="J103" t="n">
-        <v>15.306</v>
+        <v>14.814</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.31</v>
       </c>
       <c r="I104" t="n">
-        <v>0.7653</v>
+        <v>0.7407</v>
       </c>
       <c r="J104" t="n">
-        <v>15.306</v>
+        <v>14.814</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.25</v>
       </c>
       <c r="I105" t="n">
-        <v>0.6449</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="J105" t="n">
-        <v>12.898</v>
+        <v>12.308</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.96</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.213</v>
+        <v>-0.1793</v>
       </c>
       <c r="J106" t="n">
-        <v>-4.26</v>
+        <v>-3.586</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.17</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4202</v>
+        <v>0.367</v>
       </c>
       <c r="J107" t="n">
-        <v>8.404</v>
+        <v>7.34</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.93</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.1012</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="J108" t="n">
-        <v>-2.024</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.83</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2098</v>
+        <v>-0.1908</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.196</v>
+        <v>-3.816</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.76</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2782</v>
+        <v>-0.2596</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.564</v>
+        <v>-5.192</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.63</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3981</v>
+        <v>-0.3866</v>
       </c>
       <c r="J111" t="n">
-        <v>-7.962</v>
+        <v>-7.732</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.24</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6439</v>
+        <v>0.6087</v>
       </c>
       <c r="J112" t="n">
-        <v>14.8097</v>
+        <v>14.0001</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.19</v>
       </c>
       <c r="I113" t="n">
-        <v>0.5341</v>
+        <v>0.4958</v>
       </c>
       <c r="J113" t="n">
-        <v>12.2843</v>
+        <v>11.4034</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.17</v>
       </c>
       <c r="I114" t="n">
-        <v>0.4888</v>
+        <v>0.45</v>
       </c>
       <c r="J114" t="n">
-        <v>11.2424</v>
+        <v>10.35</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.06</v>
       </c>
       <c r="I115" t="n">
-        <v>0.2127</v>
+        <v>0.1826</v>
       </c>
       <c r="J115" t="n">
-        <v>4.8921</v>
+        <v>4.1998</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.95</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2231</v>
+        <v>-0.186</v>
       </c>
       <c r="J116" t="n">
-        <v>-5.1313</v>
+        <v>-4.278</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.13</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3201</v>
+        <v>0.2681</v>
       </c>
       <c r="J117" t="n">
-        <v>7.3623</v>
+        <v>6.1663</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.04</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1323</v>
+        <v>0.0998</v>
       </c>
       <c r="J118" t="n">
-        <v>3.0429</v>
+        <v>2.2954</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1</v>
       </c>
       <c r="I119" t="n">
-        <v>0.0055</v>
+        <v>0.0031</v>
       </c>
       <c r="J119" t="n">
-        <v>0.1265</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.8</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.248</v>
+        <v>-0.228</v>
       </c>
       <c r="J120" t="n">
-        <v>-5.704</v>
+        <v>-5.244</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.79</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2578</v>
+        <v>-0.2381</v>
       </c>
       <c r="J121" t="n">
-        <v>-5.9294</v>
+        <v>-5.4763</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.21</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5109</v>
+        <v>0.4613</v>
       </c>
       <c r="J122" t="n">
-        <v>11.2398</v>
+        <v>10.1486</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.82</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.2164</v>
+        <v>-0.1986</v>
       </c>
       <c r="J123" t="n">
-        <v>-4.7608</v>
+        <v>-4.3692</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.78</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2545</v>
+        <v>-0.2364</v>
       </c>
       <c r="J124" t="n">
-        <v>-5.599</v>
+        <v>-5.2008</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.7</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3295</v>
+        <v>-0.3133</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.249</v>
+        <v>-6.8926</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.58</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4376</v>
+        <v>-0.4296</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.6272</v>
+        <v>-9.4512</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.35</v>
       </c>
       <c r="I127" t="n">
-        <v>0.856</v>
+        <v>0.835</v>
       </c>
       <c r="J127" t="n">
-        <v>18.832</v>
+        <v>18.37</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.33</v>
       </c>
       <c r="I128" t="n">
-        <v>0.8162</v>
+        <v>0.7924</v>
       </c>
       <c r="J128" t="n">
-        <v>17.9564</v>
+        <v>17.4328</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.26</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6735</v>
+        <v>0.642</v>
       </c>
       <c r="J129" t="n">
-        <v>14.817</v>
+        <v>14.124</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.01</v>
       </c>
       <c r="I130" t="n">
-        <v>0.0287</v>
+        <v>0.0189</v>
       </c>
       <c r="J130" t="n">
-        <v>0.6314</v>
+        <v>0.4158</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.98</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.1324</v>
+        <v>-0.1051</v>
       </c>
       <c r="J131" t="n">
-        <v>-2.9128</v>
+        <v>-2.3122</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.93</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.0733</v>
+        <v>-0.0578</v>
       </c>
       <c r="J132" t="n">
-        <v>-1.2461</v>
+        <v>-0.9826</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.83</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.1913</v>
+        <v>-0.1758</v>
       </c>
       <c r="J133" t="n">
-        <v>-3.2521</v>
+        <v>-2.9886</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.73</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.291</v>
+        <v>-0.277</v>
       </c>
       <c r="J134" t="n">
-        <v>-4.947</v>
+        <v>-4.709</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.54</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.4591</v>
+        <v>-0.453</v>
       </c>
       <c r="J135" t="n">
-        <v>-7.8047</v>
+        <v>-7.701</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.48</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5118</v>
+        <v>-0.5115</v>
       </c>
       <c r="J136" t="n">
-        <v>-8.7006</v>
+        <v>-8.695499999999999</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.72</v>
       </c>
       <c r="I137" t="n">
-        <v>1.3723</v>
+        <v>1.3958</v>
       </c>
       <c r="J137" t="n">
-        <v>23.3291</v>
+        <v>23.7286</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.37</v>
       </c>
       <c r="I138" t="n">
-        <v>0.8731</v>
+        <v>0.8577</v>
       </c>
       <c r="J138" t="n">
-        <v>14.8427</v>
+        <v>14.5809</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.26</v>
       </c>
       <c r="I139" t="n">
-        <v>0.66</v>
+        <v>0.6337</v>
       </c>
       <c r="J139" t="n">
-        <v>11.22</v>
+        <v>10.7729</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.2</v>
       </c>
       <c r="I140" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.5027</v>
       </c>
       <c r="J140" t="n">
-        <v>9.057600000000001</v>
+        <v>8.5459</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2843</v>
+        <v>-0.2481</v>
       </c>
       <c r="J141" t="n">
-        <v>-4.8331</v>
+        <v>-4.2177</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.69</v>
       </c>
       <c r="I142" t="n">
-        <v>0.7725</v>
+        <v>0.7019</v>
       </c>
       <c r="J142" t="n">
-        <v>13.1325</v>
+        <v>11.9323</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.67</v>
       </c>
       <c r="I143" t="n">
-        <v>0.7542</v>
+        <v>0.6836</v>
       </c>
       <c r="J143" t="n">
-        <v>12.8214</v>
+        <v>11.6212</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.41</v>
       </c>
       <c r="I144" t="n">
-        <v>0.5089</v>
+        <v>0.4463</v>
       </c>
       <c r="J144" t="n">
-        <v>8.651300000000001</v>
+        <v>7.5871</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.36</v>
       </c>
       <c r="I145" t="n">
-        <v>0.4577</v>
+        <v>0.3979</v>
       </c>
       <c r="J145" t="n">
-        <v>7.7809</v>
+        <v>6.7643</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.24</v>
       </c>
       <c r="I146" t="n">
-        <v>0.3256</v>
+        <v>0.2745</v>
       </c>
       <c r="J146" t="n">
-        <v>5.5352</v>
+        <v>4.6665</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.26</v>
       </c>
       <c r="I147" t="n">
-        <v>0.503</v>
+        <v>0.5362</v>
       </c>
       <c r="J147" t="n">
-        <v>8.551</v>
+        <v>9.115399999999999</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.67</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.3479</v>
+        <v>-0.3337</v>
       </c>
       <c r="J148" t="n">
-        <v>-5.9143</v>
+        <v>-5.6729</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.65</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.3659</v>
+        <v>-0.3525</v>
       </c>
       <c r="J149" t="n">
-        <v>-6.2203</v>
+        <v>-5.9925</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.64</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3749</v>
+        <v>-0.362</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.3733</v>
+        <v>-6.154</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.47</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5248</v>
+        <v>-0.5265</v>
       </c>
       <c r="J151" t="n">
-        <v>-8.9216</v>
+        <v>-8.9505</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.35</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6633</v>
+        <v>0.6047</v>
       </c>
       <c r="J152" t="n">
-        <v>14.5926</v>
+        <v>13.3034</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.2</v>
       </c>
       <c r="I153" t="n">
-        <v>0.4246</v>
+        <v>0.3674</v>
       </c>
       <c r="J153" t="n">
-        <v>9.341200000000001</v>
+        <v>8.082800000000001</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.13</v>
       </c>
       <c r="I154" t="n">
-        <v>0.302</v>
+        <v>0.252</v>
       </c>
       <c r="J154" t="n">
-        <v>6.644</v>
+        <v>5.544</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.78</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2758</v>
+        <v>-0.257</v>
       </c>
       <c r="J155" t="n">
-        <v>-6.0676</v>
+        <v>-5.654</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.75</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3046</v>
+        <v>-0.2873</v>
       </c>
       <c r="J156" t="n">
-        <v>-6.7012</v>
+        <v>-6.3206</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.44</v>
       </c>
       <c r="I157" t="n">
-        <v>1.0274</v>
+        <v>1.0291</v>
       </c>
       <c r="J157" t="n">
-        <v>22.6028</v>
+        <v>22.6402</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.21</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5723</v>
+        <v>0.5363</v>
       </c>
       <c r="J158" t="n">
-        <v>12.5906</v>
+        <v>11.7986</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.15</v>
       </c>
       <c r="I159" t="n">
-        <v>0.439</v>
+        <v>0.4022</v>
       </c>
       <c r="J159" t="n">
-        <v>9.657999999999999</v>
+        <v>8.8484</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.14</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4158</v>
+        <v>0.3793</v>
       </c>
       <c r="J160" t="n">
-        <v>9.147600000000001</v>
+        <v>8.3446</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.84</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5237000000000001</v>
+        <v>-0.484</v>
       </c>
       <c r="J161" t="n">
-        <v>-11.5214</v>
+        <v>-10.648</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.14</v>
       </c>
       <c r="I162" t="n">
-        <v>0.3345</v>
+        <v>0.2815</v>
       </c>
       <c r="J162" t="n">
-        <v>8.028</v>
+        <v>6.756</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.13</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3159</v>
+        <v>0.2641</v>
       </c>
       <c r="J163" t="n">
-        <v>7.5816</v>
+        <v>6.3384</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.01</v>
       </c>
       <c r="I164" t="n">
-        <v>0.0469</v>
+        <v>0.0313</v>
       </c>
       <c r="J164" t="n">
-        <v>1.1256</v>
+        <v>0.7512</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.87</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1775</v>
+        <v>-0.1573</v>
       </c>
       <c r="J165" t="n">
-        <v>-4.26</v>
+        <v>-3.7752</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.7</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.345</v>
+        <v>-0.3297</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.279999999999999</v>
+        <v>-7.9128</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.49</v>
       </c>
       <c r="I167" t="n">
-        <v>1.1138</v>
+        <v>1.1269</v>
       </c>
       <c r="J167" t="n">
-        <v>26.7312</v>
+        <v>27.0456</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.43</v>
       </c>
       <c r="I168" t="n">
-        <v>1.0253</v>
+        <v>1.0271</v>
       </c>
       <c r="J168" t="n">
-        <v>24.6072</v>
+        <v>24.6504</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.3</v>
       </c>
       <c r="I169" t="n">
-        <v>0.7752</v>
+        <v>0.7469</v>
       </c>
       <c r="J169" t="n">
-        <v>18.6048</v>
+        <v>17.9256</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.73</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.7645999999999999</v>
+        <v>-0.7383999999999999</v>
       </c>
       <c r="J170" t="n">
-        <v>-18.3504</v>
+        <v>-17.7216</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.57</v>
       </c>
       <c r="I171" t="n">
-        <v>-1.0957</v>
+        <v>-1.1077</v>
       </c>
       <c r="J171" t="n">
-        <v>-26.2968</v>
+        <v>-26.5848</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.32</v>
       </c>
       <c r="I172" t="n">
-        <v>0.6312</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="J172" t="n">
-        <v>29.6664</v>
+        <v>26.9357</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.25</v>
       </c>
       <c r="I173" t="n">
-        <v>0.5192</v>
+        <v>0.4602</v>
       </c>
       <c r="J173" t="n">
-        <v>24.4024</v>
+        <v>21.6294</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.07</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1929</v>
+        <v>0.1527</v>
       </c>
       <c r="J174" t="n">
-        <v>9.0663</v>
+        <v>7.1769</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.72</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3285</v>
+        <v>-0.3122</v>
       </c>
       <c r="J175" t="n">
-        <v>-15.4395</v>
+        <v>-14.6734</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.6</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4366</v>
+        <v>-0.4301</v>
       </c>
       <c r="J176" t="n">
-        <v>-20.5202</v>
+        <v>-20.2147</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.26</v>
       </c>
       <c r="I177" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6575</v>
       </c>
       <c r="J177" t="n">
-        <v>32.477</v>
+        <v>30.9025</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.17</v>
       </c>
       <c r="I178" t="n">
-        <v>0.492</v>
+        <v>0.4524</v>
       </c>
       <c r="J178" t="n">
-        <v>23.124</v>
+        <v>21.2628</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.13</v>
       </c>
       <c r="I179" t="n">
-        <v>0.3976</v>
+        <v>0.3586</v>
       </c>
       <c r="J179" t="n">
-        <v>18.6872</v>
+        <v>16.8542</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.02</v>
       </c>
       <c r="I180" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.0668</v>
       </c>
       <c r="J180" t="n">
-        <v>3.9715</v>
+        <v>3.1396</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2502</v>
+        <v>-0.2113</v>
       </c>
       <c r="J181" t="n">
-        <v>-11.7594</v>
+        <v>-9.931100000000001</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.73</v>
       </c>
       <c r="I182" t="n">
-        <v>1.3936</v>
+        <v>1.419</v>
       </c>
       <c r="J182" t="n">
-        <v>29.2656</v>
+        <v>29.799</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.41</v>
       </c>
       <c r="I183" t="n">
-        <v>0.9537</v>
+        <v>0.9447</v>
       </c>
       <c r="J183" t="n">
-        <v>20.0277</v>
+        <v>19.8387</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.36</v>
       </c>
       <c r="I184" t="n">
-        <v>0.86</v>
+        <v>0.842</v>
       </c>
       <c r="J184" t="n">
-        <v>18.06</v>
+        <v>17.682</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.03</v>
       </c>
       <c r="I185" t="n">
-        <v>0.0936</v>
+        <v>0.073</v>
       </c>
       <c r="J185" t="n">
-        <v>1.9656</v>
+        <v>1.533</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.78</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.6807</v>
+        <v>-0.6522</v>
       </c>
       <c r="J186" t="n">
-        <v>-14.2947</v>
+        <v>-13.6962</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.22</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4695</v>
+        <v>0.4111</v>
       </c>
       <c r="J187" t="n">
-        <v>9.859500000000001</v>
+        <v>8.633100000000001</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.11</v>
       </c>
       <c r="I188" t="n">
-        <v>0.2734</v>
+        <v>0.2249</v>
       </c>
       <c r="J188" t="n">
-        <v>5.7414</v>
+        <v>4.7229</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.02</v>
       </c>
       <c r="I189" t="n">
-        <v>0.0743</v>
+        <v>0.053</v>
       </c>
       <c r="J189" t="n">
-        <v>1.5603</v>
+        <v>1.113</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.95</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.08550000000000001</v>
+        <v>-0.0699</v>
       </c>
       <c r="J190" t="n">
-        <v>-1.7955</v>
+        <v>-1.4679</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.66</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3833</v>
+        <v>-0.3715</v>
       </c>
       <c r="J191" t="n">
-        <v>-8.049300000000001</v>
+        <v>-7.8015</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.87</v>
       </c>
       <c r="I192" t="n">
-        <v>1.5913</v>
+        <v>1.6372</v>
       </c>
       <c r="J192" t="n">
-        <v>35.0086</v>
+        <v>36.0184</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.12</v>
       </c>
       <c r="I193" t="n">
-        <v>0.3624</v>
+        <v>0.3283</v>
       </c>
       <c r="J193" t="n">
-        <v>7.9728</v>
+        <v>7.2226</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.02</v>
       </c>
       <c r="I194" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0529</v>
       </c>
       <c r="J194" t="n">
-        <v>1.518</v>
+        <v>1.1638</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.98</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1335</v>
+        <v>-0.1062</v>
       </c>
       <c r="J195" t="n">
-        <v>-2.937</v>
+        <v>-2.3364</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.97</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.1701</v>
+        <v>-0.1387</v>
       </c>
       <c r="J196" t="n">
-        <v>-3.7422</v>
+        <v>-3.0514</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.19</v>
       </c>
       <c r="I197" t="n">
-        <v>0.4319</v>
+        <v>0.3753</v>
       </c>
       <c r="J197" t="n">
-        <v>9.501799999999999</v>
+        <v>8.256600000000001</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.18</v>
       </c>
       <c r="I198" t="n">
-        <v>0.4143</v>
+        <v>0.3582</v>
       </c>
       <c r="J198" t="n">
-        <v>9.114599999999999</v>
+        <v>7.8804</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.83</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2167</v>
+        <v>-0.1964</v>
       </c>
       <c r="J199" t="n">
-        <v>-4.7674</v>
+        <v>-4.3208</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.78</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2665</v>
+        <v>-0.247</v>
       </c>
       <c r="J200" t="n">
-        <v>-5.863</v>
+        <v>-5.434</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.72</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3236</v>
+        <v>-0.3068</v>
       </c>
       <c r="J201" t="n">
-        <v>-7.1192</v>
+        <v>-6.7496</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.63</v>
       </c>
       <c r="I202" t="n">
-        <v>1.2754</v>
+        <v>1.2941</v>
       </c>
       <c r="J202" t="n">
-        <v>28.0588</v>
+        <v>28.4702</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.35</v>
       </c>
       <c r="I203" t="n">
-        <v>0.8494</v>
+        <v>0.8289</v>
       </c>
       <c r="J203" t="n">
-        <v>18.6868</v>
+        <v>18.2358</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.16</v>
       </c>
       <c r="I204" t="n">
-        <v>0.4546</v>
+        <v>0.4206</v>
       </c>
       <c r="J204" t="n">
-        <v>10.0012</v>
+        <v>9.2532</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.14</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4075</v>
+        <v>0.3736</v>
       </c>
       <c r="J205" t="n">
-        <v>8.965</v>
+        <v>8.219200000000001</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.8</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.628</v>
+        <v>-0.5948</v>
       </c>
       <c r="J206" t="n">
-        <v>-13.816</v>
+        <v>-13.0856</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.11</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3008</v>
+        <v>0.2515</v>
       </c>
       <c r="J207" t="n">
-        <v>6.6176</v>
+        <v>5.533</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.99</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.0148</v>
+        <v>-0.0103</v>
       </c>
       <c r="J208" t="n">
-        <v>-0.3256</v>
+        <v>-0.2266</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.92</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1151</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="J209" t="n">
-        <v>-2.5322</v>
+        <v>-2.1912</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.8</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.241</v>
+        <v>-0.2216</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.302</v>
+        <v>-4.8752</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.58</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.444</v>
+        <v>-0.4372</v>
       </c>
       <c r="J211" t="n">
-        <v>-9.768000000000001</v>
+        <v>-9.618399999999999</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.41</v>
       </c>
       <c r="I212" t="n">
-        <v>0.9937</v>
+        <v>0.9897</v>
       </c>
       <c r="J212" t="n">
-        <v>23.8488</v>
+        <v>23.7528</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.24</v>
       </c>
       <c r="I213" t="n">
-        <v>0.6495</v>
+        <v>0.6138</v>
       </c>
       <c r="J213" t="n">
-        <v>15.588</v>
+        <v>14.7312</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.16</v>
       </c>
       <c r="I214" t="n">
-        <v>0.4699</v>
+        <v>0.4299</v>
       </c>
       <c r="J214" t="n">
-        <v>11.2776</v>
+        <v>10.3176</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.92</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3068</v>
+        <v>-0.2654</v>
       </c>
       <c r="J215" t="n">
-        <v>-7.3632</v>
+        <v>-6.3696</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.76</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.6976</v>
+        <v>-0.666</v>
       </c>
       <c r="J216" t="n">
-        <v>-16.7424</v>
+        <v>-15.984</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.46</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8308</v>
+        <v>0.7798</v>
       </c>
       <c r="J217" t="n">
-        <v>19.9392</v>
+        <v>18.7152</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.09</v>
       </c>
       <c r="I218" t="n">
-        <v>0.2282</v>
+        <v>0.1847</v>
       </c>
       <c r="J218" t="n">
-        <v>5.4768</v>
+        <v>4.4328</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.99</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.027</v>
+        <v>-0.0192</v>
       </c>
       <c r="J219" t="n">
-        <v>-0.648</v>
+        <v>-0.4608</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.9</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1493</v>
+        <v>-0.1295</v>
       </c>
       <c r="J220" t="n">
-        <v>-3.5832</v>
+        <v>-3.108</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.7</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3501</v>
+        <v>-0.3357</v>
       </c>
       <c r="J221" t="n">
-        <v>-8.4024</v>
+        <v>-8.056800000000001</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.72</v>
       </c>
       <c r="I222" t="n">
-        <v>1.362</v>
+        <v>1.3846</v>
       </c>
       <c r="J222" t="n">
-        <v>24.516</v>
+        <v>24.9228</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.36</v>
       </c>
       <c r="I223" t="n">
-        <v>0.8481</v>
+        <v>0.8337</v>
       </c>
       <c r="J223" t="n">
-        <v>15.2658</v>
+        <v>15.0066</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.28</v>
       </c>
       <c r="I224" t="n">
-        <v>0.6944</v>
+        <v>0.6718</v>
       </c>
       <c r="J224" t="n">
-        <v>12.4992</v>
+        <v>12.0924</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.23</v>
       </c>
       <c r="I225" t="n">
-        <v>0.5908</v>
+        <v>0.5638</v>
       </c>
       <c r="J225" t="n">
-        <v>10.6344</v>
+        <v>10.1484</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.14</v>
       </c>
       <c r="I226" t="n">
-        <v>0.3872</v>
+        <v>0.3553</v>
       </c>
       <c r="J226" t="n">
-        <v>6.9696</v>
+        <v>6.3954</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.06</v>
       </c>
       <c r="I227" t="n">
-        <v>0.2089</v>
+        <v>0.1692</v>
       </c>
       <c r="J227" t="n">
-        <v>3.7602</v>
+        <v>3.0456</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.0848</v>
+        <v>-0.0718</v>
       </c>
       <c r="J228" t="n">
-        <v>-1.5264</v>
+        <v>-1.2924</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.91</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.122</v>
+        <v>-0.1069</v>
       </c>
       <c r="J229" t="n">
-        <v>-2.196</v>
+        <v>-1.9242</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.65</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3769</v>
+        <v>-0.3636</v>
       </c>
       <c r="J230" t="n">
-        <v>-6.7842</v>
+        <v>-6.5448</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.61</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4128</v>
+        <v>-0.4024</v>
       </c>
       <c r="J231" t="n">
-        <v>-7.4304</v>
+        <v>-7.2432</v>
       </c>
     </row>
   </sheetData>
